--- a/app/templates/Template_Proctor.xlsx
+++ b/app/templates/Template_Proctor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE287EAC-D3DC-4240-B489-A1AF6DF790E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B8D959-2B5B-40D6-A8A8-211AA6506958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="339">
   <si>
     <t>:</t>
   </si>
@@ -1175,18 +1175,6 @@
   </si>
   <si>
     <t>Equipo utilizado</t>
-  </si>
-  <si>
-    <t>si o no</t>
-  </si>
-  <si>
-    <t>Húmedo o Seco</t>
-  </si>
-  <si>
-    <t>Manual o mecanico</t>
-  </si>
-  <si>
-    <t>se colocara si se realiza el ensayo</t>
   </si>
   <si>
     <t xml:space="preserve">* W Perdida de masa seca constante (adicional), para metodo B es &lt; 0.1% </t>
@@ -4993,22 +4981,22 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="102" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="104" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="101" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="107" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="108" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="102" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5019,35 +5007,60 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="109" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="110" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="101" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="102" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="104" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="78" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="98" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5123,136 +5136,46 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="98" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="78" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="78" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="98" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="102" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="107" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="108" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="104" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="109" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="110" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5281,6 +5204,10 @@
     <xf numFmtId="0" fontId="55" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5299,6 +5226,9 @@
     <xf numFmtId="164" fontId="14" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5310,6 +5240,130 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="78" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="96" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="98" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="78" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="98" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="87" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="53" fillId="3" borderId="78" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="53" fillId="3" borderId="96" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="53" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="53" fillId="3" borderId="1" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -5325,68 +5379,9 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="87" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="53" fillId="3" borderId="78" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="53" fillId="3" borderId="96" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="53" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="53" fillId="3" borderId="1" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="78" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="96" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="98" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="78" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="98" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="106" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5412,9 +5407,56 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="80" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="81" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="75" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="92" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="84" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="85" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="87" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="84" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="86" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="88" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="89" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5467,57 +5509,6 @@
     <xf numFmtId="0" fontId="46" fillId="11" borderId="79" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="80" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="81" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="75" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="92" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="84" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="85" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="87" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="84" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="86" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="88" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="89" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="9" borderId="69" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5607,9 +5598,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="78" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -7002,13 +6990,6 @@
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-PE" sz="1000" b="0">
-            <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="es-PE" sz="1000" b="0">
               <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
@@ -7088,13 +7069,6 @@
             </a:rPr>
             <a:t>Aprobado:</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-PE" sz="1000" b="0">
-            <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
@@ -10082,74 +10056,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="580"/>
-      <c r="B1" s="581"/>
-      <c r="C1" s="581"/>
-      <c r="D1" s="581"/>
-      <c r="E1" s="581"/>
-      <c r="F1" s="581"/>
-      <c r="G1" s="581"/>
-      <c r="H1" s="581"/>
-      <c r="I1" s="582"/>
+      <c r="A1" s="585"/>
+      <c r="B1" s="586"/>
+      <c r="C1" s="586"/>
+      <c r="D1" s="586"/>
+      <c r="E1" s="586"/>
+      <c r="F1" s="586"/>
+      <c r="G1" s="586"/>
+      <c r="H1" s="586"/>
+      <c r="I1" s="587"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="583"/>
-      <c r="B2" s="584"/>
-      <c r="C2" s="584"/>
-      <c r="D2" s="584"/>
-      <c r="E2" s="584"/>
-      <c r="F2" s="584"/>
-      <c r="G2" s="584"/>
-      <c r="H2" s="584"/>
-      <c r="I2" s="585"/>
+      <c r="A2" s="588"/>
+      <c r="B2" s="589"/>
+      <c r="C2" s="589"/>
+      <c r="D2" s="589"/>
+      <c r="E2" s="589"/>
+      <c r="F2" s="589"/>
+      <c r="G2" s="589"/>
+      <c r="H2" s="589"/>
+      <c r="I2" s="590"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="583"/>
-      <c r="B3" s="584"/>
-      <c r="C3" s="584"/>
-      <c r="D3" s="584"/>
-      <c r="E3" s="584"/>
-      <c r="F3" s="584"/>
-      <c r="G3" s="584"/>
-      <c r="H3" s="584"/>
-      <c r="I3" s="585"/>
+      <c r="A3" s="588"/>
+      <c r="B3" s="589"/>
+      <c r="C3" s="589"/>
+      <c r="D3" s="589"/>
+      <c r="E3" s="589"/>
+      <c r="F3" s="589"/>
+      <c r="G3" s="589"/>
+      <c r="H3" s="589"/>
+      <c r="I3" s="590"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="586"/>
-      <c r="B4" s="587"/>
-      <c r="C4" s="587"/>
-      <c r="D4" s="587"/>
-      <c r="E4" s="587"/>
-      <c r="F4" s="587"/>
-      <c r="G4" s="587"/>
-      <c r="H4" s="587"/>
-      <c r="I4" s="588"/>
+      <c r="A4" s="591"/>
+      <c r="B4" s="592"/>
+      <c r="C4" s="592"/>
+      <c r="D4" s="592"/>
+      <c r="E4" s="592"/>
+      <c r="F4" s="592"/>
+      <c r="G4" s="592"/>
+      <c r="H4" s="592"/>
+      <c r="I4" s="593"/>
     </row>
     <row r="5" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="589" t="s">
+      <c r="A5" s="594" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="589"/>
-      <c r="C5" s="589"/>
-      <c r="D5" s="589"/>
-      <c r="E5" s="589"/>
-      <c r="F5" s="589"/>
-      <c r="G5" s="589"/>
-      <c r="H5" s="589"/>
-      <c r="I5" s="589"/>
+      <c r="B5" s="594"/>
+      <c r="C5" s="594"/>
+      <c r="D5" s="594"/>
+      <c r="E5" s="594"/>
+      <c r="F5" s="594"/>
+      <c r="G5" s="594"/>
+      <c r="H5" s="594"/>
+      <c r="I5" s="594"/>
     </row>
     <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="590" t="s">
+      <c r="A6" s="595" t="s">
         <v>279</v>
       </c>
-      <c r="B6" s="590"/>
-      <c r="C6" s="590"/>
-      <c r="D6" s="590"/>
-      <c r="E6" s="590"/>
-      <c r="F6" s="590"/>
-      <c r="G6" s="590"/>
-      <c r="H6" s="590"/>
-      <c r="I6" s="590"/>
+      <c r="B6" s="595"/>
+      <c r="C6" s="595"/>
+      <c r="D6" s="595"/>
+      <c r="E6" s="595"/>
+      <c r="F6" s="595"/>
+      <c r="G6" s="595"/>
+      <c r="H6" s="595"/>
+      <c r="I6" s="595"/>
       <c r="L6"/>
     </row>
     <row r="7" spans="1:12" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10166,68 +10140,68 @@
     <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="473"/>
       <c r="B8" s="559" t="s">
-        <v>342</v>
-      </c>
-      <c r="C8" s="598" t="s">
+        <v>338</v>
+      </c>
+      <c r="C8" s="603" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="599"/>
+      <c r="D8" s="604"/>
       <c r="E8" s="562"/>
-      <c r="F8" s="600" t="s">
-        <v>341</v>
-      </c>
-      <c r="G8" s="599"/>
+      <c r="F8" s="605" t="s">
+        <v>337</v>
+      </c>
+      <c r="G8" s="604"/>
       <c r="H8" s="560" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I8" s="474"/>
     </row>
     <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="557"/>
-      <c r="C9" s="755"/>
-      <c r="D9" s="602"/>
+      <c r="C9" s="608"/>
+      <c r="D9" s="607"/>
       <c r="E9" s="561"/>
-      <c r="F9" s="601"/>
-      <c r="G9" s="602"/>
+      <c r="F9" s="606"/>
+      <c r="G9" s="607"/>
       <c r="H9" s="558"/>
       <c r="I9" s="474"/>
     </row>
     <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="476"/>
-      <c r="B10" s="593"/>
-      <c r="C10" s="593"/>
-      <c r="D10" s="593"/>
+      <c r="B10" s="598"/>
+      <c r="C10" s="598"/>
+      <c r="D10" s="598"/>
       <c r="E10" s="475"/>
-      <c r="F10" s="593"/>
-      <c r="G10" s="593"/>
+      <c r="F10" s="598"/>
+      <c r="G10" s="598"/>
       <c r="H10" s="475"/>
       <c r="I10" s="477"/>
     </row>
     <row r="11" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="594" t="s">
+      <c r="A11" s="599" t="s">
         <v>292</v>
       </c>
-      <c r="B11" s="595"/>
-      <c r="C11" s="595"/>
-      <c r="D11" s="595"/>
-      <c r="E11" s="596"/>
-      <c r="F11" s="595"/>
-      <c r="G11" s="595"/>
-      <c r="H11" s="595"/>
-      <c r="I11" s="597"/>
+      <c r="B11" s="600"/>
+      <c r="C11" s="600"/>
+      <c r="D11" s="600"/>
+      <c r="E11" s="601"/>
+      <c r="F11" s="600"/>
+      <c r="G11" s="600"/>
+      <c r="H11" s="600"/>
+      <c r="I11" s="602"/>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="605" t="s">
-        <v>331</v>
-      </c>
-      <c r="B12" s="606"/>
-      <c r="C12" s="607"/>
-      <c r="D12" s="606"/>
-      <c r="E12" s="607"/>
-      <c r="F12" s="606"/>
-      <c r="G12" s="607"/>
-      <c r="H12" s="606"/>
-      <c r="I12" s="608"/>
+      <c r="A12" s="577" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="578"/>
+      <c r="C12" s="579"/>
+      <c r="D12" s="578"/>
+      <c r="E12" s="579"/>
+      <c r="F12" s="578"/>
+      <c r="G12" s="579"/>
+      <c r="H12" s="578"/>
+      <c r="I12" s="580"/>
     </row>
     <row r="13" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="478"/>
@@ -10256,120 +10230,120 @@
       <c r="I14" s="488"/>
     </row>
     <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="565" t="s">
+      <c r="A15" s="581" t="s">
         <v>253</v>
       </c>
-      <c r="B15" s="565"/>
+      <c r="B15" s="581"/>
       <c r="C15" s="489" t="s">
         <v>287</v>
       </c>
-      <c r="D15" s="591"/>
-      <c r="E15" s="592"/>
+      <c r="D15" s="596"/>
+      <c r="E15" s="597"/>
       <c r="F15" s="490"/>
       <c r="G15" s="491"/>
       <c r="H15" s="491"/>
       <c r="I15" s="490"/>
     </row>
     <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="566" t="s">
+      <c r="A16" s="576" t="s">
         <v>254</v>
       </c>
-      <c r="B16" s="566"/>
+      <c r="B16" s="576"/>
       <c r="C16" s="492" t="s">
         <v>287</v>
       </c>
-      <c r="D16" s="563"/>
-      <c r="E16" s="564"/>
+      <c r="D16" s="566"/>
+      <c r="E16" s="567"/>
       <c r="F16" s="493"/>
       <c r="G16" s="494"/>
       <c r="H16" s="494"/>
       <c r="I16" s="493"/>
     </row>
     <row r="17" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="566" t="s">
+      <c r="A17" s="576" t="s">
         <v>255</v>
       </c>
-      <c r="B17" s="566"/>
+      <c r="B17" s="576"/>
       <c r="C17" s="492" t="s">
         <v>287</v>
       </c>
-      <c r="D17" s="563"/>
-      <c r="E17" s="564"/>
+      <c r="D17" s="566"/>
+      <c r="E17" s="567"/>
       <c r="F17" s="493"/>
       <c r="G17" s="494"/>
       <c r="H17" s="494"/>
       <c r="I17" s="493"/>
     </row>
     <row r="18" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="566" t="s">
+      <c r="A18" s="576" t="s">
         <v>303</v>
       </c>
-      <c r="B18" s="566"/>
+      <c r="B18" s="576"/>
       <c r="C18" s="494" t="s">
         <v>288</v>
       </c>
-      <c r="D18" s="563"/>
-      <c r="E18" s="564"/>
+      <c r="D18" s="566"/>
+      <c r="E18" s="567"/>
       <c r="F18" s="495"/>
       <c r="G18" s="496"/>
       <c r="H18" s="496"/>
       <c r="I18" s="495"/>
     </row>
     <row r="19" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="566" t="s">
+      <c r="A19" s="576" t="s">
         <v>302</v>
       </c>
-      <c r="B19" s="566"/>
+      <c r="B19" s="576"/>
       <c r="C19" s="494" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="563"/>
-      <c r="E19" s="564"/>
+      <c r="D19" s="566"/>
+      <c r="E19" s="567"/>
       <c r="F19" s="493"/>
       <c r="G19" s="494"/>
       <c r="H19" s="497"/>
       <c r="I19" s="498"/>
     </row>
     <row r="20" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="609" t="s">
+      <c r="A20" s="582" t="s">
         <v>301</v>
       </c>
-      <c r="B20" s="610"/>
+      <c r="B20" s="583"/>
       <c r="C20" s="499" t="s">
         <v>288</v>
       </c>
-      <c r="D20" s="563"/>
-      <c r="E20" s="564"/>
+      <c r="D20" s="566"/>
+      <c r="E20" s="567"/>
       <c r="F20" s="493"/>
       <c r="G20" s="494"/>
       <c r="H20" s="497"/>
       <c r="I20" s="498"/>
     </row>
     <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="566" t="s">
+      <c r="A21" s="576" t="s">
         <v>300</v>
       </c>
-      <c r="B21" s="566"/>
+      <c r="B21" s="576"/>
       <c r="C21" s="494" t="s">
         <v>290</v>
       </c>
-      <c r="D21" s="563"/>
-      <c r="E21" s="564"/>
+      <c r="D21" s="566"/>
+      <c r="E21" s="567"/>
       <c r="F21" s="493"/>
       <c r="G21" s="494"/>
       <c r="H21" s="494"/>
       <c r="I21" s="493"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="572" t="s">
+      <c r="A22" s="584" t="s">
         <v>299</v>
       </c>
-      <c r="B22" s="572"/>
+      <c r="B22" s="584"/>
       <c r="C22" s="500" t="s">
         <v>289</v>
       </c>
-      <c r="D22" s="563"/>
-      <c r="E22" s="564"/>
+      <c r="D22" s="566"/>
+      <c r="E22" s="567"/>
       <c r="F22" s="501"/>
       <c r="G22" s="502"/>
       <c r="H22" s="502"/>
@@ -10389,148 +10363,148 @@
       <c r="I23" s="503"/>
     </row>
     <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="565" t="s">
+      <c r="A24" s="581" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="565"/>
+      <c r="B24" s="581"/>
       <c r="C24" s="504"/>
-      <c r="D24" s="567"/>
-      <c r="E24" s="568"/>
+      <c r="D24" s="614"/>
+      <c r="E24" s="615"/>
       <c r="F24" s="505"/>
       <c r="G24" s="506"/>
       <c r="H24" s="506"/>
       <c r="I24" s="505"/>
     </row>
     <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="566" t="s">
+      <c r="A25" s="576" t="s">
         <v>304</v>
       </c>
-      <c r="B25" s="566"/>
+      <c r="B25" s="576"/>
       <c r="C25" s="499" t="s">
         <v>288</v>
       </c>
-      <c r="D25" s="569"/>
-      <c r="E25" s="570"/>
+      <c r="D25" s="568"/>
+      <c r="E25" s="569"/>
       <c r="F25" s="507"/>
       <c r="G25" s="508"/>
       <c r="H25" s="508"/>
       <c r="I25" s="507"/>
     </row>
     <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="566" t="s">
+      <c r="A26" s="576" t="s">
         <v>305</v>
       </c>
-      <c r="B26" s="566"/>
+      <c r="B26" s="576"/>
       <c r="C26" s="499" t="s">
         <v>288</v>
       </c>
-      <c r="D26" s="569"/>
-      <c r="E26" s="570"/>
+      <c r="D26" s="568"/>
+      <c r="E26" s="569"/>
       <c r="F26" s="507"/>
       <c r="G26" s="508"/>
       <c r="H26" s="508"/>
       <c r="I26" s="507"/>
     </row>
     <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="566" t="s">
+      <c r="A27" s="576" t="s">
         <v>298</v>
       </c>
-      <c r="B27" s="566"/>
+      <c r="B27" s="576"/>
       <c r="C27" s="499" t="s">
         <v>288</v>
       </c>
-      <c r="D27" s="569"/>
-      <c r="E27" s="570"/>
+      <c r="D27" s="568"/>
+      <c r="E27" s="569"/>
       <c r="F27" s="507"/>
       <c r="G27" s="508"/>
       <c r="H27" s="508"/>
       <c r="I27" s="507"/>
     </row>
     <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="566" t="s">
+      <c r="A28" s="576" t="s">
         <v>306</v>
       </c>
-      <c r="B28" s="566"/>
+      <c r="B28" s="576"/>
       <c r="C28" s="499" t="s">
         <v>288</v>
       </c>
-      <c r="D28" s="569"/>
-      <c r="E28" s="570"/>
+      <c r="D28" s="568"/>
+      <c r="E28" s="569"/>
       <c r="F28" s="507"/>
       <c r="G28" s="508"/>
       <c r="H28" s="508"/>
       <c r="I28" s="507"/>
     </row>
     <row r="29" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="566" t="s">
+      <c r="A29" s="576" t="s">
         <v>307</v>
       </c>
-      <c r="B29" s="566"/>
+      <c r="B29" s="576"/>
       <c r="C29" s="499" t="s">
         <v>288</v>
       </c>
-      <c r="D29" s="569"/>
-      <c r="E29" s="570"/>
+      <c r="D29" s="568"/>
+      <c r="E29" s="569"/>
       <c r="F29" s="509"/>
       <c r="G29" s="510"/>
       <c r="H29" s="510"/>
       <c r="I29" s="509"/>
     </row>
     <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="566" t="s">
+      <c r="A30" s="576" t="s">
         <v>308</v>
       </c>
-      <c r="B30" s="566"/>
+      <c r="B30" s="576"/>
       <c r="C30" s="499" t="s">
         <v>288</v>
       </c>
-      <c r="D30" s="569"/>
-      <c r="E30" s="570"/>
+      <c r="D30" s="568"/>
+      <c r="E30" s="569"/>
       <c r="F30" s="509"/>
       <c r="G30" s="510"/>
       <c r="H30" s="510"/>
       <c r="I30" s="509"/>
     </row>
     <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="566" t="s">
+      <c r="A31" s="576" t="s">
         <v>309</v>
       </c>
-      <c r="B31" s="566"/>
+      <c r="B31" s="576"/>
       <c r="C31" s="499" t="s">
         <v>288</v>
       </c>
-      <c r="D31" s="569"/>
-      <c r="E31" s="570"/>
+      <c r="D31" s="568"/>
+      <c r="E31" s="569"/>
       <c r="F31" s="509"/>
       <c r="G31" s="510"/>
       <c r="H31" s="510"/>
       <c r="I31" s="509"/>
     </row>
     <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="566" t="s">
+      <c r="A32" s="576" t="s">
         <v>310</v>
       </c>
-      <c r="B32" s="566"/>
+      <c r="B32" s="576"/>
       <c r="C32" s="494" t="s">
         <v>291</v>
       </c>
-      <c r="D32" s="569"/>
-      <c r="E32" s="570"/>
+      <c r="D32" s="568"/>
+      <c r="E32" s="569"/>
       <c r="F32" s="511"/>
       <c r="G32" s="512"/>
       <c r="H32" s="512"/>
       <c r="I32" s="511"/>
     </row>
     <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="572" t="s">
+      <c r="A33" s="584" t="s">
         <v>323</v>
       </c>
-      <c r="B33" s="572"/>
+      <c r="B33" s="584"/>
       <c r="C33" s="500" t="s">
         <v>289</v>
       </c>
-      <c r="D33" s="611"/>
-      <c r="E33" s="612"/>
+      <c r="D33" s="570"/>
+      <c r="E33" s="571"/>
       <c r="F33" s="501"/>
       <c r="G33" s="502"/>
       <c r="H33" s="502"/>
@@ -10543,7 +10517,7 @@
       <c r="B34" s="514"/>
       <c r="C34" s="514"/>
       <c r="D34" s="515" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E34" s="516"/>
       <c r="F34" s="516"/>
@@ -10556,19 +10530,19 @@
         <v>316</v>
       </c>
       <c r="B35" s="520"/>
-      <c r="C35" s="613"/>
-      <c r="D35" s="614"/>
+      <c r="C35" s="572"/>
+      <c r="D35" s="573"/>
       <c r="E35" s="521"/>
-      <c r="F35" s="578" t="s">
+      <c r="F35" s="612" t="s">
         <v>311</v>
       </c>
-      <c r="G35" s="578" t="s">
+      <c r="G35" s="612" t="s">
         <v>312</v>
       </c>
-      <c r="H35" s="578" t="s">
+      <c r="H35" s="612" t="s">
         <v>280</v>
       </c>
-      <c r="I35" s="578" t="s">
+      <c r="I35" s="612" t="s">
         <v>257</v>
       </c>
     </row>
@@ -10577,21 +10551,21 @@
         <v>317</v>
       </c>
       <c r="B36" s="523"/>
-      <c r="C36" s="613"/>
-      <c r="D36" s="614"/>
+      <c r="C36" s="572"/>
+      <c r="D36" s="573"/>
       <c r="E36" s="521"/>
-      <c r="F36" s="579"/>
-      <c r="G36" s="579"/>
-      <c r="H36" s="579"/>
-      <c r="I36" s="579"/>
+      <c r="F36" s="613"/>
+      <c r="G36" s="613"/>
+      <c r="H36" s="613"/>
+      <c r="I36" s="613"/>
     </row>
     <row r="37" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="522" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B37" s="523"/>
-      <c r="C37" s="613"/>
-      <c r="D37" s="614"/>
+      <c r="C37" s="572"/>
+      <c r="D37" s="573"/>
       <c r="E37" s="524"/>
       <c r="F37" s="525" t="s">
         <v>293</v>
@@ -10605,8 +10579,8 @@
         <v>318</v>
       </c>
       <c r="B38" s="530"/>
-      <c r="C38" s="613"/>
-      <c r="D38" s="614"/>
+      <c r="C38" s="572"/>
+      <c r="D38" s="573"/>
       <c r="E38" s="521"/>
       <c r="F38" s="525" t="s">
         <v>294</v>
@@ -10620,11 +10594,11 @@
         <v>319</v>
       </c>
       <c r="B39" s="523"/>
-      <c r="C39" s="613"/>
-      <c r="D39" s="614"/>
+      <c r="C39" s="572"/>
+      <c r="D39" s="573"/>
       <c r="E39" s="521"/>
       <c r="F39" s="525" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G39" s="526"/>
       <c r="H39" s="527"/>
@@ -10639,7 +10613,7 @@
       <c r="D40" s="531"/>
       <c r="E40" s="531"/>
       <c r="F40" s="525" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G40" s="526"/>
       <c r="H40" s="528"/>
@@ -10650,8 +10624,8 @@
         <v>295</v>
       </c>
       <c r="B41" s="533"/>
-      <c r="C41" s="577"/>
-      <c r="D41" s="577"/>
+      <c r="C41" s="565"/>
+      <c r="D41" s="565"/>
       <c r="E41" s="531"/>
       <c r="F41" s="525" t="s">
         <v>297</v>
@@ -10665,68 +10639,60 @@
         <v>314</v>
       </c>
       <c r="B42" s="536"/>
-      <c r="C42" s="577"/>
-      <c r="D42" s="577"/>
+      <c r="C42" s="565"/>
+      <c r="D42" s="565"/>
       <c r="E42" s="537"/>
-      <c r="J42" s="538" t="s">
-        <v>327</v>
-      </c>
+      <c r="J42" s="538"/>
     </row>
     <row r="43" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="539" t="s">
         <v>315</v>
       </c>
       <c r="B43" s="540"/>
-      <c r="C43" s="577"/>
-      <c r="D43" s="577"/>
+      <c r="C43" s="565"/>
+      <c r="D43" s="565"/>
       <c r="E43" s="537"/>
-      <c r="F43" s="603" t="s">
+      <c r="F43" s="574" t="s">
         <v>325</v>
       </c>
-      <c r="G43" s="604"/>
-      <c r="H43" s="573" t="s">
+      <c r="G43" s="575"/>
+      <c r="H43" s="563" t="s">
         <v>281</v>
       </c>
-      <c r="I43" s="574"/>
-      <c r="J43" s="538" t="s">
-        <v>328</v>
-      </c>
+      <c r="I43" s="564"/>
+      <c r="J43" s="538"/>
     </row>
     <row r="44" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="532" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B44" s="536"/>
-      <c r="C44" s="577"/>
-      <c r="D44" s="577"/>
+      <c r="C44" s="565"/>
+      <c r="D44" s="565"/>
       <c r="E44" s="537"/>
       <c r="F44" s="541" t="s">
         <v>296</v>
       </c>
       <c r="G44" s="542"/>
-      <c r="H44" s="573"/>
-      <c r="I44" s="574"/>
-      <c r="J44" s="538" t="s">
-        <v>329</v>
-      </c>
+      <c r="H44" s="563"/>
+      <c r="I44" s="564"/>
+      <c r="J44" s="538"/>
     </row>
     <row r="45" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="575" t="s">
-        <v>334</v>
-      </c>
-      <c r="B45" s="576"/>
-      <c r="C45" s="577"/>
-      <c r="D45" s="577"/>
+      <c r="A45" s="610" t="s">
+        <v>330</v>
+      </c>
+      <c r="B45" s="611"/>
+      <c r="C45" s="565"/>
+      <c r="D45" s="565"/>
       <c r="E45" s="537"/>
       <c r="F45" s="541" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G45" s="542"/>
-      <c r="H45" s="573"/>
-      <c r="I45" s="574"/>
-      <c r="J45" s="538" t="s">
-        <v>326</v>
-      </c>
+      <c r="H45" s="563"/>
+      <c r="I45" s="564"/>
+      <c r="J45" s="538"/>
     </row>
     <row r="46" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="543" t="s">
@@ -10739,8 +10705,8 @@
         <v>320</v>
       </c>
       <c r="G46" s="542"/>
-      <c r="H46" s="573"/>
-      <c r="I46" s="574"/>
+      <c r="H46" s="563"/>
+      <c r="I46" s="564"/>
     </row>
     <row r="47" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="546"/>
@@ -10748,11 +10714,11 @@
       <c r="C47" s="547"/>
       <c r="D47" s="548"/>
       <c r="F47" s="541" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G47" s="542"/>
-      <c r="H47" s="573"/>
-      <c r="I47" s="574"/>
+      <c r="H47" s="563"/>
+      <c r="I47" s="564"/>
     </row>
     <row r="48" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="546"/>
@@ -10763,8 +10729,8 @@
         <v>282</v>
       </c>
       <c r="G48" s="549"/>
-      <c r="H48" s="573"/>
-      <c r="I48" s="574"/>
+      <c r="H48" s="563"/>
+      <c r="I48" s="564"/>
     </row>
     <row r="49" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="550"/>
@@ -10775,8 +10741,8 @@
         <v>283</v>
       </c>
       <c r="G49" s="542"/>
-      <c r="H49" s="577"/>
-      <c r="I49" s="577"/>
+      <c r="H49" s="565"/>
+      <c r="I49" s="565"/>
     </row>
     <row r="50" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E50" s="553"/>
@@ -10802,7 +10768,7 @@
     </row>
     <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="554" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B54" s="44"/>
       <c r="C54" s="44"/>
@@ -10817,17 +10783,17 @@
     </row>
     <row r="55" spans="1:9" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="571" t="s">
+      <c r="A56" s="609" t="s">
         <v>278</v>
       </c>
-      <c r="B56" s="571"/>
-      <c r="C56" s="571"/>
-      <c r="D56" s="571"/>
-      <c r="E56" s="571"/>
-      <c r="F56" s="571"/>
-      <c r="G56" s="571"/>
-      <c r="H56" s="571"/>
-      <c r="I56" s="571"/>
+      <c r="B56" s="609"/>
+      <c r="C56" s="609"/>
+      <c r="D56" s="609"/>
+      <c r="E56" s="609"/>
+      <c r="F56" s="609"/>
+      <c r="G56" s="609"/>
+      <c r="H56" s="609"/>
+      <c r="I56" s="609"/>
     </row>
     <row r="57" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10837,53 +10803,13 @@
     <protectedRange sqref="B9:C10" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="71">
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A29:B29"/>
@@ -10900,14 +10826,54 @@
     <mergeCell ref="H35:H36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
     <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.39370078740157483" top="0.78740157480314965" bottom="0" header="0" footer="0"/>
@@ -11117,19 +11083,19 @@
       <c r="Z6" s="51"/>
     </row>
     <row r="7" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="644" t="s">
+      <c r="A7" s="623" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="644"/>
-      <c r="C7" s="644"/>
-      <c r="D7" s="644"/>
-      <c r="E7" s="644"/>
-      <c r="F7" s="644"/>
-      <c r="G7" s="644"/>
-      <c r="H7" s="644"/>
-      <c r="I7" s="644"/>
-      <c r="J7" s="644"/>
-      <c r="K7" s="644"/>
+      <c r="B7" s="623"/>
+      <c r="C7" s="623"/>
+      <c r="D7" s="623"/>
+      <c r="E7" s="623"/>
+      <c r="F7" s="623"/>
+      <c r="G7" s="623"/>
+      <c r="H7" s="623"/>
+      <c r="I7" s="623"/>
+      <c r="J7" s="623"/>
+      <c r="K7" s="623"/>
       <c r="N7" s="469" t="s">
         <v>73</v>
       </c>
@@ -11154,20 +11120,20 @@
       <c r="Z7" s="51"/>
     </row>
     <row r="8" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="645">
+      <c r="A8" s="624">
         <f>+K12</f>
         <v>1</v>
       </c>
-      <c r="B8" s="645"/>
-      <c r="C8" s="645"/>
-      <c r="D8" s="645"/>
-      <c r="E8" s="645"/>
-      <c r="F8" s="645"/>
-      <c r="G8" s="645"/>
-      <c r="H8" s="645"/>
-      <c r="I8" s="645"/>
-      <c r="J8" s="645"/>
-      <c r="K8" s="645"/>
+      <c r="B8" s="624"/>
+      <c r="C8" s="624"/>
+      <c r="D8" s="624"/>
+      <c r="E8" s="624"/>
+      <c r="F8" s="624"/>
+      <c r="G8" s="624"/>
+      <c r="H8" s="624"/>
+      <c r="I8" s="624"/>
+      <c r="J8" s="624"/>
+      <c r="K8" s="624"/>
       <c r="N8" s="343" t="s">
         <v>74</v>
       </c>
@@ -11222,14 +11188,14 @@
       <c r="B10" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="638" t="s">
+      <c r="C10" s="647" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="638"/>
-      <c r="E10" s="638"/>
-      <c r="F10" s="638"/>
-      <c r="G10" s="638"/>
-      <c r="H10" s="638"/>
+      <c r="D10" s="647"/>
+      <c r="E10" s="647"/>
+      <c r="F10" s="647"/>
+      <c r="G10" s="647"/>
+      <c r="H10" s="647"/>
       <c r="I10" s="36" t="s">
         <v>38</v>
       </c>
@@ -11272,14 +11238,14 @@
       <c r="B11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="638" t="s">
+      <c r="C11" s="647" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="638"/>
-      <c r="E11" s="638"/>
-      <c r="F11" s="638"/>
-      <c r="G11" s="638"/>
-      <c r="H11" s="638"/>
+      <c r="D11" s="647"/>
+      <c r="E11" s="647"/>
+      <c r="F11" s="647"/>
+      <c r="G11" s="647"/>
+      <c r="H11" s="647"/>
       <c r="I11" s="39" t="s">
         <v>21</v>
       </c>
@@ -11321,14 +11287,14 @@
       <c r="B12" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="638" t="s">
+      <c r="C12" s="647" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="638"/>
-      <c r="E12" s="638"/>
-      <c r="F12" s="638"/>
-      <c r="G12" s="638"/>
-      <c r="H12" s="638"/>
+      <c r="D12" s="647"/>
+      <c r="E12" s="647"/>
+      <c r="F12" s="647"/>
+      <c r="G12" s="647"/>
+      <c r="H12" s="647"/>
       <c r="I12" s="39" t="s">
         <v>22</v>
       </c>
@@ -11408,19 +11374,19 @@
       <c r="Z13" s="51"/>
     </row>
     <row r="14" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="594" t="s">
+      <c r="A14" s="599" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="595"/>
-      <c r="C14" s="595"/>
-      <c r="D14" s="595"/>
-      <c r="E14" s="595"/>
-      <c r="F14" s="595"/>
-      <c r="G14" s="595"/>
-      <c r="H14" s="595"/>
-      <c r="I14" s="595"/>
-      <c r="J14" s="595"/>
-      <c r="K14" s="597"/>
+      <c r="B14" s="600"/>
+      <c r="C14" s="600"/>
+      <c r="D14" s="600"/>
+      <c r="E14" s="600"/>
+      <c r="F14" s="600"/>
+      <c r="G14" s="600"/>
+      <c r="H14" s="600"/>
+      <c r="I14" s="600"/>
+      <c r="J14" s="600"/>
+      <c r="K14" s="602"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="343" t="s">
@@ -11443,19 +11409,19 @@
       <c r="Z14" s="51"/>
     </row>
     <row r="15" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="605" t="s">
+      <c r="A15" s="577" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="606"/>
-      <c r="C15" s="606"/>
-      <c r="D15" s="606"/>
-      <c r="E15" s="606"/>
-      <c r="F15" s="606"/>
-      <c r="G15" s="606"/>
-      <c r="H15" s="606"/>
-      <c r="I15" s="606"/>
-      <c r="J15" s="606"/>
-      <c r="K15" s="608"/>
+      <c r="B15" s="578"/>
+      <c r="C15" s="578"/>
+      <c r="D15" s="578"/>
+      <c r="E15" s="578"/>
+      <c r="F15" s="578"/>
+      <c r="G15" s="578"/>
+      <c r="H15" s="578"/>
+      <c r="I15" s="578"/>
+      <c r="J15" s="578"/>
+      <c r="K15" s="580"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="38"/>
@@ -11502,30 +11468,30 @@
       <c r="S16" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="T16" s="618" t="s">
+      <c r="T16" s="651" t="s">
         <v>99</v>
       </c>
-      <c r="U16" s="619"/>
-      <c r="V16" s="620"/>
+      <c r="U16" s="652"/>
+      <c r="V16" s="653"/>
       <c r="W16" s="51"/>
       <c r="X16" s="51"/>
       <c r="Y16" s="51"/>
       <c r="Z16" s="51"/>
     </row>
     <row r="17" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="635" t="s">
+      <c r="A17" s="644" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="636"/>
-      <c r="C17" s="636"/>
-      <c r="D17" s="636"/>
-      <c r="E17" s="636"/>
-      <c r="F17" s="636"/>
-      <c r="G17" s="636"/>
-      <c r="H17" s="636"/>
-      <c r="I17" s="636"/>
-      <c r="J17" s="636"/>
-      <c r="K17" s="637"/>
+      <c r="B17" s="645"/>
+      <c r="C17" s="645"/>
+      <c r="D17" s="645"/>
+      <c r="E17" s="645"/>
+      <c r="F17" s="645"/>
+      <c r="G17" s="645"/>
+      <c r="H17" s="645"/>
+      <c r="I17" s="645"/>
+      <c r="J17" s="645"/>
+      <c r="K17" s="646"/>
       <c r="M17" s="15"/>
       <c r="N17" s="367" t="s">
         <v>46</v>
@@ -11545,11 +11511,11 @@
       <c r="S17" s="368" t="s">
         <v>48</v>
       </c>
-      <c r="T17" s="615" t="s">
+      <c r="T17" s="648" t="s">
         <v>276</v>
       </c>
-      <c r="U17" s="616"/>
-      <c r="V17" s="617"/>
+      <c r="U17" s="649"/>
+      <c r="V17" s="650"/>
       <c r="W17" s="51"/>
       <c r="X17" s="51"/>
       <c r="Y17" s="51"/>
@@ -11809,21 +11775,21 @@
       <c r="Z22" s="51"/>
     </row>
     <row r="23" spans="1:26" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="648" t="s">
+      <c r="A23" s="627" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="649"/>
-      <c r="C23" s="650"/>
-      <c r="D23" s="623" t="s">
+      <c r="B23" s="628"/>
+      <c r="C23" s="629"/>
+      <c r="D23" s="655" t="s">
         <v>57</v>
       </c>
       <c r="E23" s="313"/>
-      <c r="F23" s="651" t="s">
+      <c r="F23" s="631" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="652"/>
-      <c r="H23" s="653"/>
-      <c r="I23" s="628" t="s">
+      <c r="G23" s="632"/>
+      <c r="H23" s="633"/>
+      <c r="I23" s="637" t="s">
         <v>50</v>
       </c>
       <c r="J23" s="307"/>
@@ -11867,16 +11833,16 @@
       <c r="A24" s="314" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="647" t="s">
+      <c r="B24" s="626" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="647"/>
-      <c r="D24" s="624"/>
+      <c r="C24" s="626"/>
+      <c r="D24" s="656"/>
       <c r="E24" s="313"/>
-      <c r="F24" s="654"/>
-      <c r="G24" s="655"/>
-      <c r="H24" s="656"/>
-      <c r="I24" s="657"/>
+      <c r="F24" s="634"/>
+      <c r="G24" s="635"/>
+      <c r="H24" s="636"/>
+      <c r="I24" s="638"/>
       <c r="J24" s="307"/>
       <c r="K24" s="308"/>
       <c r="L24" s="15"/>
@@ -11914,10 +11880,10 @@
       <c r="A25" s="315" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="646">
+      <c r="B25" s="625">
         <v>76.2</v>
       </c>
-      <c r="C25" s="646"/>
+      <c r="C25" s="625"/>
       <c r="D25" s="316">
         <f>+S18</f>
         <v>100</v>
@@ -11968,21 +11934,21 @@
       <c r="A26" s="317" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="622">
+      <c r="B26" s="630">
         <v>50.6</v>
       </c>
-      <c r="C26" s="622"/>
+      <c r="C26" s="630"/>
       <c r="D26" s="318">
         <f>+S20</f>
         <v>96.737365729020368</v>
       </c>
       <c r="E26" s="313"/>
-      <c r="F26" s="648" t="s">
+      <c r="F26" s="627" t="s">
         <v>64</v>
       </c>
-      <c r="G26" s="649"/>
-      <c r="H26" s="649"/>
-      <c r="I26" s="650"/>
+      <c r="G26" s="628"/>
+      <c r="H26" s="628"/>
+      <c r="I26" s="629"/>
       <c r="J26" s="319"/>
       <c r="K26" s="320"/>
       <c r="L26" s="15"/>
@@ -12020,19 +11986,19 @@
       <c r="A27" s="321" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="622">
+      <c r="B27" s="630">
         <v>38.1</v>
       </c>
-      <c r="C27" s="622"/>
+      <c r="C27" s="630"/>
       <c r="D27" s="318">
         <f>+S21</f>
         <v>90.324022891039832</v>
       </c>
       <c r="E27" s="313"/>
-      <c r="F27" s="658"/>
-      <c r="G27" s="659"/>
-      <c r="H27" s="659"/>
-      <c r="I27" s="660"/>
+      <c r="F27" s="639"/>
+      <c r="G27" s="640"/>
+      <c r="H27" s="640"/>
+      <c r="I27" s="641"/>
       <c r="J27" s="319"/>
       <c r="K27" s="320"/>
       <c r="L27" s="15"/>
@@ -12074,19 +12040,19 @@
       <c r="A28" s="317" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="622">
+      <c r="B28" s="630">
         <v>25.4</v>
       </c>
-      <c r="C28" s="622"/>
+      <c r="C28" s="630"/>
       <c r="D28" s="318">
         <f>+S22</f>
         <v>84.873241107276272</v>
       </c>
       <c r="E28" s="313"/>
-      <c r="F28" s="631" t="s">
+      <c r="F28" s="642" t="s">
         <v>58</v>
       </c>
-      <c r="G28" s="633">
+      <c r="G28" s="643">
         <f>R27</f>
         <v>45.788805497693524</v>
       </c>
@@ -12134,17 +12100,17 @@
       <c r="A29" s="317" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="622">
+      <c r="B29" s="630">
         <v>19.05</v>
       </c>
-      <c r="C29" s="622"/>
+      <c r="C29" s="630"/>
       <c r="D29" s="318">
         <f>+S23</f>
         <v>73.456819301447041</v>
       </c>
       <c r="E29" s="313"/>
-      <c r="F29" s="632"/>
-      <c r="G29" s="634"/>
+      <c r="F29" s="618"/>
+      <c r="G29" s="621"/>
       <c r="H29" s="324" t="s">
         <v>60</v>
       </c>
@@ -12193,19 +12159,19 @@
       <c r="A30" s="317" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="622">
+      <c r="B30" s="630">
         <v>9.5250000000000004</v>
       </c>
-      <c r="C30" s="622"/>
+      <c r="C30" s="630"/>
       <c r="D30" s="318">
         <f>+S25</f>
         <v>62.661585152699679</v>
       </c>
       <c r="E30" s="313"/>
-      <c r="F30" s="639" t="s">
+      <c r="F30" s="616" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="641">
+      <c r="G30" s="619">
         <f>100-(G28+G33)</f>
         <v>40.754382185876274</v>
       </c>
@@ -12253,17 +12219,17 @@
       <c r="A31" s="317" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="622">
+      <c r="B31" s="630">
         <v>4.76</v>
       </c>
-      <c r="C31" s="622"/>
+      <c r="C31" s="630"/>
       <c r="D31" s="318">
         <f>+S27</f>
         <v>54.211194502306476</v>
       </c>
       <c r="E31" s="313"/>
-      <c r="F31" s="640"/>
-      <c r="G31" s="642"/>
+      <c r="F31" s="617"/>
+      <c r="G31" s="620"/>
       <c r="H31" s="324" t="s">
         <v>62</v>
       </c>
@@ -12311,17 +12277,17 @@
       <c r="A32" s="317">
         <v>8</v>
       </c>
-      <c r="B32" s="622">
+      <c r="B32" s="630">
         <v>2.36</v>
       </c>
-      <c r="C32" s="622"/>
+      <c r="C32" s="630"/>
       <c r="D32" s="318">
         <f>+S28</f>
         <v>49.032616067382399</v>
       </c>
       <c r="E32" s="313"/>
-      <c r="F32" s="632"/>
-      <c r="G32" s="634"/>
+      <c r="F32" s="618"/>
+      <c r="G32" s="621"/>
       <c r="H32" s="324" t="s">
         <v>60</v>
       </c>
@@ -12373,10 +12339,10 @@
       <c r="A33" s="317">
         <v>16</v>
       </c>
-      <c r="B33" s="622">
+      <c r="B33" s="630">
         <v>1.19</v>
       </c>
-      <c r="C33" s="622"/>
+      <c r="C33" s="630"/>
       <c r="D33" s="318">
         <f t="shared" ref="D33:D38" si="4">+S30</f>
         <v>40.351707913359583</v>
@@ -12431,10 +12397,10 @@
       <c r="A34" s="317">
         <v>30</v>
       </c>
-      <c r="B34" s="622">
+      <c r="B34" s="630">
         <v>0.6</v>
       </c>
-      <c r="C34" s="622"/>
+      <c r="C34" s="630"/>
       <c r="D34" s="318">
         <f t="shared" si="4"/>
         <v>31.408593256302638</v>
@@ -12481,25 +12447,25 @@
       <c r="A35" s="317">
         <v>40</v>
       </c>
-      <c r="B35" s="622">
+      <c r="B35" s="630">
         <v>0.42</v>
       </c>
-      <c r="C35" s="622"/>
+      <c r="C35" s="630"/>
       <c r="D35" s="318">
         <f t="shared" si="4"/>
         <v>27.175831135894526</v>
       </c>
       <c r="E35" s="313"/>
-      <c r="F35" s="625" t="str">
+      <c r="F35" s="657" t="str">
         <f>IF(O3="No","","Clasificacion SUCS")</f>
         <v/>
       </c>
-      <c r="G35" s="625"/>
-      <c r="H35" s="628" t="str">
+      <c r="G35" s="657"/>
+      <c r="H35" s="637" t="str">
         <f>IF(O3="No","",'Sucs '!G4)</f>
         <v/>
       </c>
-      <c r="I35" s="628"/>
+      <c r="I35" s="637"/>
       <c r="J35" s="319"/>
       <c r="K35" s="320"/>
       <c r="L35" s="15"/>
@@ -12541,19 +12507,19 @@
       <c r="A36" s="317">
         <v>50</v>
       </c>
-      <c r="B36" s="622">
+      <c r="B36" s="630">
         <v>0.3</v>
       </c>
-      <c r="C36" s="622"/>
+      <c r="C36" s="630"/>
       <c r="D36" s="318">
         <f t="shared" si="4"/>
         <v>23.785875632381845</v>
       </c>
       <c r="E36" s="313"/>
-      <c r="F36" s="626"/>
-      <c r="G36" s="626"/>
-      <c r="H36" s="629"/>
-      <c r="I36" s="629"/>
+      <c r="F36" s="658"/>
+      <c r="G36" s="658"/>
+      <c r="H36" s="660"/>
+      <c r="I36" s="660"/>
       <c r="J36" s="319"/>
       <c r="K36" s="320"/>
       <c r="L36" s="15"/>
@@ -12592,25 +12558,25 @@
       <c r="A37" s="317">
         <v>100</v>
       </c>
-      <c r="B37" s="622">
+      <c r="B37" s="630">
         <v>0.14899999999999999</v>
       </c>
-      <c r="C37" s="622"/>
+      <c r="C37" s="630"/>
       <c r="D37" s="318">
         <f t="shared" si="4"/>
         <v>17.820677688355374</v>
       </c>
       <c r="E37" s="313"/>
-      <c r="F37" s="626" t="str">
+      <c r="F37" s="658" t="str">
         <f>IF(O3="No","","Clasificacion AASHTO")</f>
         <v/>
       </c>
-      <c r="G37" s="626"/>
-      <c r="H37" s="629" t="str">
+      <c r="G37" s="658"/>
+      <c r="H37" s="660" t="str">
         <f>IF(O3="No","",Aashto!J26)</f>
         <v/>
       </c>
-      <c r="I37" s="629"/>
+      <c r="I37" s="660"/>
       <c r="J37" s="319"/>
       <c r="K37" s="320"/>
       <c r="L37" s="15"/>
@@ -12636,19 +12602,19 @@
       <c r="A38" s="329">
         <v>200</v>
       </c>
-      <c r="B38" s="621">
+      <c r="B38" s="654">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="C38" s="621"/>
+      <c r="C38" s="654"/>
       <c r="D38" s="330">
         <f t="shared" si="4"/>
         <v>13.456812316430202</v>
       </c>
       <c r="E38" s="313"/>
-      <c r="F38" s="627"/>
-      <c r="G38" s="627"/>
-      <c r="H38" s="630"/>
-      <c r="I38" s="630"/>
+      <c r="F38" s="659"/>
+      <c r="G38" s="659"/>
+      <c r="H38" s="661"/>
+      <c r="I38" s="661"/>
       <c r="J38" s="319"/>
       <c r="K38" s="320"/>
       <c r="L38" s="15"/>
@@ -13540,19 +13506,19 @@
       <c r="Z63" s="51"/>
     </row>
     <row r="64" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="643" t="s">
+      <c r="A64" s="622" t="s">
         <v>41</v>
       </c>
-      <c r="B64" s="643"/>
-      <c r="C64" s="643"/>
-      <c r="D64" s="643"/>
-      <c r="E64" s="643"/>
-      <c r="F64" s="643"/>
-      <c r="G64" s="643"/>
-      <c r="H64" s="643"/>
-      <c r="I64" s="643"/>
-      <c r="J64" s="643"/>
-      <c r="K64" s="643"/>
+      <c r="B64" s="622"/>
+      <c r="C64" s="622"/>
+      <c r="D64" s="622"/>
+      <c r="E64" s="622"/>
+      <c r="F64" s="622"/>
+      <c r="G64" s="622"/>
+      <c r="H64" s="622"/>
+      <c r="I64" s="622"/>
+      <c r="J64" s="622"/>
+      <c r="K64" s="622"/>
       <c r="W64" s="51"/>
       <c r="X64" s="51"/>
       <c r="Y64" s="51"/>
@@ -13588,6 +13554,29 @@
     <protectedRange sqref="C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="F35:G36"/>
+    <mergeCell ref="F37:G38"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="F30:F32"/>
     <mergeCell ref="G30:G32"/>
     <mergeCell ref="A64:K64"/>
@@ -13604,29 +13593,6 @@
     <mergeCell ref="F23:H24"/>
     <mergeCell ref="I23:I24"/>
     <mergeCell ref="F26:I27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="F35:G36"/>
-    <mergeCell ref="F37:G38"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="H37:I38"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -13754,35 +13720,35 @@
       <c r="K7" s="203"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="662" t="s">
+      <c r="A8" s="682" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="662"/>
-      <c r="C8" s="662"/>
-      <c r="D8" s="662"/>
-      <c r="E8" s="662"/>
-      <c r="F8" s="662"/>
-      <c r="G8" s="662"/>
-      <c r="H8" s="662"/>
-      <c r="I8" s="662"/>
-      <c r="J8" s="662"/>
-      <c r="K8" s="662"/>
+      <c r="B8" s="682"/>
+      <c r="C8" s="682"/>
+      <c r="D8" s="682"/>
+      <c r="E8" s="682"/>
+      <c r="F8" s="682"/>
+      <c r="G8" s="682"/>
+      <c r="H8" s="682"/>
+      <c r="I8" s="682"/>
+      <c r="J8" s="682"/>
+      <c r="K8" s="682"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="663">
+      <c r="A9" s="683">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="663"/>
-      <c r="C9" s="663"/>
-      <c r="D9" s="663"/>
-      <c r="E9" s="663"/>
-      <c r="F9" s="663"/>
-      <c r="G9" s="663"/>
-      <c r="H9" s="663"/>
-      <c r="I9" s="663"/>
-      <c r="J9" s="663"/>
-      <c r="K9" s="663"/>
+      <c r="B9" s="683"/>
+      <c r="C9" s="683"/>
+      <c r="D9" s="683"/>
+      <c r="E9" s="683"/>
+      <c r="F9" s="683"/>
+      <c r="G9" s="683"/>
+      <c r="H9" s="683"/>
+      <c r="I9" s="683"/>
+      <c r="J9" s="683"/>
+      <c r="K9" s="683"/>
       <c r="O9" s="204"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -13805,14 +13771,14 @@
       <c r="B11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="664" t="s">
+      <c r="C11" s="684" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="664"/>
-      <c r="E11" s="664"/>
-      <c r="F11" s="664"/>
-      <c r="G11" s="664"/>
-      <c r="H11" s="664"/>
+      <c r="D11" s="684"/>
+      <c r="E11" s="684"/>
+      <c r="F11" s="684"/>
+      <c r="G11" s="684"/>
+      <c r="H11" s="684"/>
       <c r="I11" s="206" t="s">
         <v>38</v>
       </c>
@@ -13833,14 +13799,14 @@
       <c r="B12" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="664" t="s">
+      <c r="C12" s="684" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="664"/>
-      <c r="E12" s="664"/>
-      <c r="F12" s="664"/>
-      <c r="G12" s="664"/>
-      <c r="H12" s="664"/>
+      <c r="D12" s="684"/>
+      <c r="E12" s="684"/>
+      <c r="F12" s="684"/>
+      <c r="G12" s="684"/>
+      <c r="H12" s="684"/>
       <c r="I12" s="39" t="s">
         <v>21</v>
       </c>
@@ -13864,14 +13830,14 @@
       <c r="B13" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="664" t="s">
+      <c r="C13" s="684" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="664"/>
-      <c r="E13" s="664"/>
-      <c r="F13" s="664"/>
-      <c r="G13" s="664"/>
-      <c r="H13" s="664"/>
+      <c r="D13" s="684"/>
+      <c r="E13" s="684"/>
+      <c r="F13" s="684"/>
+      <c r="G13" s="684"/>
+      <c r="H13" s="684"/>
       <c r="I13" s="39" t="s">
         <v>22</v>
       </c>
@@ -13885,8 +13851,8 @@
       <c r="M13" s="209"/>
       <c r="P13" s="212"/>
       <c r="Q13" s="212"/>
-      <c r="R13" s="661"/>
-      <c r="S13" s="661"/>
+      <c r="R13" s="681"/>
+      <c r="S13" s="681"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
@@ -13908,19 +13874,19 @@
       <c r="S14" s="217"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="665" t="s">
+      <c r="A15" s="669" t="s">
         <v>229</v>
       </c>
-      <c r="B15" s="666"/>
-      <c r="C15" s="666"/>
-      <c r="D15" s="666"/>
-      <c r="E15" s="666"/>
-      <c r="F15" s="666"/>
-      <c r="G15" s="666"/>
-      <c r="H15" s="666"/>
-      <c r="I15" s="666"/>
-      <c r="J15" s="666"/>
-      <c r="K15" s="667"/>
+      <c r="B15" s="670"/>
+      <c r="C15" s="670"/>
+      <c r="D15" s="670"/>
+      <c r="E15" s="670"/>
+      <c r="F15" s="670"/>
+      <c r="G15" s="670"/>
+      <c r="H15" s="670"/>
+      <c r="I15" s="670"/>
+      <c r="J15" s="670"/>
+      <c r="K15" s="671"/>
       <c r="L15" s="209"/>
       <c r="M15" s="209"/>
       <c r="P15" s="212"/>
@@ -13929,19 +13895,19 @@
       <c r="S15" s="217"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="668" t="s">
+      <c r="A16" s="672" t="s">
         <v>277</v>
       </c>
-      <c r="B16" s="669"/>
-      <c r="C16" s="669"/>
-      <c r="D16" s="669"/>
-      <c r="E16" s="669"/>
-      <c r="F16" s="669"/>
-      <c r="G16" s="669"/>
-      <c r="H16" s="669"/>
-      <c r="I16" s="669"/>
-      <c r="J16" s="669"/>
-      <c r="K16" s="670"/>
+      <c r="B16" s="673"/>
+      <c r="C16" s="673"/>
+      <c r="D16" s="673"/>
+      <c r="E16" s="673"/>
+      <c r="F16" s="673"/>
+      <c r="G16" s="673"/>
+      <c r="H16" s="673"/>
+      <c r="I16" s="673"/>
+      <c r="J16" s="673"/>
+      <c r="K16" s="674"/>
       <c r="L16" s="209"/>
       <c r="M16" s="209"/>
       <c r="P16" s="212"/>
@@ -13969,19 +13935,19 @@
       <c r="S17" s="217"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="671" t="s">
+      <c r="A18" s="675" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="636"/>
-      <c r="C18" s="636"/>
-      <c r="D18" s="636"/>
-      <c r="E18" s="636"/>
-      <c r="F18" s="636"/>
-      <c r="G18" s="636"/>
-      <c r="H18" s="636"/>
-      <c r="I18" s="636"/>
-      <c r="J18" s="636"/>
-      <c r="K18" s="637"/>
+      <c r="B18" s="645"/>
+      <c r="C18" s="645"/>
+      <c r="D18" s="645"/>
+      <c r="E18" s="645"/>
+      <c r="F18" s="645"/>
+      <c r="G18" s="645"/>
+      <c r="H18" s="645"/>
+      <c r="I18" s="645"/>
+      <c r="J18" s="645"/>
+      <c r="K18" s="646"/>
       <c r="M18" s="209"/>
       <c r="P18" s="212"/>
       <c r="Q18" s="212"/>
@@ -14098,8 +14064,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="231"/>
-      <c r="I23" s="672"/>
-      <c r="J23" s="672"/>
+      <c r="I23" s="676"/>
+      <c r="J23" s="676"/>
       <c r="K23" s="232"/>
       <c r="L23" s="209"/>
       <c r="M23" s="233"/>
@@ -14107,41 +14073,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="235"/>
-      <c r="D24" s="673" t="s">
+      <c r="D24" s="677" t="s">
         <v>232</v>
       </c>
-      <c r="E24" s="674"/>
-      <c r="F24" s="674"/>
-      <c r="G24" s="675" t="s">
+      <c r="E24" s="678"/>
+      <c r="F24" s="678"/>
+      <c r="G24" s="679" t="s">
         <v>233</v>
       </c>
-      <c r="H24" s="676"/>
-      <c r="I24" s="677"/>
-      <c r="J24" s="677"/>
+      <c r="H24" s="680"/>
+      <c r="I24" s="667"/>
+      <c r="J24" s="667"/>
       <c r="K24" s="236"/>
       <c r="L24" s="209"/>
       <c r="M24" s="237"/>
-      <c r="O24" s="678" t="s">
+      <c r="O24" s="662" t="s">
         <v>232</v>
       </c>
-      <c r="P24" s="679"/>
+      <c r="P24" s="663"/>
       <c r="Q24" s="238" t="s">
         <v>231</v>
       </c>
-      <c r="R24" s="678" t="s">
+      <c r="R24" s="662" t="s">
         <v>233</v>
       </c>
-      <c r="S24" s="680"/>
+      <c r="S24" s="664"/>
       <c r="T24" s="238" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="235"/>
-      <c r="B25" s="681" t="s">
+      <c r="B25" s="665" t="s">
         <v>234</v>
       </c>
-      <c r="C25" s="682"/>
+      <c r="C25" s="666"/>
       <c r="D25" s="239" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -14162,8 +14128,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="677"/>
-      <c r="J25" s="677"/>
+      <c r="I25" s="667"/>
+      <c r="J25" s="667"/>
       <c r="K25" s="236"/>
       <c r="L25" s="209"/>
       <c r="M25" s="237"/>
@@ -14212,8 +14178,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="683"/>
-      <c r="J26" s="683"/>
+      <c r="I26" s="668"/>
+      <c r="J26" s="668"/>
       <c r="K26" s="249"/>
       <c r="L26" s="250"/>
       <c r="M26" s="237"/>
@@ -14928,19 +14894,19 @@
     </row>
     <row r="49" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="643" t="s">
+      <c r="A50" s="622" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="643"/>
-      <c r="C50" s="643"/>
-      <c r="D50" s="643"/>
-      <c r="E50" s="643"/>
-      <c r="F50" s="643"/>
-      <c r="G50" s="643"/>
-      <c r="H50" s="643"/>
-      <c r="I50" s="643"/>
-      <c r="J50" s="643"/>
-      <c r="K50" s="643"/>
+      <c r="B50" s="622"/>
+      <c r="C50" s="622"/>
+      <c r="D50" s="622"/>
+      <c r="E50" s="622"/>
+      <c r="F50" s="622"/>
+      <c r="G50" s="622"/>
+      <c r="H50" s="622"/>
+      <c r="I50" s="622"/>
+      <c r="J50" s="622"/>
+      <c r="K50" s="622"/>
     </row>
     <row r="51" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14950,11 +14916,12 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -14963,12 +14930,11 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -15082,33 +15048,33 @@
       <c r="J7" s="203"/>
     </row>
     <row r="8" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="662" t="s">
+      <c r="A8" s="682" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="662"/>
-      <c r="C8" s="662"/>
-      <c r="D8" s="662"/>
-      <c r="E8" s="662"/>
-      <c r="F8" s="662"/>
-      <c r="G8" s="662"/>
-      <c r="H8" s="662"/>
-      <c r="I8" s="662"/>
-      <c r="J8" s="662"/>
+      <c r="B8" s="682"/>
+      <c r="C8" s="682"/>
+      <c r="D8" s="682"/>
+      <c r="E8" s="682"/>
+      <c r="F8" s="682"/>
+      <c r="G8" s="682"/>
+      <c r="H8" s="682"/>
+      <c r="I8" s="682"/>
+      <c r="J8" s="682"/>
     </row>
     <row r="9" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="690">
+      <c r="A9" s="685">
         <f>J13</f>
         <v>1</v>
       </c>
-      <c r="B9" s="690"/>
-      <c r="C9" s="690"/>
-      <c r="D9" s="690"/>
-      <c r="E9" s="690"/>
-      <c r="F9" s="690"/>
-      <c r="G9" s="690"/>
-      <c r="H9" s="690"/>
-      <c r="I9" s="690"/>
-      <c r="J9" s="690"/>
+      <c r="B9" s="685"/>
+      <c r="C9" s="685"/>
+      <c r="D9" s="685"/>
+      <c r="E9" s="685"/>
+      <c r="F9" s="685"/>
+      <c r="G9" s="685"/>
+      <c r="H9" s="685"/>
+      <c r="I9" s="685"/>
+      <c r="J9" s="685"/>
       <c r="O9" s="204"/>
     </row>
     <row r="10" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -15130,13 +15096,13 @@
       <c r="B11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="664" t="s">
+      <c r="C11" s="684" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="664"/>
-      <c r="E11" s="664"/>
-      <c r="F11" s="664"/>
-      <c r="G11" s="664"/>
+      <c r="D11" s="684"/>
+      <c r="E11" s="684"/>
+      <c r="F11" s="684"/>
+      <c r="G11" s="684"/>
       <c r="H11" s="206" t="s">
         <v>38</v>
       </c>
@@ -15158,13 +15124,13 @@
       <c r="B12" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="664" t="s">
+      <c r="C12" s="684" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="664"/>
-      <c r="E12" s="664"/>
-      <c r="F12" s="664"/>
-      <c r="G12" s="664"/>
+      <c r="D12" s="684"/>
+      <c r="E12" s="684"/>
+      <c r="F12" s="684"/>
+      <c r="G12" s="684"/>
       <c r="H12" s="39" t="s">
         <v>21</v>
       </c>
@@ -15188,13 +15154,13 @@
       <c r="B13" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="664" t="s">
+      <c r="C13" s="684" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="664"/>
-      <c r="E13" s="664"/>
-      <c r="F13" s="664"/>
-      <c r="G13" s="664"/>
+      <c r="D13" s="684"/>
+      <c r="E13" s="684"/>
+      <c r="F13" s="684"/>
+      <c r="G13" s="684"/>
       <c r="H13" s="39" t="s">
         <v>22</v>
       </c>
@@ -15207,8 +15173,8 @@
       <c r="K13" s="209"/>
       <c r="L13" s="209"/>
       <c r="M13" s="209"/>
-      <c r="P13" s="661"/>
-      <c r="Q13" s="661"/>
+      <c r="P13" s="681"/>
+      <c r="Q13" s="681"/>
     </row>
     <row r="14" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
@@ -15228,34 +15194,34 @@
       <c r="Q14" s="217"/>
     </row>
     <row r="15" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="665" t="s">
+      <c r="A15" s="669" t="s">
         <v>259</v>
       </c>
-      <c r="B15" s="666"/>
-      <c r="C15" s="666"/>
-      <c r="D15" s="666"/>
-      <c r="E15" s="666"/>
-      <c r="F15" s="666"/>
-      <c r="G15" s="666"/>
-      <c r="H15" s="666"/>
-      <c r="I15" s="666"/>
-      <c r="J15" s="667"/>
+      <c r="B15" s="670"/>
+      <c r="C15" s="670"/>
+      <c r="D15" s="670"/>
+      <c r="E15" s="670"/>
+      <c r="F15" s="670"/>
+      <c r="G15" s="670"/>
+      <c r="H15" s="670"/>
+      <c r="I15" s="670"/>
+      <c r="J15" s="671"/>
       <c r="K15" s="209"/>
       <c r="L15" s="209"/>
     </row>
     <row r="16" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="668" t="s">
+      <c r="A16" s="672" t="s">
         <v>260</v>
       </c>
-      <c r="B16" s="684"/>
-      <c r="C16" s="684"/>
-      <c r="D16" s="684"/>
-      <c r="E16" s="684"/>
-      <c r="F16" s="684"/>
-      <c r="G16" s="684"/>
-      <c r="H16" s="684"/>
-      <c r="I16" s="684"/>
-      <c r="J16" s="685"/>
+      <c r="B16" s="686"/>
+      <c r="C16" s="686"/>
+      <c r="D16" s="686"/>
+      <c r="E16" s="686"/>
+      <c r="F16" s="686"/>
+      <c r="G16" s="686"/>
+      <c r="H16" s="686"/>
+      <c r="I16" s="686"/>
+      <c r="J16" s="687"/>
       <c r="K16" s="209"/>
       <c r="L16" s="209"/>
     </row>
@@ -15274,18 +15240,18 @@
       <c r="L17" s="209"/>
     </row>
     <row r="18" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="636" t="s">
+      <c r="A18" s="645" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="636"/>
-      <c r="C18" s="636"/>
-      <c r="D18" s="636"/>
-      <c r="E18" s="636"/>
-      <c r="F18" s="636"/>
-      <c r="G18" s="636"/>
-      <c r="H18" s="636"/>
-      <c r="I18" s="636"/>
-      <c r="J18" s="636"/>
+      <c r="B18" s="645"/>
+      <c r="C18" s="645"/>
+      <c r="D18" s="645"/>
+      <c r="E18" s="645"/>
+      <c r="F18" s="645"/>
+      <c r="G18" s="645"/>
+      <c r="H18" s="645"/>
+      <c r="I18" s="645"/>
+      <c r="J18" s="645"/>
       <c r="L18" s="209"/>
     </row>
     <row r="19" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -15400,12 +15366,12 @@
     <row r="24" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="402"/>
       <c r="B24" s="400"/>
-      <c r="C24" s="686" t="s">
+      <c r="C24" s="688" t="s">
         <v>261</v>
       </c>
-      <c r="D24" s="687"/>
-      <c r="E24" s="687"/>
-      <c r="F24" s="688"/>
+      <c r="D24" s="689"/>
+      <c r="E24" s="689"/>
+      <c r="F24" s="690"/>
       <c r="G24" s="400"/>
       <c r="H24" s="400"/>
       <c r="I24" s="400"/>
@@ -15522,10 +15488,10 @@
     <row r="28" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="402"/>
       <c r="B28" s="282"/>
-      <c r="C28" s="689"/>
-      <c r="D28" s="689"/>
-      <c r="E28" s="689"/>
-      <c r="F28" s="689"/>
+      <c r="C28" s="691"/>
+      <c r="D28" s="691"/>
+      <c r="E28" s="691"/>
+      <c r="F28" s="691"/>
       <c r="G28" s="396"/>
       <c r="H28" s="411"/>
       <c r="I28" s="411"/>
@@ -15549,12 +15515,12 @@
     <row r="29" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="402"/>
       <c r="B29" s="282"/>
-      <c r="C29" s="686" t="s">
+      <c r="C29" s="688" t="s">
         <v>267</v>
       </c>
-      <c r="D29" s="687"/>
-      <c r="E29" s="687"/>
-      <c r="F29" s="688"/>
+      <c r="D29" s="689"/>
+      <c r="E29" s="689"/>
+      <c r="F29" s="690"/>
       <c r="G29" s="426" t="s">
         <v>268</v>
       </c>
@@ -15983,18 +15949,18 @@
     </row>
     <row r="53" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="643" t="s">
+      <c r="A54" s="622" t="s">
         <v>41</v>
       </c>
-      <c r="B54" s="643"/>
-      <c r="C54" s="643"/>
-      <c r="D54" s="643"/>
-      <c r="E54" s="643"/>
-      <c r="F54" s="643"/>
-      <c r="G54" s="643"/>
-      <c r="H54" s="643"/>
-      <c r="I54" s="643"/>
-      <c r="J54" s="643"/>
+      <c r="B54" s="622"/>
+      <c r="C54" s="622"/>
+      <c r="D54" s="622"/>
+      <c r="E54" s="622"/>
+      <c r="F54" s="622"/>
+      <c r="G54" s="622"/>
+      <c r="H54" s="622"/>
+      <c r="I54" s="622"/>
+      <c r="J54" s="622"/>
     </row>
     <row r="55" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -16004,12 +15970,6 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="13">
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A16:J16"/>
@@ -16017,6 +15977,12 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -16048,15 +16014,15 @@
       <c r="A1" s="145" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="691" t="s">
+      <c r="B1" s="709" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="691"/>
-      <c r="D1" s="691"/>
-      <c r="E1" s="691"/>
-      <c r="F1" s="691"/>
-      <c r="G1" s="691"/>
-      <c r="H1" s="691"/>
+      <c r="C1" s="709"/>
+      <c r="D1" s="709"/>
+      <c r="E1" s="709"/>
+      <c r="F1" s="709"/>
+      <c r="G1" s="709"/>
+      <c r="H1" s="709"/>
       <c r="I1" s="145"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -16194,29 +16160,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="145"/>
-      <c r="B8" s="692" t="s">
+      <c r="B8" s="710" t="s">
         <v>168</v>
       </c>
-      <c r="C8" s="692"/>
-      <c r="D8" s="692"/>
+      <c r="C8" s="710"/>
+      <c r="D8" s="710"/>
       <c r="E8" s="154" t="s">
         <v>169</v>
       </c>
       <c r="F8" s="155" t="s">
         <v>170</v>
       </c>
-      <c r="G8" s="693" t="s">
+      <c r="G8" s="711" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="693"/>
+      <c r="H8" s="711"/>
       <c r="I8" s="145"/>
       <c r="L8" s="156" t="s">
         <v>172</v>
       </c>
-      <c r="M8" s="694" t="s">
+      <c r="M8" s="712" t="s">
         <v>173</v>
       </c>
-      <c r="N8" s="694"/>
+      <c r="N8" s="712"/>
       <c r="O8" s="157" t="s">
         <v>174</v>
       </c>
@@ -16229,13 +16195,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="145"/>
-      <c r="B9" s="695" t="s">
+      <c r="B9" s="713" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="697" t="s">
+      <c r="C9" s="715" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="699" t="s">
+      <c r="D9" s="717" t="s">
         <v>179</v>
       </c>
       <c r="E9" s="159" t="s">
@@ -16244,10 +16210,10 @@
       <c r="F9" s="160" t="s">
         <v>181</v>
       </c>
-      <c r="G9" s="700" t="s">
+      <c r="G9" s="718" t="s">
         <v>182</v>
       </c>
-      <c r="H9" s="701"/>
+      <c r="H9" s="719"/>
       <c r="I9" s="145"/>
       <c r="L9" s="140" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -16276,19 +16242,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="145"/>
-      <c r="B10" s="695"/>
-      <c r="C10" s="697"/>
-      <c r="D10" s="699"/>
+      <c r="B10" s="713"/>
+      <c r="C10" s="715"/>
+      <c r="D10" s="717"/>
       <c r="E10" s="161" t="s">
         <v>183</v>
       </c>
       <c r="F10" s="162" t="s">
         <v>184</v>
       </c>
-      <c r="G10" s="702" t="s">
+      <c r="G10" s="720" t="s">
         <v>185</v>
       </c>
-      <c r="H10" s="703"/>
+      <c r="H10" s="721"/>
       <c r="I10" s="145"/>
       <c r="L10" s="140" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -16313,9 +16279,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="145"/>
-      <c r="B11" s="695"/>
-      <c r="C11" s="697"/>
-      <c r="D11" s="699" t="s">
+      <c r="B11" s="713"/>
+      <c r="C11" s="715"/>
+      <c r="D11" s="717" t="s">
         <v>186</v>
       </c>
       <c r="E11" s="161" t="s">
@@ -16327,7 +16293,7 @@
       <c r="G11" s="164" t="s">
         <v>189</v>
       </c>
-      <c r="H11" s="704" t="s">
+      <c r="H11" s="722" t="s">
         <v>190</v>
       </c>
       <c r="I11" s="145"/>
@@ -16346,9 +16312,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="145"/>
-      <c r="B12" s="695"/>
-      <c r="C12" s="698"/>
-      <c r="D12" s="699"/>
+      <c r="B12" s="713"/>
+      <c r="C12" s="716"/>
+      <c r="D12" s="717"/>
       <c r="E12" s="165" t="s">
         <v>191</v>
       </c>
@@ -16358,7 +16324,7 @@
       <c r="G12" s="164" t="s">
         <v>193</v>
       </c>
-      <c r="H12" s="705"/>
+      <c r="H12" s="723"/>
       <c r="I12" s="145"/>
       <c r="L12" s="140" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -16371,11 +16337,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="145"/>
-      <c r="B13" s="695"/>
-      <c r="C13" s="697" t="s">
+      <c r="B13" s="713"/>
+      <c r="C13" s="715" t="s">
         <v>194</v>
       </c>
-      <c r="D13" s="699" t="s">
+      <c r="D13" s="717" t="s">
         <v>195</v>
       </c>
       <c r="E13" s="166" t="s">
@@ -16384,10 +16350,10 @@
       <c r="F13" s="167" t="s">
         <v>197</v>
       </c>
-      <c r="G13" s="706" t="s">
+      <c r="G13" s="724" t="s">
         <v>198</v>
       </c>
-      <c r="H13" s="707"/>
+      <c r="H13" s="725"/>
       <c r="I13" s="145"/>
       <c r="L13" s="140" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -16412,19 +16378,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="145"/>
-      <c r="B14" s="695"/>
-      <c r="C14" s="697"/>
-      <c r="D14" s="699"/>
+      <c r="B14" s="713"/>
+      <c r="C14" s="715"/>
+      <c r="D14" s="717"/>
       <c r="E14" s="166" t="s">
         <v>199</v>
       </c>
       <c r="F14" s="167" t="s">
         <v>200</v>
       </c>
-      <c r="G14" s="706" t="s">
+      <c r="G14" s="724" t="s">
         <v>201</v>
       </c>
-      <c r="H14" s="707"/>
+      <c r="H14" s="725"/>
       <c r="I14" s="145"/>
       <c r="L14" s="140" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -16449,9 +16415,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="145"/>
-      <c r="B15" s="695"/>
-      <c r="C15" s="697"/>
-      <c r="D15" s="699" t="s">
+      <c r="B15" s="713"/>
+      <c r="C15" s="715"/>
+      <c r="D15" s="717" t="s">
         <v>202</v>
       </c>
       <c r="E15" s="166" t="s">
@@ -16463,7 +16429,7 @@
       <c r="G15" s="169" t="s">
         <v>205</v>
       </c>
-      <c r="H15" s="708" t="s">
+      <c r="H15" s="692" t="s">
         <v>206</v>
       </c>
       <c r="I15" s="145"/>
@@ -16482,9 +16448,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="145"/>
-      <c r="B16" s="696"/>
-      <c r="C16" s="697"/>
-      <c r="D16" s="699"/>
+      <c r="B16" s="714"/>
+      <c r="C16" s="715"/>
+      <c r="D16" s="717"/>
       <c r="E16" s="170" t="s">
         <v>207</v>
       </c>
@@ -16494,7 +16460,7 @@
       <c r="G16" s="167" t="s">
         <v>209</v>
       </c>
-      <c r="H16" s="709"/>
+      <c r="H16" s="693"/>
       <c r="I16" s="145"/>
       <c r="L16" s="140" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -16507,23 +16473,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="145"/>
-      <c r="B17" s="710" t="s">
+      <c r="B17" s="694" t="s">
         <v>210</v>
       </c>
-      <c r="C17" s="713" t="s">
+      <c r="C17" s="697" t="s">
         <v>211</v>
       </c>
-      <c r="D17" s="714"/>
+      <c r="D17" s="698"/>
       <c r="E17" s="171" t="s">
         <v>212</v>
       </c>
       <c r="F17" s="172" t="s">
         <v>213</v>
       </c>
-      <c r="G17" s="719" t="s">
+      <c r="G17" s="703" t="s">
         <v>214</v>
       </c>
-      <c r="H17" s="720"/>
+      <c r="H17" s="704"/>
       <c r="I17" s="145"/>
       <c r="L17" s="140" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -16536,17 +16502,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="145"/>
-      <c r="B18" s="711"/>
-      <c r="C18" s="715"/>
-      <c r="D18" s="716"/>
+      <c r="B18" s="695"/>
+      <c r="C18" s="699"/>
+      <c r="D18" s="700"/>
       <c r="E18" s="171" t="s">
         <v>215</v>
       </c>
       <c r="F18" s="172" t="s">
         <v>216</v>
       </c>
-      <c r="G18" s="721"/>
-      <c r="H18" s="722"/>
+      <c r="G18" s="705"/>
+      <c r="H18" s="706"/>
       <c r="I18" s="145"/>
       <c r="L18" s="140" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -16559,9 +16525,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="145"/>
-      <c r="B19" s="711"/>
-      <c r="C19" s="717"/>
-      <c r="D19" s="718"/>
+      <c r="B19" s="695"/>
+      <c r="C19" s="701"/>
+      <c r="D19" s="702"/>
       <c r="E19" s="171" t="s">
         <v>217</v>
       </c>
@@ -16582,11 +16548,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="145"/>
-      <c r="B20" s="711"/>
-      <c r="C20" s="715" t="s">
+      <c r="B20" s="695"/>
+      <c r="C20" s="699" t="s">
         <v>219</v>
       </c>
-      <c r="D20" s="723"/>
+      <c r="D20" s="707"/>
       <c r="E20" s="175" t="s">
         <v>220</v>
       </c>
@@ -16607,9 +16573,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="145"/>
-      <c r="B21" s="711"/>
-      <c r="C21" s="715"/>
-      <c r="D21" s="723"/>
+      <c r="B21" s="695"/>
+      <c r="C21" s="699"/>
+      <c r="D21" s="707"/>
       <c r="E21" s="175" t="s">
         <v>222</v>
       </c>
@@ -16630,9 +16596,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="145"/>
-      <c r="B22" s="711"/>
-      <c r="C22" s="717"/>
-      <c r="D22" s="724"/>
+      <c r="B22" s="695"/>
+      <c r="C22" s="701"/>
+      <c r="D22" s="708"/>
       <c r="E22" s="177" t="s">
         <v>224</v>
       </c>
@@ -16653,11 +16619,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="145"/>
-      <c r="B23" s="711"/>
-      <c r="C23" s="713" t="s">
+      <c r="B23" s="695"/>
+      <c r="C23" s="697" t="s">
         <v>226</v>
       </c>
-      <c r="D23" s="714"/>
+      <c r="D23" s="698"/>
       <c r="E23" s="178" t="s">
         <v>227</v>
       </c>
@@ -16678,7 +16644,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="145"/>
-      <c r="B24" s="712"/>
+      <c r="B24" s="696"/>
       <c r="C24" s="180"/>
       <c r="D24" s="181"/>
       <c r="E24" s="182"/>
@@ -16785,12 +16751,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -16807,6 +16767,12 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16882,71 +16848,71 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="72"/>
-      <c r="B4" s="731" t="s">
+      <c r="B4" s="732" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="732"/>
-      <c r="D4" s="733" t="s">
+      <c r="C4" s="733"/>
+      <c r="D4" s="734" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="733"/>
-      <c r="F4" s="733"/>
-      <c r="G4" s="733"/>
-      <c r="H4" s="733"/>
-      <c r="I4" s="733"/>
-      <c r="J4" s="733"/>
-      <c r="K4" s="734" t="s">
+      <c r="E4" s="734"/>
+      <c r="F4" s="734"/>
+      <c r="G4" s="734"/>
+      <c r="H4" s="734"/>
+      <c r="I4" s="734"/>
+      <c r="J4" s="734"/>
+      <c r="K4" s="735" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="735"/>
-      <c r="M4" s="735"/>
-      <c r="N4" s="735"/>
-      <c r="O4" s="736"/>
+      <c r="L4" s="736"/>
+      <c r="M4" s="736"/>
+      <c r="N4" s="736"/>
+      <c r="O4" s="737"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="72"/>
-      <c r="B5" s="737" t="s">
+      <c r="B5" s="738" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="738"/>
-      <c r="D5" s="741" t="s">
+      <c r="C5" s="739"/>
+      <c r="D5" s="742" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="742"/>
-      <c r="F5" s="743" t="s">
+      <c r="E5" s="743"/>
+      <c r="F5" s="744" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="741" t="s">
+      <c r="G5" s="742" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="745"/>
-      <c r="I5" s="745"/>
-      <c r="J5" s="742"/>
-      <c r="K5" s="746" t="s">
+      <c r="H5" s="746"/>
+      <c r="I5" s="746"/>
+      <c r="J5" s="743"/>
+      <c r="K5" s="747" t="s">
         <v>107</v>
       </c>
-      <c r="L5" s="748" t="s">
+      <c r="L5" s="749" t="s">
         <v>108</v>
       </c>
-      <c r="M5" s="750" t="s">
+      <c r="M5" s="751" t="s">
         <v>109</v>
       </c>
-      <c r="N5" s="752" t="s">
+      <c r="N5" s="753" t="s">
         <v>110</v>
       </c>
-      <c r="O5" s="753"/>
+      <c r="O5" s="754"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="72"/>
-      <c r="B6" s="739"/>
-      <c r="C6" s="740"/>
+      <c r="B6" s="740"/>
+      <c r="C6" s="741"/>
       <c r="D6" s="76" t="s">
         <v>111</v>
       </c>
       <c r="E6" s="77" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="744"/>
+      <c r="F6" s="745"/>
       <c r="G6" s="76" t="s">
         <v>113</v>
       </c>
@@ -16959,9 +16925,9 @@
       <c r="J6" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="K6" s="747"/>
-      <c r="L6" s="749"/>
-      <c r="M6" s="751"/>
+      <c r="K6" s="748"/>
+      <c r="L6" s="750"/>
+      <c r="M6" s="752"/>
       <c r="N6" s="80" t="s">
         <v>117</v>
       </c>
@@ -17361,21 +17327,21 @@
         <f>+D38</f>
         <v>0</v>
       </c>
-      <c r="D23" s="725">
+      <c r="D23" s="726">
         <v>0</v>
       </c>
-      <c r="E23" s="726"/>
+      <c r="E23" s="727"/>
       <c r="F23" s="133">
         <v>0</v>
       </c>
-      <c r="G23" s="725">
+      <c r="G23" s="726">
         <v>0</v>
       </c>
-      <c r="H23" s="727"/>
-      <c r="I23" s="728" t="s">
+      <c r="H23" s="728"/>
+      <c r="I23" s="729" t="s">
         <v>145</v>
       </c>
-      <c r="J23" s="726"/>
+      <c r="J23" s="727"/>
       <c r="K23" s="134" t="s">
         <v>146</v>
       </c>
@@ -17438,11 +17404,11 @@
       <c r="G26" s="139"/>
       <c r="H26" s="74"/>
       <c r="I26" s="74"/>
-      <c r="J26" s="729" t="str">
+      <c r="J26" s="730" t="str">
         <f>+D31&amp;" "&amp;F38</f>
         <v>A-1-a (0)</v>
       </c>
-      <c r="K26" s="730"/>
+      <c r="K26" s="731"/>
       <c r="L26" s="72"/>
       <c r="M26" s="72"/>
       <c r="N26" s="72"/>
@@ -17702,10 +17668,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="754" t="s">
+      <c r="A2" s="755" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="754"/>
+      <c r="B2" s="755"/>
       <c r="C2" s="6" t="s">
         <v>11</v>
       </c>

--- a/app/templates/Template_Proctor.xlsx
+++ b/app/templates/Template_Proctor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6813F0B8-EF77-4E7E-A5CC-C8E790B28C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC72944F-4990-4255-BDCB-6355B69D2865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="613" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="formato" sheetId="102" r:id="rId1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="667">
   <si>
     <t>LABORATORIO DE ENSAYO DE MATERIALES</t>
   </si>
@@ -2552,6 +2552,9 @@
   </si>
   <si>
     <t>Factor de precision HUMEDAD SUELO</t>
+  </si>
+  <si>
+    <t>7-may.-26</t>
   </si>
 </sst>
 </file>
@@ -9642,6 +9645,141 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9694,208 +9832,80 @@
     <xf numFmtId="0" fontId="122" fillId="3" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="168" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="62" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="63" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="169" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="170" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="62" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="12" fillId="3" borderId="165" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="165" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="167" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9939,73 +9949,72 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="123" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="124" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="64" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="65" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="12" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="199" fontId="116" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="206" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="207" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10014,32 +10023,14 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -10047,48 +10038,108 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="113" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="109" fillId="0" borderId="128" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="206" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="207" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="208" fontId="118" fillId="19" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="123" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="164" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="124" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="128" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="130" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="112" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="155" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10110,54 +10161,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="3" borderId="58" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="18" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="81" fillId="0" borderId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="165" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="4" fillId="3" borderId="167" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="104" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10168,146 +10171,78 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="193" fontId="81" fillId="0" borderId="155" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="189" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="189" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10336,6 +10271,10 @@
     <xf numFmtId="0" fontId="58" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -10354,6 +10293,9 @@
     <xf numFmtId="164" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10365,6 +10307,127 @@
     </xf>
     <xf numFmtId="0" fontId="58" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="51" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="58" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -10380,65 +10443,9 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="113" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="51" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="58" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="71" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="57" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="46" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="58" fillId="3" borderId="52" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10456,9 +10463,56 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="122" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="131" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="124" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="128" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="125" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="126" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="127" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10510,57 +10564,6 @@
     </xf>
     <xf numFmtId="0" fontId="49" fillId="11" borderId="120" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="11" borderId="47" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="122" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="118" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="131" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="124" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="128" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="123" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="125" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="126" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="127" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="9" borderId="149" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -17495,90 +17498,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1277"/>
-      <c r="B1" s="1278"/>
-      <c r="C1" s="1278"/>
-      <c r="D1" s="1278"/>
-      <c r="E1" s="1278"/>
-      <c r="F1" s="1278"/>
-      <c r="G1" s="1278"/>
-      <c r="H1" s="1278"/>
-      <c r="I1" s="1279"/>
+      <c r="A1" s="1316"/>
+      <c r="B1" s="1317"/>
+      <c r="C1" s="1317"/>
+      <c r="D1" s="1317"/>
+      <c r="E1" s="1317"/>
+      <c r="F1" s="1317"/>
+      <c r="G1" s="1317"/>
+      <c r="H1" s="1317"/>
+      <c r="I1" s="1318"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1280"/>
-      <c r="B2" s="1281"/>
-      <c r="C2" s="1281"/>
-      <c r="D2" s="1281"/>
-      <c r="E2" s="1281"/>
-      <c r="F2" s="1281"/>
-      <c r="G2" s="1281"/>
-      <c r="H2" s="1281"/>
-      <c r="I2" s="1282"/>
+      <c r="A2" s="1319"/>
+      <c r="B2" s="1320"/>
+      <c r="C2" s="1320"/>
+      <c r="D2" s="1320"/>
+      <c r="E2" s="1320"/>
+      <c r="F2" s="1320"/>
+      <c r="G2" s="1320"/>
+      <c r="H2" s="1320"/>
+      <c r="I2" s="1321"/>
       <c r="K2" s="329" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="1260"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1280"/>
-      <c r="B3" s="1281"/>
-      <c r="C3" s="1281"/>
-      <c r="D3" s="1281"/>
-      <c r="E3" s="1281"/>
-      <c r="F3" s="1281"/>
-      <c r="G3" s="1281"/>
-      <c r="H3" s="1281"/>
-      <c r="I3" s="1282"/>
+      <c r="A3" s="1319"/>
+      <c r="B3" s="1320"/>
+      <c r="C3" s="1320"/>
+      <c r="D3" s="1320"/>
+      <c r="E3" s="1320"/>
+      <c r="F3" s="1320"/>
+      <c r="G3" s="1320"/>
+      <c r="H3" s="1320"/>
+      <c r="I3" s="1321"/>
       <c r="K3" s="329" t="s">
         <v>5</v>
       </c>
       <c r="L3" s="1261"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1283"/>
-      <c r="B4" s="1284"/>
-      <c r="C4" s="1284"/>
-      <c r="D4" s="1284"/>
-      <c r="E4" s="1284"/>
-      <c r="F4" s="1284"/>
-      <c r="G4" s="1284"/>
-      <c r="H4" s="1284"/>
-      <c r="I4" s="1285"/>
+      <c r="A4" s="1322"/>
+      <c r="B4" s="1323"/>
+      <c r="C4" s="1323"/>
+      <c r="D4" s="1323"/>
+      <c r="E4" s="1323"/>
+      <c r="F4" s="1323"/>
+      <c r="G4" s="1323"/>
+      <c r="H4" s="1323"/>
+      <c r="I4" s="1324"/>
       <c r="K4" s="329" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="1261"/>
     </row>
     <row r="5" spans="1:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1286" t="s">
+      <c r="A5" s="1325" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1286"/>
-      <c r="C5" s="1286"/>
-      <c r="D5" s="1286"/>
-      <c r="E5" s="1286"/>
-      <c r="F5" s="1286"/>
-      <c r="G5" s="1286"/>
-      <c r="H5" s="1286"/>
-      <c r="I5" s="1286"/>
+      <c r="B5" s="1325"/>
+      <c r="C5" s="1325"/>
+      <c r="D5" s="1325"/>
+      <c r="E5" s="1325"/>
+      <c r="F5" s="1325"/>
+      <c r="G5" s="1325"/>
+      <c r="H5" s="1325"/>
+      <c r="I5" s="1325"/>
       <c r="K5" s="329" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="1261"/>
     </row>
     <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1287" t="s">
+      <c r="A6" s="1326" t="s">
         <v>594</v>
       </c>
-      <c r="B6" s="1287"/>
-      <c r="C6" s="1287"/>
-      <c r="D6" s="1287"/>
-      <c r="E6" s="1287"/>
-      <c r="F6" s="1287"/>
-      <c r="G6" s="1287"/>
-      <c r="H6" s="1287"/>
-      <c r="I6" s="1287"/>
+      <c r="B6" s="1326"/>
+      <c r="C6" s="1326"/>
+      <c r="D6" s="1326"/>
+      <c r="E6" s="1326"/>
+      <c r="F6" s="1326"/>
+      <c r="G6" s="1326"/>
+      <c r="H6" s="1326"/>
+      <c r="I6" s="1326"/>
       <c r="K6" s="1262"/>
       <c r="L6" s="1263"/>
     </row>
@@ -17602,15 +17605,15 @@
       <c r="B8" s="1171" t="s">
         <v>595</v>
       </c>
-      <c r="C8" s="1288" t="s">
+      <c r="C8" s="1327" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1289"/>
+      <c r="D8" s="1328"/>
       <c r="E8" s="1173"/>
-      <c r="F8" s="1290" t="s">
+      <c r="F8" s="1329" t="s">
         <v>596</v>
       </c>
-      <c r="G8" s="1289"/>
+      <c r="G8" s="1328"/>
       <c r="H8" s="1172" t="s">
         <v>597</v>
       </c>
@@ -17622,11 +17625,11 @@
     </row>
     <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1174"/>
-      <c r="C9" s="1274"/>
-      <c r="D9" s="1275"/>
+      <c r="C9" s="1313"/>
+      <c r="D9" s="1314"/>
       <c r="E9" s="1175"/>
-      <c r="F9" s="1276"/>
-      <c r="G9" s="1275"/>
+      <c r="F9" s="1315"/>
+      <c r="G9" s="1314"/>
       <c r="H9" s="1176"/>
       <c r="I9" s="243"/>
       <c r="K9" s="329" t="s">
@@ -17636,46 +17639,46 @@
     </row>
     <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1177"/>
-      <c r="B10" s="1291"/>
-      <c r="C10" s="1291"/>
-      <c r="D10" s="1291"/>
+      <c r="B10" s="1304"/>
+      <c r="C10" s="1304"/>
+      <c r="D10" s="1304"/>
       <c r="E10" s="1178"/>
-      <c r="F10" s="1291"/>
-      <c r="G10" s="1291"/>
+      <c r="F10" s="1304"/>
+      <c r="G10" s="1304"/>
       <c r="H10" s="1178"/>
       <c r="I10" s="1179"/>
       <c r="K10" s="1262"/>
       <c r="L10" s="1263"/>
     </row>
     <row r="11" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1292" t="s">
+      <c r="A11" s="1305" t="s">
         <v>598</v>
       </c>
-      <c r="B11" s="1293"/>
-      <c r="C11" s="1293"/>
-      <c r="D11" s="1293"/>
-      <c r="E11" s="1293"/>
-      <c r="F11" s="1293"/>
-      <c r="G11" s="1293"/>
-      <c r="H11" s="1293"/>
-      <c r="I11" s="1294"/>
+      <c r="B11" s="1306"/>
+      <c r="C11" s="1306"/>
+      <c r="D11" s="1306"/>
+      <c r="E11" s="1306"/>
+      <c r="F11" s="1306"/>
+      <c r="G11" s="1306"/>
+      <c r="H11" s="1306"/>
+      <c r="I11" s="1307"/>
       <c r="K11" s="329" t="s">
         <v>15</v>
       </c>
       <c r="L11" s="1263"/>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1295" t="s">
+      <c r="A12" s="1308" t="s">
         <v>535</v>
       </c>
-      <c r="B12" s="1296"/>
-      <c r="C12" s="1296"/>
-      <c r="D12" s="1296"/>
-      <c r="E12" s="1296"/>
-      <c r="F12" s="1296"/>
-      <c r="G12" s="1296"/>
-      <c r="H12" s="1296"/>
-      <c r="I12" s="1297"/>
+      <c r="B12" s="1309"/>
+      <c r="C12" s="1309"/>
+      <c r="D12" s="1309"/>
+      <c r="E12" s="1309"/>
+      <c r="F12" s="1309"/>
+      <c r="G12" s="1309"/>
+      <c r="H12" s="1309"/>
+      <c r="I12" s="1310"/>
       <c r="K12" s="329" t="s">
         <v>18</v>
       </c>
@@ -17714,17 +17717,17 @@
       <c r="L14" s="1263"/>
     </row>
     <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1298" t="s">
+      <c r="A15" s="1295" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1298"/>
+      <c r="B15" s="1295"/>
       <c r="C15" s="1189" t="s">
         <v>600</v>
       </c>
-      <c r="D15" s="1299">
+      <c r="D15" s="1311">
         <v>1</v>
       </c>
-      <c r="E15" s="1300"/>
+      <c r="E15" s="1312"/>
       <c r="F15" s="1191">
         <v>2</v>
       </c>
@@ -17743,17 +17746,17 @@
       <c r="L15" s="1265"/>
     </row>
     <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1301" t="s">
+      <c r="A16" s="1287" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1301"/>
+      <c r="B16" s="1287"/>
       <c r="C16" s="1192" t="s">
         <v>600</v>
       </c>
-      <c r="D16" s="1302">
+      <c r="D16" s="1298">
         <v>5</v>
       </c>
-      <c r="E16" s="1303"/>
+      <c r="E16" s="1299"/>
       <c r="F16" s="1194">
         <v>5</v>
       </c>
@@ -17772,15 +17775,15 @@
       <c r="L16" s="1265"/>
     </row>
     <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1301" t="s">
+      <c r="A17" s="1287" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1301"/>
+      <c r="B17" s="1287"/>
       <c r="C17" s="1192" t="s">
         <v>600</v>
       </c>
-      <c r="D17" s="1302"/>
-      <c r="E17" s="1303"/>
+      <c r="D17" s="1298"/>
+      <c r="E17" s="1299"/>
       <c r="F17" s="1194"/>
       <c r="G17" s="1193"/>
       <c r="H17" s="1193"/>
@@ -17791,75 +17794,75 @@
       <c r="L17" s="1266"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1301" t="s">
+      <c r="A18" s="1287" t="s">
         <v>601</v>
       </c>
-      <c r="B18" s="1301"/>
+      <c r="B18" s="1287"/>
       <c r="C18" s="1193" t="s">
         <v>186</v>
       </c>
-      <c r="D18" s="1302"/>
-      <c r="E18" s="1303"/>
+      <c r="D18" s="1298"/>
+      <c r="E18" s="1299"/>
       <c r="F18" s="1195"/>
       <c r="G18" s="1196"/>
       <c r="H18" s="1196"/>
       <c r="I18" s="1195"/>
     </row>
     <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1301" t="s">
+      <c r="A19" s="1287" t="s">
         <v>602</v>
       </c>
-      <c r="B19" s="1301"/>
+      <c r="B19" s="1287"/>
       <c r="C19" s="1193" t="s">
         <v>186</v>
       </c>
-      <c r="D19" s="1302"/>
-      <c r="E19" s="1303"/>
+      <c r="D19" s="1298"/>
+      <c r="E19" s="1299"/>
       <c r="F19" s="1194"/>
       <c r="G19" s="1193"/>
       <c r="H19" s="1197"/>
       <c r="I19" s="1198"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1304" t="s">
+      <c r="A20" s="1300" t="s">
         <v>603</v>
       </c>
-      <c r="B20" s="1305"/>
+      <c r="B20" s="1301"/>
       <c r="C20" s="1199" t="s">
         <v>186</v>
       </c>
-      <c r="D20" s="1302"/>
-      <c r="E20" s="1303"/>
+      <c r="D20" s="1298"/>
+      <c r="E20" s="1299"/>
       <c r="F20" s="1194"/>
       <c r="G20" s="1193"/>
       <c r="H20" s="1197"/>
       <c r="I20" s="1198"/>
     </row>
     <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1301" t="s">
+      <c r="A21" s="1287" t="s">
         <v>604</v>
       </c>
-      <c r="B21" s="1301"/>
+      <c r="B21" s="1287"/>
       <c r="C21" s="1193" t="s">
         <v>605</v>
       </c>
-      <c r="D21" s="1306"/>
-      <c r="E21" s="1307"/>
+      <c r="D21" s="1302"/>
+      <c r="E21" s="1303"/>
       <c r="F21" s="1194"/>
       <c r="G21" s="1193"/>
       <c r="H21" s="1193"/>
       <c r="I21" s="1194"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1308" t="s">
+      <c r="A22" s="1290" t="s">
         <v>606</v>
       </c>
-      <c r="B22" s="1308"/>
+      <c r="B22" s="1290"/>
       <c r="C22" s="1200" t="s">
         <v>607</v>
       </c>
-      <c r="D22" s="1309"/>
-      <c r="E22" s="1310"/>
+      <c r="D22" s="1293"/>
+      <c r="E22" s="1294"/>
       <c r="F22" s="1201"/>
       <c r="G22" s="1202"/>
       <c r="H22" s="1202"/>
@@ -17879,148 +17882,148 @@
       <c r="I23" s="1203"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1298" t="s">
+      <c r="A24" s="1295" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="1298"/>
+      <c r="B24" s="1295"/>
       <c r="C24" s="1204"/>
-      <c r="D24" s="1311"/>
-      <c r="E24" s="1312"/>
+      <c r="D24" s="1296"/>
+      <c r="E24" s="1297"/>
       <c r="F24" s="1206"/>
       <c r="G24" s="1205"/>
       <c r="H24" s="1205"/>
       <c r="I24" s="1206"/>
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1301" t="s">
+      <c r="A25" s="1287" t="s">
         <v>608</v>
       </c>
-      <c r="B25" s="1301"/>
+      <c r="B25" s="1287"/>
       <c r="C25" s="1199" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="1313"/>
-      <c r="E25" s="1314"/>
+      <c r="D25" s="1288"/>
+      <c r="E25" s="1289"/>
       <c r="F25" s="1208"/>
       <c r="G25" s="1207"/>
       <c r="H25" s="1207"/>
       <c r="I25" s="1208"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1301" t="s">
+      <c r="A26" s="1287" t="s">
         <v>609</v>
       </c>
-      <c r="B26" s="1301"/>
+      <c r="B26" s="1287"/>
       <c r="C26" s="1199" t="s">
         <v>186</v>
       </c>
-      <c r="D26" s="1313"/>
-      <c r="E26" s="1314"/>
+      <c r="D26" s="1288"/>
+      <c r="E26" s="1289"/>
       <c r="F26" s="1208"/>
       <c r="G26" s="1207"/>
       <c r="H26" s="1207"/>
       <c r="I26" s="1208"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1301" t="s">
+      <c r="A27" s="1287" t="s">
         <v>610</v>
       </c>
-      <c r="B27" s="1301"/>
+      <c r="B27" s="1287"/>
       <c r="C27" s="1199" t="s">
         <v>186</v>
       </c>
-      <c r="D27" s="1313"/>
-      <c r="E27" s="1314"/>
+      <c r="D27" s="1288"/>
+      <c r="E27" s="1289"/>
       <c r="F27" s="1208"/>
       <c r="G27" s="1207"/>
       <c r="H27" s="1207"/>
       <c r="I27" s="1208"/>
     </row>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1301" t="s">
+      <c r="A28" s="1287" t="s">
         <v>611</v>
       </c>
-      <c r="B28" s="1301"/>
+      <c r="B28" s="1287"/>
       <c r="C28" s="1199" t="s">
         <v>186</v>
       </c>
-      <c r="D28" s="1313"/>
-      <c r="E28" s="1314"/>
+      <c r="D28" s="1288"/>
+      <c r="E28" s="1289"/>
       <c r="F28" s="1208"/>
       <c r="G28" s="1207"/>
       <c r="H28" s="1207"/>
       <c r="I28" s="1208"/>
     </row>
     <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1301" t="s">
+      <c r="A29" s="1287" t="s">
         <v>612</v>
       </c>
-      <c r="B29" s="1301"/>
+      <c r="B29" s="1287"/>
       <c r="C29" s="1199" t="s">
         <v>186</v>
       </c>
-      <c r="D29" s="1313"/>
-      <c r="E29" s="1314"/>
+      <c r="D29" s="1288"/>
+      <c r="E29" s="1289"/>
       <c r="F29" s="1209"/>
       <c r="G29" s="1210"/>
       <c r="H29" s="1210"/>
       <c r="I29" s="1209"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1301" t="s">
+      <c r="A30" s="1287" t="s">
         <v>613</v>
       </c>
-      <c r="B30" s="1301"/>
+      <c r="B30" s="1287"/>
       <c r="C30" s="1199" t="s">
         <v>186</v>
       </c>
-      <c r="D30" s="1313"/>
-      <c r="E30" s="1314"/>
+      <c r="D30" s="1288"/>
+      <c r="E30" s="1289"/>
       <c r="F30" s="1209"/>
       <c r="G30" s="1210"/>
       <c r="H30" s="1210"/>
       <c r="I30" s="1209"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1301" t="s">
+      <c r="A31" s="1287" t="s">
         <v>614</v>
       </c>
-      <c r="B31" s="1301"/>
+      <c r="B31" s="1287"/>
       <c r="C31" s="1199" t="s">
         <v>186</v>
       </c>
-      <c r="D31" s="1313"/>
-      <c r="E31" s="1314"/>
+      <c r="D31" s="1288"/>
+      <c r="E31" s="1289"/>
       <c r="F31" s="1209"/>
       <c r="G31" s="1210"/>
       <c r="H31" s="1210"/>
       <c r="I31" s="1209"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1301" t="s">
+      <c r="A32" s="1287" t="s">
         <v>615</v>
       </c>
-      <c r="B32" s="1301"/>
+      <c r="B32" s="1287"/>
       <c r="C32" s="1193" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="1313"/>
-      <c r="E32" s="1314"/>
+      <c r="D32" s="1288"/>
+      <c r="E32" s="1289"/>
       <c r="F32" s="1211"/>
       <c r="G32" s="1212"/>
       <c r="H32" s="1212"/>
       <c r="I32" s="1211"/>
     </row>
     <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1308" t="s">
+      <c r="A33" s="1290" t="s">
         <v>616</v>
       </c>
-      <c r="B33" s="1308"/>
+      <c r="B33" s="1290"/>
       <c r="C33" s="1200" t="s">
         <v>607</v>
       </c>
-      <c r="D33" s="1315"/>
-      <c r="E33" s="1316"/>
+      <c r="D33" s="1291"/>
+      <c r="E33" s="1292"/>
       <c r="F33" s="1201"/>
       <c r="G33" s="1202"/>
       <c r="H33" s="1202"/>
@@ -18046,19 +18049,19 @@
         <v>618</v>
       </c>
       <c r="B35" s="1218"/>
-      <c r="C35" s="1317"/>
-      <c r="D35" s="1318"/>
+      <c r="C35" s="1282"/>
+      <c r="D35" s="1283"/>
       <c r="E35" s="1219"/>
-      <c r="F35" s="1321" t="s">
+      <c r="F35" s="1280" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="1321" t="s">
+      <c r="G35" s="1280" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="1321" t="s">
+      <c r="H35" s="1280" t="s">
         <v>619</v>
       </c>
-      <c r="I35" s="1321" t="s">
+      <c r="I35" s="1280" t="s">
         <v>235</v>
       </c>
     </row>
@@ -18067,21 +18070,21 @@
         <v>620</v>
       </c>
       <c r="B36" s="1221"/>
-      <c r="C36" s="1317"/>
-      <c r="D36" s="1318"/>
+      <c r="C36" s="1282"/>
+      <c r="D36" s="1283"/>
       <c r="E36" s="1219"/>
-      <c r="F36" s="1322"/>
-      <c r="G36" s="1322"/>
-      <c r="H36" s="1322"/>
-      <c r="I36" s="1322"/>
+      <c r="F36" s="1281"/>
+      <c r="G36" s="1281"/>
+      <c r="H36" s="1281"/>
+      <c r="I36" s="1281"/>
     </row>
     <row r="37" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1220" t="s">
         <v>621</v>
       </c>
       <c r="B37" s="1221"/>
-      <c r="C37" s="1323"/>
-      <c r="D37" s="1318"/>
+      <c r="C37" s="1284"/>
+      <c r="D37" s="1283"/>
       <c r="E37" s="1222"/>
       <c r="F37" s="1223" t="s">
         <v>622</v>
@@ -18095,8 +18098,8 @@
         <v>623</v>
       </c>
       <c r="B38" s="1228"/>
-      <c r="C38" s="1317"/>
-      <c r="D38" s="1318"/>
+      <c r="C38" s="1282"/>
+      <c r="D38" s="1283"/>
       <c r="E38" s="1219"/>
       <c r="F38" s="1223" t="s">
         <v>624</v>
@@ -18110,8 +18113,8 @@
         <v>625</v>
       </c>
       <c r="B39" s="1221"/>
-      <c r="C39" s="1317"/>
-      <c r="D39" s="1318"/>
+      <c r="C39" s="1282"/>
+      <c r="D39" s="1283"/>
       <c r="E39" s="1219"/>
       <c r="F39" s="1223" t="s">
         <v>114</v>
@@ -18140,8 +18143,8 @@
         <v>626</v>
       </c>
       <c r="B41" s="1231"/>
-      <c r="C41" s="1324"/>
-      <c r="D41" s="1324"/>
+      <c r="C41" s="1276"/>
+      <c r="D41" s="1276"/>
       <c r="E41" s="1229"/>
       <c r="F41" s="1223" t="s">
         <v>627</v>
@@ -18155,8 +18158,8 @@
         <v>628</v>
       </c>
       <c r="B42" s="1233"/>
-      <c r="C42" s="1324"/>
-      <c r="D42" s="1324"/>
+      <c r="C42" s="1276"/>
+      <c r="D42" s="1276"/>
       <c r="E42" s="1234"/>
       <c r="J42" s="1235"/>
     </row>
@@ -18165,17 +18168,17 @@
         <v>629</v>
       </c>
       <c r="B43" s="1237"/>
-      <c r="C43" s="1324"/>
-      <c r="D43" s="1324"/>
+      <c r="C43" s="1276"/>
+      <c r="D43" s="1276"/>
       <c r="E43" s="1234"/>
-      <c r="F43" s="1325" t="s">
+      <c r="F43" s="1285" t="s">
         <v>630</v>
       </c>
-      <c r="G43" s="1326"/>
-      <c r="H43" s="1319" t="s">
+      <c r="G43" s="1286"/>
+      <c r="H43" s="1274" t="s">
         <v>631</v>
       </c>
-      <c r="I43" s="1320"/>
+      <c r="I43" s="1275"/>
       <c r="J43" s="1235"/>
     </row>
     <row r="44" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18183,31 +18186,31 @@
         <v>632</v>
       </c>
       <c r="B44" s="1233"/>
-      <c r="C44" s="1324"/>
-      <c r="D44" s="1324"/>
+      <c r="C44" s="1276"/>
+      <c r="D44" s="1276"/>
       <c r="E44" s="1234"/>
       <c r="F44" s="1238" t="s">
         <v>633</v>
       </c>
       <c r="G44" s="1239"/>
-      <c r="H44" s="1319"/>
-      <c r="I44" s="1320"/>
+      <c r="H44" s="1274"/>
+      <c r="I44" s="1275"/>
       <c r="J44" s="1235"/>
     </row>
     <row r="45" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1328" t="s">
+      <c r="A45" s="1278" t="s">
         <v>634</v>
       </c>
-      <c r="B45" s="1329"/>
-      <c r="C45" s="1324"/>
-      <c r="D45" s="1324"/>
+      <c r="B45" s="1279"/>
+      <c r="C45" s="1276"/>
+      <c r="D45" s="1276"/>
       <c r="E45" s="1234"/>
       <c r="F45" s="1238" t="s">
         <v>635</v>
       </c>
       <c r="G45" s="1239"/>
-      <c r="H45" s="1319"/>
-      <c r="I45" s="1320"/>
+      <c r="H45" s="1274"/>
+      <c r="I45" s="1275"/>
       <c r="J45" s="1235"/>
     </row>
     <row r="46" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18221,8 +18224,8 @@
         <v>636</v>
       </c>
       <c r="G46" s="1239"/>
-      <c r="H46" s="1319"/>
-      <c r="I46" s="1320"/>
+      <c r="H46" s="1274"/>
+      <c r="I46" s="1275"/>
     </row>
     <row r="47" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1243"/>
@@ -18233,8 +18236,8 @@
         <v>637</v>
       </c>
       <c r="G47" s="1239"/>
-      <c r="H47" s="1319"/>
-      <c r="I47" s="1320"/>
+      <c r="H47" s="1274"/>
+      <c r="I47" s="1275"/>
     </row>
     <row r="48" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1243"/>
@@ -18245,8 +18248,8 @@
         <v>589</v>
       </c>
       <c r="G48" s="1246"/>
-      <c r="H48" s="1319"/>
-      <c r="I48" s="1320"/>
+      <c r="H48" s="1274"/>
+      <c r="I48" s="1275"/>
     </row>
     <row r="49" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1247"/>
@@ -18257,8 +18260,8 @@
         <v>638</v>
       </c>
       <c r="G49" s="1239"/>
-      <c r="H49" s="1324"/>
-      <c r="I49" s="1324"/>
+      <c r="H49" s="1276"/>
+      <c r="I49" s="1276"/>
     </row>
     <row r="50" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E50" s="352"/>
@@ -18299,17 +18302,17 @@
     </row>
     <row r="55" spans="1:9" ht="0.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1327" t="s">
+      <c r="A56" s="1277" t="s">
         <v>641</v>
       </c>
-      <c r="B56" s="1327"/>
-      <c r="C56" s="1327"/>
-      <c r="D56" s="1327"/>
-      <c r="E56" s="1327"/>
-      <c r="F56" s="1327"/>
-      <c r="G56" s="1327"/>
-      <c r="H56" s="1327"/>
-      <c r="I56" s="1327"/>
+      <c r="B56" s="1277"/>
+      <c r="C56" s="1277"/>
+      <c r="D56" s="1277"/>
+      <c r="E56" s="1277"/>
+      <c r="F56" s="1277"/>
+      <c r="G56" s="1277"/>
+      <c r="H56" s="1277"/>
+      <c r="I56" s="1277"/>
     </row>
     <row r="57" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -18319,16 +18322,54 @@
     <protectedRange sqref="B9:C10" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="71">
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="H35:H36"/>
@@ -18342,54 +18383,16 @@
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.3" top="0.75" bottom="0.15" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="80" fitToWidth="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -18496,33 +18499,33 @@
       <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1502" t="s">
+      <c r="A8" s="1520" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1502"/>
-      <c r="C8" s="1502"/>
-      <c r="D8" s="1502"/>
-      <c r="E8" s="1502"/>
-      <c r="F8" s="1502"/>
-      <c r="G8" s="1502"/>
-      <c r="H8" s="1502"/>
-      <c r="I8" s="1502"/>
-      <c r="J8" s="1502"/>
+      <c r="B8" s="1520"/>
+      <c r="C8" s="1520"/>
+      <c r="D8" s="1520"/>
+      <c r="E8" s="1520"/>
+      <c r="F8" s="1520"/>
+      <c r="G8" s="1520"/>
+      <c r="H8" s="1520"/>
+      <c r="I8" s="1520"/>
+      <c r="J8" s="1520"/>
     </row>
     <row r="9" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1527">
+      <c r="A9" s="1523">
         <f>J13</f>
         <v>1</v>
       </c>
-      <c r="B9" s="1527"/>
-      <c r="C9" s="1527"/>
-      <c r="D9" s="1527"/>
-      <c r="E9" s="1527"/>
-      <c r="F9" s="1527"/>
-      <c r="G9" s="1527"/>
-      <c r="H9" s="1527"/>
-      <c r="I9" s="1527"/>
-      <c r="J9" s="1527"/>
+      <c r="B9" s="1523"/>
+      <c r="C9" s="1523"/>
+      <c r="D9" s="1523"/>
+      <c r="E9" s="1523"/>
+      <c r="F9" s="1523"/>
+      <c r="G9" s="1523"/>
+      <c r="H9" s="1523"/>
+      <c r="I9" s="1523"/>
+      <c r="J9" s="1523"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -18544,13 +18547,13 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1504" t="s">
+      <c r="C11" s="1522" t="s">
         <v>281</v>
       </c>
-      <c r="D11" s="1504"/>
-      <c r="E11" s="1504"/>
-      <c r="F11" s="1504"/>
-      <c r="G11" s="1504"/>
+      <c r="D11" s="1522"/>
+      <c r="E11" s="1522"/>
+      <c r="F11" s="1522"/>
+      <c r="G11" s="1522"/>
       <c r="H11" s="121" t="s">
         <v>3</v>
       </c>
@@ -18572,13 +18575,13 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1504" t="s">
+      <c r="C12" s="1522" t="s">
         <v>286</v>
       </c>
-      <c r="D12" s="1504"/>
-      <c r="E12" s="1504"/>
-      <c r="F12" s="1504"/>
-      <c r="G12" s="1504"/>
+      <c r="D12" s="1522"/>
+      <c r="E12" s="1522"/>
+      <c r="F12" s="1522"/>
+      <c r="G12" s="1522"/>
       <c r="H12" s="26" t="s">
         <v>6</v>
       </c>
@@ -18602,13 +18605,13 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1504" t="s">
+      <c r="C13" s="1522" t="s">
         <v>291</v>
       </c>
-      <c r="D13" s="1504"/>
-      <c r="E13" s="1504"/>
-      <c r="F13" s="1504"/>
-      <c r="G13" s="1504"/>
+      <c r="D13" s="1522"/>
+      <c r="E13" s="1522"/>
+      <c r="F13" s="1522"/>
+      <c r="G13" s="1522"/>
       <c r="H13" s="26" t="s">
         <v>292</v>
       </c>
@@ -18621,8 +18624,8 @@
       <c r="K13" s="124"/>
       <c r="L13" s="124"/>
       <c r="M13" s="124"/>
-      <c r="P13" s="1501"/>
-      <c r="Q13" s="1501"/>
+      <c r="P13" s="1519"/>
+      <c r="Q13" s="1519"/>
     </row>
     <row r="14" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -18642,34 +18645,34 @@
       <c r="Q14" s="737"/>
     </row>
     <row r="15" spans="1:17" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1505" t="s">
+      <c r="A15" s="1508" t="s">
         <v>371</v>
       </c>
-      <c r="B15" s="1506"/>
-      <c r="C15" s="1506"/>
-      <c r="D15" s="1506"/>
-      <c r="E15" s="1506"/>
-      <c r="F15" s="1506"/>
-      <c r="G15" s="1506"/>
-      <c r="H15" s="1506"/>
-      <c r="I15" s="1506"/>
-      <c r="J15" s="1507"/>
+      <c r="B15" s="1509"/>
+      <c r="C15" s="1509"/>
+      <c r="D15" s="1509"/>
+      <c r="E15" s="1509"/>
+      <c r="F15" s="1509"/>
+      <c r="G15" s="1509"/>
+      <c r="H15" s="1509"/>
+      <c r="I15" s="1509"/>
+      <c r="J15" s="1510"/>
       <c r="K15" s="124"/>
       <c r="L15" s="124"/>
     </row>
     <row r="16" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1508" t="s">
+      <c r="A16" s="1511" t="s">
         <v>372</v>
       </c>
-      <c r="B16" s="1509"/>
-      <c r="C16" s="1509"/>
-      <c r="D16" s="1509"/>
-      <c r="E16" s="1509"/>
-      <c r="F16" s="1509"/>
-      <c r="G16" s="1509"/>
-      <c r="H16" s="1509"/>
-      <c r="I16" s="1509"/>
-      <c r="J16" s="1510"/>
+      <c r="B16" s="1512"/>
+      <c r="C16" s="1512"/>
+      <c r="D16" s="1512"/>
+      <c r="E16" s="1512"/>
+      <c r="F16" s="1512"/>
+      <c r="G16" s="1512"/>
+      <c r="H16" s="1512"/>
+      <c r="I16" s="1512"/>
+      <c r="J16" s="1513"/>
       <c r="K16" s="124"/>
       <c r="L16" s="124"/>
     </row>
@@ -18688,18 +18691,18 @@
       <c r="L17" s="124"/>
     </row>
     <row r="18" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1475" t="s">
+      <c r="A18" s="1483" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1476"/>
-      <c r="C18" s="1476"/>
-      <c r="D18" s="1476"/>
-      <c r="E18" s="1476"/>
-      <c r="F18" s="1476"/>
-      <c r="G18" s="1476"/>
-      <c r="H18" s="1476"/>
-      <c r="I18" s="1476"/>
-      <c r="J18" s="1477"/>
+      <c r="B18" s="1484"/>
+      <c r="C18" s="1484"/>
+      <c r="D18" s="1484"/>
+      <c r="E18" s="1484"/>
+      <c r="F18" s="1484"/>
+      <c r="G18" s="1484"/>
+      <c r="H18" s="1484"/>
+      <c r="I18" s="1484"/>
+      <c r="J18" s="1485"/>
       <c r="L18" s="124"/>
     </row>
     <row r="19" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -18814,12 +18817,12 @@
     <row r="24" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="251"/>
       <c r="B24" s="249"/>
-      <c r="C24" s="1523" t="s">
+      <c r="C24" s="1524" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="1524"/>
-      <c r="E24" s="1524"/>
-      <c r="F24" s="1525"/>
+      <c r="D24" s="1525"/>
+      <c r="E24" s="1525"/>
+      <c r="F24" s="1526"/>
       <c r="G24" s="249"/>
       <c r="H24" s="249"/>
       <c r="I24" s="249"/>
@@ -18936,10 +18939,10 @@
     <row r="28" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="251"/>
       <c r="B28" s="173"/>
-      <c r="C28" s="1526"/>
-      <c r="D28" s="1526"/>
-      <c r="E28" s="1526"/>
-      <c r="F28" s="1526"/>
+      <c r="C28" s="1527"/>
+      <c r="D28" s="1527"/>
+      <c r="E28" s="1527"/>
+      <c r="F28" s="1527"/>
       <c r="G28" s="247"/>
       <c r="H28" s="260"/>
       <c r="I28" s="260"/>
@@ -18963,12 +18966,12 @@
     <row r="29" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="251"/>
       <c r="B29" s="173"/>
-      <c r="C29" s="1523" t="s">
+      <c r="C29" s="1524" t="s">
         <v>383</v>
       </c>
-      <c r="D29" s="1524"/>
-      <c r="E29" s="1524"/>
-      <c r="F29" s="1525"/>
+      <c r="D29" s="1525"/>
+      <c r="E29" s="1525"/>
+      <c r="F29" s="1526"/>
       <c r="G29" s="275" t="s">
         <v>384</v>
       </c>
@@ -19397,18 +19400,18 @@
     </row>
     <row r="53" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1483" t="s">
+      <c r="A54" s="1461" t="s">
         <v>349</v>
       </c>
-      <c r="B54" s="1483"/>
-      <c r="C54" s="1483"/>
-      <c r="D54" s="1483"/>
-      <c r="E54" s="1483"/>
-      <c r="F54" s="1483"/>
-      <c r="G54" s="1483"/>
-      <c r="H54" s="1483"/>
-      <c r="I54" s="1483"/>
-      <c r="J54" s="1483"/>
+      <c r="B54" s="1461"/>
+      <c r="C54" s="1461"/>
+      <c r="D54" s="1461"/>
+      <c r="E54" s="1461"/>
+      <c r="F54" s="1461"/>
+      <c r="G54" s="1461"/>
+      <c r="H54" s="1461"/>
+      <c r="I54" s="1461"/>
+      <c r="J54" s="1461"/>
     </row>
     <row r="55" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19418,12 +19421,6 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="13">
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A16:J16"/>
@@ -19431,6 +19428,12 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -19462,15 +19465,15 @@
       <c r="A1" s="82" t="s">
         <v>393</v>
       </c>
-      <c r="B1" s="1528" t="s">
+      <c r="B1" s="1545" t="s">
         <v>394</v>
       </c>
-      <c r="C1" s="1528"/>
-      <c r="D1" s="1528"/>
-      <c r="E1" s="1528"/>
-      <c r="F1" s="1528"/>
-      <c r="G1" s="1528"/>
-      <c r="H1" s="1528"/>
+      <c r="C1" s="1545"/>
+      <c r="D1" s="1545"/>
+      <c r="E1" s="1545"/>
+      <c r="F1" s="1545"/>
+      <c r="G1" s="1545"/>
+      <c r="H1" s="1545"/>
       <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -19608,29 +19611,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="82"/>
-      <c r="B8" s="1529" t="s">
+      <c r="B8" s="1546" t="s">
         <v>406</v>
       </c>
-      <c r="C8" s="1529"/>
-      <c r="D8" s="1529"/>
+      <c r="C8" s="1546"/>
+      <c r="D8" s="1546"/>
       <c r="E8" s="830" t="s">
         <v>407</v>
       </c>
       <c r="F8" s="831" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="1530" t="s">
+      <c r="G8" s="1547" t="s">
         <v>409</v>
       </c>
-      <c r="H8" s="1530"/>
+      <c r="H8" s="1547"/>
       <c r="I8" s="82"/>
       <c r="L8" s="90" t="s">
         <v>410</v>
       </c>
-      <c r="M8" s="1531" t="s">
+      <c r="M8" s="1548" t="s">
         <v>411</v>
       </c>
-      <c r="N8" s="1531"/>
+      <c r="N8" s="1548"/>
       <c r="O8" s="91" t="s">
         <v>412</v>
       </c>
@@ -19643,13 +19646,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82"/>
-      <c r="B9" s="1532" t="s">
+      <c r="B9" s="1549" t="s">
         <v>415</v>
       </c>
-      <c r="C9" s="1534" t="s">
+      <c r="C9" s="1551" t="s">
         <v>416</v>
       </c>
-      <c r="D9" s="1536" t="s">
+      <c r="D9" s="1553" t="s">
         <v>417</v>
       </c>
       <c r="E9" s="832" t="s">
@@ -19658,10 +19661,10 @@
       <c r="F9" s="833" t="s">
         <v>419</v>
       </c>
-      <c r="G9" s="1537" t="s">
+      <c r="G9" s="1554" t="s">
         <v>420</v>
       </c>
-      <c r="H9" s="1538"/>
+      <c r="H9" s="1555"/>
       <c r="I9" s="82"/>
       <c r="L9" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -19690,19 +19693,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="82"/>
-      <c r="B10" s="1532"/>
-      <c r="C10" s="1534"/>
-      <c r="D10" s="1536"/>
+      <c r="B10" s="1549"/>
+      <c r="C10" s="1551"/>
+      <c r="D10" s="1553"/>
       <c r="E10" s="834" t="s">
         <v>421</v>
       </c>
       <c r="F10" s="835" t="s">
         <v>422</v>
       </c>
-      <c r="G10" s="1539" t="s">
+      <c r="G10" s="1556" t="s">
         <v>423</v>
       </c>
-      <c r="H10" s="1540"/>
+      <c r="H10" s="1557"/>
       <c r="I10" s="82"/>
       <c r="L10" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -19727,9 +19730,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="82"/>
-      <c r="B11" s="1532"/>
-      <c r="C11" s="1534"/>
-      <c r="D11" s="1536" t="s">
+      <c r="B11" s="1549"/>
+      <c r="C11" s="1551"/>
+      <c r="D11" s="1553" t="s">
         <v>424</v>
       </c>
       <c r="E11" s="834" t="s">
@@ -19741,7 +19744,7 @@
       <c r="G11" s="837" t="s">
         <v>427</v>
       </c>
-      <c r="H11" s="1541" t="s">
+      <c r="H11" s="1558" t="s">
         <v>428</v>
       </c>
       <c r="I11" s="82"/>
@@ -19760,9 +19763,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="82"/>
-      <c r="B12" s="1532"/>
-      <c r="C12" s="1535"/>
-      <c r="D12" s="1536"/>
+      <c r="B12" s="1549"/>
+      <c r="C12" s="1552"/>
+      <c r="D12" s="1553"/>
       <c r="E12" s="93" t="s">
         <v>429</v>
       </c>
@@ -19772,7 +19775,7 @@
       <c r="G12" s="837" t="s">
         <v>431</v>
       </c>
-      <c r="H12" s="1542"/>
+      <c r="H12" s="1559"/>
       <c r="I12" s="82"/>
       <c r="L12" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -19785,11 +19788,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="82"/>
-      <c r="B13" s="1532"/>
-      <c r="C13" s="1534" t="s">
+      <c r="B13" s="1549"/>
+      <c r="C13" s="1551" t="s">
         <v>432</v>
       </c>
-      <c r="D13" s="1536" t="s">
+      <c r="D13" s="1553" t="s">
         <v>433</v>
       </c>
       <c r="E13" s="838" t="s">
@@ -19798,10 +19801,10 @@
       <c r="F13" s="839" t="s">
         <v>435</v>
       </c>
-      <c r="G13" s="1543" t="s">
+      <c r="G13" s="1560" t="s">
         <v>436</v>
       </c>
-      <c r="H13" s="1544"/>
+      <c r="H13" s="1561"/>
       <c r="I13" s="82"/>
       <c r="L13" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -19826,19 +19829,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="82"/>
-      <c r="B14" s="1532"/>
-      <c r="C14" s="1534"/>
-      <c r="D14" s="1536"/>
+      <c r="B14" s="1549"/>
+      <c r="C14" s="1551"/>
+      <c r="D14" s="1553"/>
       <c r="E14" s="838" t="s">
         <v>437</v>
       </c>
       <c r="F14" s="839" t="s">
         <v>438</v>
       </c>
-      <c r="G14" s="1543" t="s">
+      <c r="G14" s="1560" t="s">
         <v>439</v>
       </c>
-      <c r="H14" s="1544"/>
+      <c r="H14" s="1561"/>
       <c r="I14" s="82"/>
       <c r="L14" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -19863,9 +19866,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="82"/>
-      <c r="B15" s="1532"/>
-      <c r="C15" s="1534"/>
-      <c r="D15" s="1536" t="s">
+      <c r="B15" s="1549"/>
+      <c r="C15" s="1551"/>
+      <c r="D15" s="1553" t="s">
         <v>440</v>
       </c>
       <c r="E15" s="838" t="s">
@@ -19877,7 +19880,7 @@
       <c r="G15" s="841" t="s">
         <v>443</v>
       </c>
-      <c r="H15" s="1545" t="s">
+      <c r="H15" s="1528" t="s">
         <v>444</v>
       </c>
       <c r="I15" s="82"/>
@@ -19896,9 +19899,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="82"/>
-      <c r="B16" s="1533"/>
-      <c r="C16" s="1534"/>
-      <c r="D16" s="1536"/>
+      <c r="B16" s="1550"/>
+      <c r="C16" s="1551"/>
+      <c r="D16" s="1553"/>
       <c r="E16" s="94" t="s">
         <v>445</v>
       </c>
@@ -19908,7 +19911,7 @@
       <c r="G16" s="839" t="s">
         <v>447</v>
       </c>
-      <c r="H16" s="1546"/>
+      <c r="H16" s="1529"/>
       <c r="I16" s="82"/>
       <c r="L16" s="77" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -19921,23 +19924,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="82"/>
-      <c r="B17" s="1547" t="s">
+      <c r="B17" s="1530" t="s">
         <v>448</v>
       </c>
-      <c r="C17" s="1550" t="s">
+      <c r="C17" s="1533" t="s">
         <v>449</v>
       </c>
-      <c r="D17" s="1551"/>
+      <c r="D17" s="1534"/>
       <c r="E17" s="842" t="s">
         <v>450</v>
       </c>
       <c r="F17" s="843" t="s">
         <v>451</v>
       </c>
-      <c r="G17" s="1556" t="s">
+      <c r="G17" s="1539" t="s">
         <v>452</v>
       </c>
-      <c r="H17" s="1557"/>
+      <c r="H17" s="1540"/>
       <c r="I17" s="82"/>
       <c r="L17" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -19950,17 +19953,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="82"/>
-      <c r="B18" s="1548"/>
-      <c r="C18" s="1552"/>
-      <c r="D18" s="1553"/>
+      <c r="B18" s="1531"/>
+      <c r="C18" s="1535"/>
+      <c r="D18" s="1536"/>
       <c r="E18" s="842" t="s">
         <v>453</v>
       </c>
       <c r="F18" s="843" t="s">
         <v>454</v>
       </c>
-      <c r="G18" s="1558"/>
-      <c r="H18" s="1559"/>
+      <c r="G18" s="1541"/>
+      <c r="H18" s="1542"/>
       <c r="I18" s="82"/>
       <c r="L18" s="77" t="str">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -19973,9 +19976,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="82"/>
-      <c r="B19" s="1548"/>
-      <c r="C19" s="1554"/>
-      <c r="D19" s="1555"/>
+      <c r="B19" s="1531"/>
+      <c r="C19" s="1537"/>
+      <c r="D19" s="1538"/>
       <c r="E19" s="842" t="s">
         <v>455</v>
       </c>
@@ -19996,11 +19999,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="82"/>
-      <c r="B20" s="1548"/>
-      <c r="C20" s="1552" t="s">
+      <c r="B20" s="1531"/>
+      <c r="C20" s="1535" t="s">
         <v>457</v>
       </c>
-      <c r="D20" s="1560"/>
+      <c r="D20" s="1543"/>
       <c r="E20" s="844" t="s">
         <v>458</v>
       </c>
@@ -20021,9 +20024,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="82"/>
-      <c r="B21" s="1548"/>
-      <c r="C21" s="1552"/>
-      <c r="D21" s="1560"/>
+      <c r="B21" s="1531"/>
+      <c r="C21" s="1535"/>
+      <c r="D21" s="1543"/>
       <c r="E21" s="844" t="s">
         <v>145</v>
       </c>
@@ -20044,9 +20047,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="82"/>
-      <c r="B22" s="1548"/>
-      <c r="C22" s="1554"/>
-      <c r="D22" s="1561"/>
+      <c r="B22" s="1531"/>
+      <c r="C22" s="1537"/>
+      <c r="D22" s="1544"/>
       <c r="E22" s="98" t="s">
         <v>461</v>
       </c>
@@ -20067,11 +20070,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="82"/>
-      <c r="B23" s="1548"/>
-      <c r="C23" s="1550" t="s">
+      <c r="B23" s="1531"/>
+      <c r="C23" s="1533" t="s">
         <v>463</v>
       </c>
-      <c r="D23" s="1551"/>
+      <c r="D23" s="1534"/>
       <c r="E23" s="845" t="s">
         <v>464</v>
       </c>
@@ -20092,7 +20095,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="82"/>
-      <c r="B24" s="1549"/>
+      <c r="B24" s="1532"/>
       <c r="C24" s="847"/>
       <c r="D24" s="848"/>
       <c r="E24" s="849"/>
@@ -20199,12 +20202,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -20221,6 +20218,12 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21511,37 +21514,37 @@
       <c r="N5" s="1101"/>
     </row>
     <row r="6" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1353" t="s">
+      <c r="A6" s="1355" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1353"/>
-      <c r="C6" s="1353"/>
-      <c r="D6" s="1353"/>
-      <c r="E6" s="1353"/>
-      <c r="F6" s="1353"/>
-      <c r="G6" s="1353"/>
-      <c r="H6" s="1353"/>
-      <c r="I6" s="1353"/>
-      <c r="J6" s="1353"/>
-      <c r="K6" s="1353"/>
-      <c r="L6" s="1353"/>
+      <c r="B6" s="1355"/>
+      <c r="C6" s="1355"/>
+      <c r="D6" s="1355"/>
+      <c r="E6" s="1355"/>
+      <c r="F6" s="1355"/>
+      <c r="G6" s="1355"/>
+      <c r="H6" s="1355"/>
+      <c r="I6" s="1355"/>
+      <c r="J6" s="1355"/>
+      <c r="K6" s="1355"/>
+      <c r="L6" s="1355"/>
       <c r="N6" s="961"/>
     </row>
     <row r="7" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1354">
+      <c r="A7" s="1356">
         <v>0</v>
       </c>
-      <c r="B7" s="1354"/>
-      <c r="C7" s="1354"/>
-      <c r="D7" s="1354"/>
-      <c r="E7" s="1354"/>
-      <c r="F7" s="1354"/>
-      <c r="G7" s="1354"/>
-      <c r="H7" s="1354"/>
-      <c r="I7" s="1354"/>
-      <c r="J7" s="1354"/>
-      <c r="K7" s="1354"/>
-      <c r="L7" s="1354"/>
+      <c r="B7" s="1356"/>
+      <c r="C7" s="1356"/>
+      <c r="D7" s="1356"/>
+      <c r="E7" s="1356"/>
+      <c r="F7" s="1356"/>
+      <c r="G7" s="1356"/>
+      <c r="H7" s="1356"/>
+      <c r="I7" s="1356"/>
+      <c r="J7" s="1356"/>
+      <c r="K7" s="1356"/>
+      <c r="L7" s="1356"/>
       <c r="N7" s="962"/>
     </row>
     <row r="8" spans="1:40" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -21569,15 +21572,15 @@
       <c r="B9" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="1364">
+      <c r="C9" s="1366">
         <f>+formato!L2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="1364"/>
-      <c r="E9" s="1364"/>
-      <c r="F9" s="1364"/>
-      <c r="G9" s="1364"/>
-      <c r="H9" s="1364"/>
+      <c r="D9" s="1366"/>
+      <c r="E9" s="1366"/>
+      <c r="F9" s="1366"/>
+      <c r="G9" s="1366"/>
+      <c r="H9" s="1366"/>
       <c r="I9" s="963"/>
       <c r="J9" s="329" t="s">
         <v>3</v>
@@ -21612,15 +21615,15 @@
       <c r="B10" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1364">
+      <c r="C10" s="1366">
         <f>+formato!L3</f>
         <v>0</v>
       </c>
-      <c r="D10" s="1364"/>
-      <c r="E10" s="1364"/>
-      <c r="F10" s="1364"/>
-      <c r="G10" s="1364"/>
-      <c r="H10" s="1364"/>
+      <c r="D10" s="1366"/>
+      <c r="E10" s="1366"/>
+      <c r="F10" s="1366"/>
+      <c r="G10" s="1366"/>
+      <c r="H10" s="1366"/>
       <c r="I10" s="964"/>
       <c r="J10" s="329" t="s">
         <v>538</v>
@@ -21656,15 +21659,15 @@
       <c r="B11" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1364">
+      <c r="C11" s="1366">
         <f>+formato!L4</f>
         <v>0</v>
       </c>
-      <c r="D11" s="1364"/>
-      <c r="E11" s="1364"/>
-      <c r="F11" s="1364"/>
-      <c r="G11" s="1364"/>
-      <c r="H11" s="1364"/>
+      <c r="D11" s="1366"/>
+      <c r="E11" s="1366"/>
+      <c r="F11" s="1366"/>
+      <c r="G11" s="1366"/>
+      <c r="H11" s="1366"/>
       <c r="I11" s="964"/>
       <c r="J11" s="329" t="s">
         <v>8</v>
@@ -21700,16 +21703,16 @@
       <c r="B12" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1364">
+      <c r="C12" s="1366">
         <f>+formato!L5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="1364"/>
-      <c r="E12" s="1364"/>
-      <c r="F12" s="1364"/>
-      <c r="G12" s="1364"/>
-      <c r="H12" s="1364"/>
-      <c r="I12" s="1364"/>
+      <c r="D12" s="1366"/>
+      <c r="E12" s="1366"/>
+      <c r="F12" s="1366"/>
+      <c r="G12" s="1366"/>
+      <c r="H12" s="1366"/>
+      <c r="I12" s="1366"/>
       <c r="J12" s="478"/>
       <c r="K12" s="478"/>
       <c r="M12" s="1102"/>
@@ -21762,20 +21765,20 @@
       <c r="AN13" s="722"/>
     </row>
     <row r="14" spans="1:40" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1355" t="s">
+      <c r="A14" s="1357" t="s">
         <v>576</v>
       </c>
-      <c r="B14" s="1356"/>
-      <c r="C14" s="1356"/>
-      <c r="D14" s="1356"/>
-      <c r="E14" s="1356"/>
-      <c r="F14" s="1356"/>
-      <c r="G14" s="1356"/>
-      <c r="H14" s="1356"/>
-      <c r="I14" s="1356"/>
-      <c r="J14" s="1356"/>
-      <c r="K14" s="1356"/>
-      <c r="L14" s="1357"/>
+      <c r="B14" s="1358"/>
+      <c r="C14" s="1358"/>
+      <c r="D14" s="1358"/>
+      <c r="E14" s="1358"/>
+      <c r="F14" s="1358"/>
+      <c r="G14" s="1358"/>
+      <c r="H14" s="1358"/>
+      <c r="I14" s="1358"/>
+      <c r="J14" s="1358"/>
+      <c r="K14" s="1358"/>
+      <c r="L14" s="1359"/>
       <c r="M14" s="1102"/>
       <c r="Z14" s="720"/>
       <c r="AA14" s="719"/>
@@ -21794,20 +21797,20 @@
       <c r="AN14" s="722"/>
     </row>
     <row r="15" spans="1:40" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1358" t="s">
+      <c r="A15" s="1360" t="s">
         <v>535</v>
       </c>
-      <c r="B15" s="1359"/>
-      <c r="C15" s="1359"/>
-      <c r="D15" s="1359"/>
-      <c r="E15" s="1359"/>
-      <c r="F15" s="1359"/>
-      <c r="G15" s="1359"/>
-      <c r="H15" s="1359"/>
-      <c r="I15" s="1359"/>
-      <c r="J15" s="1359"/>
-      <c r="K15" s="1359"/>
-      <c r="L15" s="1360"/>
+      <c r="B15" s="1361"/>
+      <c r="C15" s="1361"/>
+      <c r="D15" s="1361"/>
+      <c r="E15" s="1361"/>
+      <c r="F15" s="1361"/>
+      <c r="G15" s="1361"/>
+      <c r="H15" s="1361"/>
+      <c r="I15" s="1361"/>
+      <c r="J15" s="1361"/>
+      <c r="K15" s="1361"/>
+      <c r="L15" s="1362"/>
       <c r="M15" s="1102"/>
       <c r="N15" s="1102"/>
       <c r="Z15" s="720"/>
@@ -21858,20 +21861,20 @@
       <c r="AN16" s="722"/>
     </row>
     <row r="17" spans="1:40" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1361" t="s">
+      <c r="A17" s="1363" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1362"/>
-      <c r="C17" s="1362"/>
-      <c r="D17" s="1362"/>
-      <c r="E17" s="1362"/>
-      <c r="F17" s="1362"/>
-      <c r="G17" s="1362"/>
-      <c r="H17" s="1362"/>
-      <c r="I17" s="1362"/>
-      <c r="J17" s="1362"/>
-      <c r="K17" s="1362"/>
-      <c r="L17" s="1363"/>
+      <c r="B17" s="1364"/>
+      <c r="C17" s="1364"/>
+      <c r="D17" s="1364"/>
+      <c r="E17" s="1364"/>
+      <c r="F17" s="1364"/>
+      <c r="G17" s="1364"/>
+      <c r="H17" s="1364"/>
+      <c r="I17" s="1364"/>
+      <c r="J17" s="1364"/>
+      <c r="K17" s="1364"/>
+      <c r="L17" s="1365"/>
       <c r="N17" s="1102"/>
       <c r="Z17" s="475"/>
       <c r="AI17" s="475"/>
@@ -22219,10 +22222,10 @@
       <c r="J26" s="330"/>
       <c r="K26" s="478"/>
       <c r="L26" s="972"/>
-      <c r="N26" s="1366" t="s">
+      <c r="N26" s="1331" t="s">
         <v>49</v>
       </c>
-      <c r="O26" s="1367"/>
+      <c r="O26" s="1332"/>
       <c r="Y26" s="1104"/>
       <c r="Z26" s="475"/>
       <c r="AA26" s="1104"/>
@@ -22487,11 +22490,11 @@
       <c r="D32" s="1126"/>
       <c r="E32" s="1126"/>
       <c r="F32" s="1127"/>
-      <c r="G32" s="1385">
+      <c r="G32" s="1353">
         <f>DATOS!F41</f>
         <v>0</v>
       </c>
-      <c r="H32" s="1385"/>
+      <c r="H32" s="1353"/>
       <c r="I32" s="991"/>
       <c r="J32" s="330"/>
       <c r="K32" s="478"/>
@@ -22583,13 +22586,13 @@
       <c r="AN34" s="722"/>
     </row>
     <row r="35" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1339" t="s">
+      <c r="A35" s="1349" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="1339"/>
-      <c r="C35" s="1339"/>
-      <c r="D35" s="1339"/>
-      <c r="E35" s="1339"/>
+      <c r="B35" s="1349"/>
+      <c r="C35" s="1349"/>
+      <c r="D35" s="1349"/>
+      <c r="E35" s="1349"/>
       <c r="F35" s="1082">
         <v>1</v>
       </c>
@@ -22602,9 +22605,9 @@
       <c r="I35" s="1082">
         <v>4</v>
       </c>
-      <c r="J35" s="1352"/>
-      <c r="K35" s="1352"/>
-      <c r="L35" s="1352"/>
+      <c r="J35" s="1354"/>
+      <c r="K35" s="1354"/>
+      <c r="L35" s="1354"/>
       <c r="M35" s="1102"/>
       <c r="N35" s="994"/>
       <c r="Y35" s="475"/>
@@ -22625,13 +22628,13 @@
       <c r="AN35" s="722"/>
     </row>
     <row r="36" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1339" t="s">
+      <c r="A36" s="1349" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="1339"/>
-      <c r="C36" s="1339"/>
-      <c r="D36" s="1339"/>
-      <c r="E36" s="1339"/>
+      <c r="B36" s="1349"/>
+      <c r="C36" s="1349"/>
+      <c r="D36" s="1349"/>
+      <c r="E36" s="1349"/>
       <c r="F36" s="1083">
         <f>+DATOS!F15</f>
         <v>5</v>
@@ -22648,9 +22651,9 @@
         <f>+DATOS!L15</f>
         <v>5</v>
       </c>
-      <c r="J36" s="1352"/>
-      <c r="K36" s="1352"/>
-      <c r="L36" s="1352"/>
+      <c r="J36" s="1354"/>
+      <c r="K36" s="1354"/>
+      <c r="L36" s="1354"/>
       <c r="M36" s="1102"/>
       <c r="N36" s="995"/>
       <c r="Y36" s="475"/>
@@ -22671,13 +22674,13 @@
       <c r="AN36" s="722"/>
     </row>
     <row r="37" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1339" t="s">
+      <c r="A37" s="1349" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="1339"/>
-      <c r="C37" s="1339"/>
-      <c r="D37" s="1339"/>
-      <c r="E37" s="1339"/>
+      <c r="B37" s="1349"/>
+      <c r="C37" s="1349"/>
+      <c r="D37" s="1349"/>
+      <c r="E37" s="1349"/>
       <c r="F37" s="1083">
         <f>+DATOS!F16</f>
         <v>0</v>
@@ -22694,9 +22697,9 @@
         <f>+DATOS!L16</f>
         <v>0</v>
       </c>
-      <c r="J37" s="1352"/>
-      <c r="K37" s="1352"/>
-      <c r="L37" s="1352"/>
+      <c r="J37" s="1354"/>
+      <c r="K37" s="1354"/>
+      <c r="L37" s="1354"/>
       <c r="M37" s="1107"/>
       <c r="N37" s="995"/>
       <c r="Y37" s="475"/>
@@ -22717,13 +22720,13 @@
       <c r="AN37" s="722"/>
     </row>
     <row r="38" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1339" t="s">
+      <c r="A38" s="1349" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="1339"/>
-      <c r="C38" s="1339"/>
-      <c r="D38" s="1339"/>
-      <c r="E38" s="1339"/>
+      <c r="B38" s="1349"/>
+      <c r="C38" s="1349"/>
+      <c r="D38" s="1349"/>
+      <c r="E38" s="1349"/>
       <c r="F38" s="1085" t="e">
         <f>+DATOS!F21</f>
         <v>#DIV/0!</v>
@@ -22740,9 +22743,9 @@
         <f>+DATOS!L21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J38" s="1352"/>
-      <c r="K38" s="1352"/>
-      <c r="L38" s="1352"/>
+      <c r="J38" s="1354"/>
+      <c r="K38" s="1354"/>
+      <c r="L38" s="1354"/>
       <c r="M38" s="1102"/>
       <c r="N38" s="1102"/>
       <c r="V38" s="718"/>
@@ -22802,13 +22805,13 @@
       <c r="AN39" s="722"/>
     </row>
     <row r="40" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1339" t="s">
+      <c r="A40" s="1349" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="1339"/>
-      <c r="C40" s="1339"/>
-      <c r="D40" s="1339"/>
-      <c r="E40" s="1339"/>
+      <c r="B40" s="1349"/>
+      <c r="C40" s="1349"/>
+      <c r="D40" s="1349"/>
+      <c r="E40" s="1349"/>
       <c r="F40" s="1088" t="e">
         <f>+DATOS!F31</f>
         <v>#DIV/0!</v>
@@ -22825,9 +22828,9 @@
         <f>+DATOS!L31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="1382"/>
-      <c r="K40" s="1383"/>
-      <c r="L40" s="1384"/>
+      <c r="J40" s="1350"/>
+      <c r="K40" s="1351"/>
+      <c r="L40" s="1352"/>
       <c r="M40" s="1108"/>
       <c r="N40" s="1102"/>
       <c r="Q40" s="1109"/>
@@ -22852,13 +22855,13 @@
       <c r="AN40" s="722"/>
     </row>
     <row r="41" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1339" t="s">
+      <c r="A41" s="1349" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="1339"/>
-      <c r="C41" s="1339"/>
-      <c r="D41" s="1339"/>
-      <c r="E41" s="1339"/>
+      <c r="B41" s="1349"/>
+      <c r="C41" s="1349"/>
+      <c r="D41" s="1349"/>
+      <c r="E41" s="1349"/>
       <c r="F41" s="1085" t="e">
         <f>+DATOS!F32</f>
         <v>#DIV/0!</v>
@@ -22875,9 +22878,9 @@
         <f>+DATOS!L32</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="1382"/>
-      <c r="K41" s="1383"/>
-      <c r="L41" s="1384"/>
+      <c r="J41" s="1350"/>
+      <c r="K41" s="1351"/>
+      <c r="L41" s="1352"/>
       <c r="M41" s="1110"/>
       <c r="N41" s="1102"/>
       <c r="V41" s="718"/>
@@ -22924,9 +22927,9 @@
         <f>+DATOS!L33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J42" s="1382"/>
-      <c r="K42" s="1383"/>
-      <c r="L42" s="1384"/>
+      <c r="J42" s="1350"/>
+      <c r="K42" s="1351"/>
+      <c r="L42" s="1352"/>
       <c r="M42" s="1110"/>
       <c r="N42" s="1102"/>
       <c r="V42" s="718"/>
@@ -22994,16 +22997,16 @@
       <c r="G44" s="480"/>
       <c r="H44" s="407"/>
       <c r="I44" s="997"/>
-      <c r="J44" s="1340" t="s">
+      <c r="J44" s="1367" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="1341"/>
-      <c r="L44" s="1342"/>
+      <c r="K44" s="1368"/>
+      <c r="L44" s="1369"/>
       <c r="M44" s="1102"/>
-      <c r="N44" s="1368" t="s">
+      <c r="N44" s="1333" t="s">
         <v>38</v>
       </c>
-      <c r="O44" s="1368"/>
+      <c r="O44" s="1333"/>
       <c r="V44" s="718"/>
       <c r="W44" s="475"/>
       <c r="X44" s="475"/>
@@ -23034,12 +23037,12 @@
       <c r="G45" s="480"/>
       <c r="H45" s="407"/>
       <c r="I45" s="997"/>
-      <c r="J45" s="1343" t="e">
+      <c r="J45" s="1370" t="e">
         <f>+DATOS!C50</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K45" s="1344"/>
-      <c r="L45" s="1345"/>
+      <c r="K45" s="1371"/>
+      <c r="L45" s="1372"/>
       <c r="M45" s="1102"/>
       <c r="N45" s="680">
         <v>0</v>
@@ -23078,11 +23081,11 @@
       <c r="G46" s="480"/>
       <c r="H46" s="407"/>
       <c r="I46" s="997"/>
-      <c r="J46" s="1369" t="s">
+      <c r="J46" s="1334" t="s">
         <v>36</v>
       </c>
-      <c r="K46" s="1370"/>
-      <c r="L46" s="1371"/>
+      <c r="K46" s="1335"/>
+      <c r="L46" s="1336"/>
       <c r="M46" s="1102"/>
       <c r="N46" s="680" t="e">
         <f>+DATOS!J75</f>
@@ -23122,12 +23125,12 @@
       <c r="G47" s="480"/>
       <c r="H47" s="480"/>
       <c r="I47" s="997"/>
-      <c r="J47" s="1372" t="e">
+      <c r="J47" s="1337" t="e">
         <f>MROUND(N52,0.02)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K47" s="1373"/>
-      <c r="L47" s="1374"/>
+      <c r="K47" s="1338"/>
+      <c r="L47" s="1339"/>
       <c r="M47" s="1102" t="s">
         <v>574</v>
       </c>
@@ -23168,11 +23171,11 @@
       <c r="G48" s="480"/>
       <c r="H48" s="480"/>
       <c r="I48" s="997"/>
-      <c r="J48" s="1346" t="s">
+      <c r="J48" s="1373" t="s">
         <v>37</v>
       </c>
-      <c r="K48" s="1347"/>
-      <c r="L48" s="1348"/>
+      <c r="K48" s="1374"/>
+      <c r="L48" s="1375"/>
       <c r="M48" s="1102"/>
       <c r="N48" s="728"/>
       <c r="O48" s="728"/>
@@ -23207,14 +23210,14 @@
       <c r="G49" s="480"/>
       <c r="H49" s="480"/>
       <c r="I49" s="997"/>
-      <c r="J49" s="1349"/>
-      <c r="K49" s="1350"/>
-      <c r="L49" s="1351"/>
+      <c r="J49" s="1376"/>
+      <c r="K49" s="1377"/>
+      <c r="L49" s="1378"/>
       <c r="M49" s="1102"/>
-      <c r="N49" s="1368" t="s">
+      <c r="N49" s="1333" t="s">
         <v>571</v>
       </c>
-      <c r="O49" s="1368"/>
+      <c r="O49" s="1333"/>
       <c r="S49" s="348"/>
       <c r="V49" s="718"/>
       <c r="W49" s="475"/>
@@ -23246,12 +23249,12 @@
       <c r="G50" s="480"/>
       <c r="H50" s="480"/>
       <c r="I50" s="997"/>
-      <c r="J50" s="1375" t="e">
+      <c r="J50" s="1341" t="e">
         <f>+DATOS!J74</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K50" s="1376"/>
-      <c r="L50" s="1377"/>
+      <c r="K50" s="1342"/>
+      <c r="L50" s="1343"/>
       <c r="M50" s="1108"/>
       <c r="N50" s="987">
         <v>0</v>
@@ -23290,9 +23293,9 @@
       <c r="G51" s="480"/>
       <c r="H51" s="480"/>
       <c r="I51" s="997"/>
-      <c r="J51" s="1378"/>
-      <c r="K51" s="1379"/>
-      <c r="L51" s="1380"/>
+      <c r="J51" s="1344"/>
+      <c r="K51" s="1345"/>
+      <c r="L51" s="1346"/>
       <c r="M51" s="1102"/>
       <c r="N51" s="680" t="e">
         <f>+N46*9.8066</f>
@@ -23589,9 +23592,9 @@
       <c r="G60" s="480"/>
       <c r="H60" s="480"/>
       <c r="I60" s="997"/>
-      <c r="J60" s="1332"/>
-      <c r="K60" s="1332"/>
-      <c r="L60" s="1332"/>
+      <c r="J60" s="1340"/>
+      <c r="K60" s="1340"/>
+      <c r="L60" s="1340"/>
       <c r="M60" s="1102"/>
       <c r="Q60" s="1000"/>
       <c r="R60" s="1000"/>
@@ -23627,9 +23630,9 @@
       <c r="G61" s="480"/>
       <c r="H61" s="480"/>
       <c r="I61" s="997"/>
-      <c r="J61" s="1331"/>
-      <c r="K61" s="1331"/>
-      <c r="L61" s="1331"/>
+      <c r="J61" s="1379"/>
+      <c r="K61" s="1379"/>
+      <c r="L61" s="1379"/>
       <c r="M61" s="1102"/>
       <c r="Q61" s="1001"/>
       <c r="R61" s="1001"/>
@@ -23665,9 +23668,9 @@
       <c r="G62" s="480"/>
       <c r="H62" s="480"/>
       <c r="I62" s="997"/>
-      <c r="J62" s="1332"/>
-      <c r="K62" s="1332"/>
-      <c r="L62" s="1332"/>
+      <c r="J62" s="1340"/>
+      <c r="K62" s="1340"/>
+      <c r="L62" s="1340"/>
       <c r="M62" s="1102"/>
       <c r="P62" s="1000"/>
       <c r="Q62" s="1000"/>
@@ -23809,11 +23812,11 @@
       <c r="C66" s="1115"/>
       <c r="D66" s="478"/>
       <c r="E66" s="478"/>
-      <c r="F66" s="1333">
+      <c r="F66" s="1380">
         <f>+formato!C36</f>
         <v>0</v>
       </c>
-      <c r="G66" s="1333"/>
+      <c r="G66" s="1380"/>
       <c r="H66" s="478"/>
       <c r="I66" s="378"/>
       <c r="J66" s="478"/>
@@ -23847,11 +23850,11 @@
       <c r="C67" s="1115"/>
       <c r="D67" s="478"/>
       <c r="E67" s="478"/>
-      <c r="F67" s="1334">
+      <c r="F67" s="1381">
         <f>+formato!C37</f>
         <v>0</v>
       </c>
-      <c r="G67" s="1334"/>
+      <c r="G67" s="1381"/>
       <c r="H67" s="478"/>
       <c r="I67" s="378"/>
       <c r="J67" s="1116"/>
@@ -23885,11 +23888,11 @@
       <c r="C68" s="1115"/>
       <c r="D68" s="478"/>
       <c r="E68" s="478"/>
-      <c r="F68" s="1333">
+      <c r="F68" s="1380">
         <f>+formato!C38</f>
         <v>0</v>
       </c>
-      <c r="G68" s="1333"/>
+      <c r="G68" s="1380"/>
       <c r="H68" s="478"/>
       <c r="I68" s="1117"/>
       <c r="J68" s="1116"/>
@@ -24106,11 +24109,11 @@
       <c r="G74" s="1014" t="s">
         <v>67</v>
       </c>
-      <c r="H74" s="1335">
+      <c r="H74" s="1382">
         <f>DATOS!F37</f>
         <v>0</v>
       </c>
-      <c r="I74" s="1336"/>
+      <c r="I74" s="1383"/>
       <c r="J74" s="1116"/>
       <c r="K74" s="478"/>
       <c r="L74" s="478"/>
@@ -24151,11 +24154,11 @@
       <c r="G75" s="1014" t="s">
         <v>67</v>
       </c>
-      <c r="H75" s="1337">
+      <c r="H75" s="1384">
         <f>DATOS!F38</f>
         <v>0</v>
       </c>
-      <c r="I75" s="1338"/>
+      <c r="I75" s="1385"/>
       <c r="J75" s="1116"/>
       <c r="K75" s="478"/>
       <c r="L75" s="478"/>
@@ -24220,18 +24223,18 @@
       <c r="AN76" s="722"/>
     </row>
     <row r="77" spans="1:40" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1381"/>
-      <c r="B77" s="1381"/>
-      <c r="C77" s="1381"/>
-      <c r="D77" s="1381"/>
-      <c r="E77" s="1381"/>
-      <c r="F77" s="1381"/>
-      <c r="G77" s="1381"/>
-      <c r="H77" s="1381"/>
-      <c r="I77" s="1381"/>
-      <c r="J77" s="1381"/>
-      <c r="K77" s="1381"/>
-      <c r="L77" s="1381"/>
+      <c r="A77" s="1348"/>
+      <c r="B77" s="1348"/>
+      <c r="C77" s="1348"/>
+      <c r="D77" s="1348"/>
+      <c r="E77" s="1348"/>
+      <c r="F77" s="1348"/>
+      <c r="G77" s="1348"/>
+      <c r="H77" s="1348"/>
+      <c r="I77" s="1348"/>
+      <c r="J77" s="1348"/>
+      <c r="K77" s="1348"/>
+      <c r="L77" s="1348"/>
       <c r="V77" s="718"/>
       <c r="W77" s="475"/>
       <c r="X77" s="475"/>
@@ -24364,20 +24367,20 @@
       <c r="AN80" s="722"/>
     </row>
     <row r="81" spans="1:40" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1330" t="s">
+      <c r="A81" s="1347" t="s">
         <v>73</v>
       </c>
-      <c r="B81" s="1330"/>
-      <c r="C81" s="1330"/>
-      <c r="D81" s="1330"/>
-      <c r="E81" s="1330"/>
-      <c r="F81" s="1330"/>
-      <c r="G81" s="1330"/>
-      <c r="H81" s="1330"/>
-      <c r="I81" s="1330"/>
-      <c r="J81" s="1330"/>
-      <c r="K81" s="1330"/>
-      <c r="L81" s="1330"/>
+      <c r="B81" s="1347"/>
+      <c r="C81" s="1347"/>
+      <c r="D81" s="1347"/>
+      <c r="E81" s="1347"/>
+      <c r="F81" s="1347"/>
+      <c r="G81" s="1347"/>
+      <c r="H81" s="1347"/>
+      <c r="I81" s="1347"/>
+      <c r="J81" s="1347"/>
+      <c r="K81" s="1347"/>
+      <c r="L81" s="1347"/>
       <c r="M81" s="1017"/>
       <c r="N81" s="1017"/>
       <c r="V81" s="718"/>
@@ -24438,20 +24441,20 @@
       <c r="AN82" s="722"/>
     </row>
     <row r="83" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1330" t="s">
+      <c r="A83" s="1347" t="s">
         <v>537</v>
       </c>
-      <c r="B83" s="1330"/>
-      <c r="C83" s="1330"/>
-      <c r="D83" s="1330"/>
-      <c r="E83" s="1330"/>
-      <c r="F83" s="1330"/>
-      <c r="G83" s="1330"/>
-      <c r="H83" s="1330"/>
-      <c r="I83" s="1330"/>
-      <c r="J83" s="1330"/>
-      <c r="K83" s="1330"/>
-      <c r="L83" s="1330"/>
+      <c r="B83" s="1347"/>
+      <c r="C83" s="1347"/>
+      <c r="D83" s="1347"/>
+      <c r="E83" s="1347"/>
+      <c r="F83" s="1347"/>
+      <c r="G83" s="1347"/>
+      <c r="H83" s="1347"/>
+      <c r="I83" s="1347"/>
+      <c r="J83" s="1347"/>
+      <c r="K83" s="1347"/>
+      <c r="L83" s="1347"/>
       <c r="M83" s="1120"/>
       <c r="N83" s="1120"/>
       <c r="V83" s="718"/>
@@ -24547,18 +24550,18 @@
       <c r="AN85" s="722"/>
     </row>
     <row r="86" spans="1:40" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1365"/>
-      <c r="B86" s="1365"/>
-      <c r="C86" s="1365"/>
-      <c r="D86" s="1365"/>
-      <c r="E86" s="1365"/>
-      <c r="F86" s="1365"/>
-      <c r="G86" s="1365"/>
-      <c r="H86" s="1365"/>
-      <c r="I86" s="1365"/>
-      <c r="J86" s="1365"/>
-      <c r="K86" s="1365"/>
-      <c r="L86" s="1365"/>
+      <c r="A86" s="1330"/>
+      <c r="B86" s="1330"/>
+      <c r="C86" s="1330"/>
+      <c r="D86" s="1330"/>
+      <c r="E86" s="1330"/>
+      <c r="F86" s="1330"/>
+      <c r="G86" s="1330"/>
+      <c r="H86" s="1330"/>
+      <c r="I86" s="1330"/>
+      <c r="J86" s="1330"/>
+      <c r="K86" s="1330"/>
+      <c r="L86" s="1330"/>
       <c r="M86" s="1120"/>
       <c r="N86" s="1120"/>
       <c r="V86" s="718"/>
@@ -25852,6 +25855,34 @@
     <protectedRange sqref="E9:E10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="44">
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="J48:L49"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:I12"/>
     <mergeCell ref="A86:L86"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="N44:O44"/>
@@ -25868,34 +25899,6 @@
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="J40:L40"/>
     <mergeCell ref="J38:L38"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="J48:L49"/>
-    <mergeCell ref="A81:L81"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.70866141732283472" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -25938,40 +25941,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1392" t="s">
+      <c r="B2" s="1404" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1393"/>
-      <c r="D2" s="1393"/>
-      <c r="E2" s="1393"/>
-      <c r="F2" s="1393"/>
-      <c r="G2" s="1393"/>
-      <c r="H2" s="1393"/>
-      <c r="I2" s="1393"/>
-      <c r="J2" s="1393"/>
-      <c r="K2" s="1393"/>
-      <c r="L2" s="1393"/>
-      <c r="M2" s="1393"/>
-      <c r="N2" s="1393"/>
-      <c r="O2" s="1394"/>
+      <c r="C2" s="1405"/>
+      <c r="D2" s="1405"/>
+      <c r="E2" s="1405"/>
+      <c r="F2" s="1405"/>
+      <c r="G2" s="1405"/>
+      <c r="H2" s="1405"/>
+      <c r="I2" s="1405"/>
+      <c r="J2" s="1405"/>
+      <c r="K2" s="1405"/>
+      <c r="L2" s="1405"/>
+      <c r="M2" s="1405"/>
+      <c r="N2" s="1405"/>
+      <c r="O2" s="1406"/>
     </row>
     <row r="3" spans="2:19" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1395" t="s">
+      <c r="B3" s="1407" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1396"/>
-      <c r="D3" s="1396"/>
-      <c r="E3" s="1396"/>
-      <c r="F3" s="1396"/>
-      <c r="G3" s="1396"/>
-      <c r="H3" s="1396"/>
-      <c r="I3" s="1396"/>
-      <c r="J3" s="1396"/>
-      <c r="K3" s="1396"/>
-      <c r="L3" s="1396"/>
-      <c r="M3" s="1396"/>
-      <c r="N3" s="1396"/>
-      <c r="O3" s="1397"/>
+      <c r="C3" s="1408"/>
+      <c r="D3" s="1408"/>
+      <c r="E3" s="1408"/>
+      <c r="F3" s="1408"/>
+      <c r="G3" s="1408"/>
+      <c r="H3" s="1408"/>
+      <c r="I3" s="1408"/>
+      <c r="J3" s="1408"/>
+      <c r="K3" s="1408"/>
+      <c r="L3" s="1408"/>
+      <c r="M3" s="1408"/>
+      <c r="N3" s="1408"/>
+      <c r="O3" s="1409"/>
     </row>
     <row r="5" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="682" t="s">
@@ -26161,31 +26164,31 @@
       <c r="N11" s="494"/>
     </row>
     <row r="12" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1386" t="s">
+      <c r="B12" s="1400" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="1386"/>
-      <c r="D12" s="1386"/>
-      <c r="E12" s="1386">
+      <c r="C12" s="1400"/>
+      <c r="D12" s="1400"/>
+      <c r="E12" s="1400">
         <v>1</v>
       </c>
-      <c r="F12" s="1386"/>
-      <c r="G12" s="1386">
+      <c r="F12" s="1400"/>
+      <c r="G12" s="1400">
         <v>2</v>
       </c>
-      <c r="H12" s="1386"/>
-      <c r="I12" s="1386">
+      <c r="H12" s="1400"/>
+      <c r="I12" s="1400">
         <v>3</v>
       </c>
-      <c r="J12" s="1386"/>
-      <c r="K12" s="1386">
+      <c r="J12" s="1400"/>
+      <c r="K12" s="1400">
         <v>4</v>
       </c>
-      <c r="L12" s="1386"/>
-      <c r="M12" s="1386">
+      <c r="L12" s="1400"/>
+      <c r="M12" s="1400">
         <v>5</v>
       </c>
-      <c r="N12" s="1386"/>
+      <c r="N12" s="1400"/>
       <c r="Q12" s="1139" t="s">
         <v>586</v>
       </c>
@@ -26197,9 +26200,9 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1386"/>
-      <c r="C13" s="1386"/>
-      <c r="D13" s="1386"/>
+      <c r="B13" s="1400"/>
+      <c r="C13" s="1400"/>
+      <c r="D13" s="1400"/>
       <c r="E13" s="730" t="s">
         <v>88</v>
       </c>
@@ -26233,19 +26236,19 @@
       <c r="Q13" s="1138">
         <v>46112</v>
       </c>
-      <c r="R13" s="1138">
-        <v>46043</v>
+      <c r="R13" s="1138" t="s">
+        <v>666</v>
       </c>
       <c r="S13" s="1137" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="14" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1398" t="s">
+      <c r="B14" s="1394" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1398"/>
-      <c r="D14" s="1399"/>
+      <c r="C14" s="1394"/>
+      <c r="D14" s="1395"/>
       <c r="E14" s="1256">
         <v>1</v>
       </c>
@@ -26271,11 +26274,11 @@
       </c>
     </row>
     <row r="15" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1387" t="s">
+      <c r="B15" s="1389" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="1387"/>
-      <c r="D15" s="1388"/>
+      <c r="C15" s="1389"/>
+      <c r="D15" s="1390"/>
       <c r="E15" s="1140">
         <v>5</v>
       </c>
@@ -26320,11 +26323,11 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1387" t="s">
+      <c r="B16" s="1389" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="1387"/>
-      <c r="D16" s="1388"/>
+      <c r="C16" s="1389"/>
+      <c r="D16" s="1390"/>
       <c r="E16" s="1140">
         <f>+formato!D17</f>
         <v>0</v>
@@ -26363,18 +26366,18 @@
         <v>6819</v>
       </c>
       <c r="R16" s="1160">
-        <v>3899.2</v>
+        <v>3876</v>
       </c>
       <c r="S16" s="1137" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="17" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="1387" t="s">
+      <c r="B17" s="1389" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="1387"/>
-      <c r="D17" s="1388"/>
+      <c r="C17" s="1389"/>
+      <c r="D17" s="1390"/>
       <c r="E17" s="1140">
         <f>+formato!D18</f>
         <v>0</v>
@@ -26413,18 +26416,18 @@
         <v>2130</v>
       </c>
       <c r="R17" s="1160">
-        <v>939.32</v>
+        <v>940</v>
       </c>
       <c r="S17" s="1137" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="18" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1387" t="s">
+      <c r="B18" s="1389" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="1387"/>
-      <c r="D18" s="1388"/>
+      <c r="C18" s="1389"/>
+      <c r="D18" s="1390"/>
       <c r="E18" s="1140">
         <f>+formato!D19</f>
         <v>0</v>
@@ -26461,11 +26464,11 @@
       <c r="N18" s="1146"/>
     </row>
     <row r="19" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="1388" t="s">
+      <c r="B19" s="1390" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1409"/>
-      <c r="D19" s="1409"/>
+      <c r="C19" s="1391"/>
+      <c r="D19" s="1391"/>
       <c r="E19" s="1143">
         <f t="shared" ref="E19:K19" si="0">+E17-E18</f>
         <v>0</v>
@@ -26502,11 +26505,11 @@
       <c r="N19" s="1146"/>
     </row>
     <row r="20" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="1387" t="s">
+      <c r="B20" s="1389" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="1387"/>
-      <c r="D20" s="1388"/>
+      <c r="C20" s="1389"/>
+      <c r="D20" s="1390"/>
       <c r="E20" s="1140">
         <f>+formato!D21</f>
         <v>0</v>
@@ -26556,11 +26559,11 @@
       <c r="U20" s="948"/>
     </row>
     <row r="21" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="1410" t="s">
+      <c r="B21" s="1392" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="1410"/>
-      <c r="D21" s="1411"/>
+      <c r="C21" s="1392"/>
+      <c r="D21" s="1393"/>
       <c r="E21" s="1143" t="e">
         <f t="shared" ref="E21:K21" si="1">+E19/E20</f>
         <v>#DIV/0!</v>
@@ -26641,11 +26644,11 @@
       <c r="U22" s="950"/>
     </row>
     <row r="23" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="1398" t="s">
+      <c r="B23" s="1394" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="1398"/>
-      <c r="D23" s="1399"/>
+      <c r="C23" s="1394"/>
+      <c r="D23" s="1395"/>
       <c r="E23" s="1140">
         <f>+formato!D24</f>
         <v>0</v>
@@ -26684,11 +26687,11 @@
       <c r="U23" s="953"/>
     </row>
     <row r="24" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="1387" t="s">
+      <c r="B24" s="1389" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="1387"/>
-      <c r="D24" s="1388"/>
+      <c r="C24" s="1389"/>
+      <c r="D24" s="1390"/>
       <c r="E24" s="1140">
         <f>+formato!D25</f>
         <v>0</v>
@@ -26744,11 +26747,11 @@
       </c>
     </row>
     <row r="25" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="1387" t="s">
+      <c r="B25" s="1389" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="1387"/>
-      <c r="D25" s="1388"/>
+      <c r="C25" s="1389"/>
+      <c r="D25" s="1390"/>
       <c r="E25" s="1140">
         <f>+formato!D26</f>
         <v>0</v>
@@ -26800,11 +26803,11 @@
       </c>
     </row>
     <row r="26" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="1387" t="s">
+      <c r="B26" s="1389" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="1387"/>
-      <c r="D26" s="1388"/>
+      <c r="C26" s="1389"/>
+      <c r="D26" s="1390"/>
       <c r="E26" s="1140">
         <f>+formato!D27</f>
         <v>0</v>
@@ -26860,11 +26863,11 @@
       </c>
     </row>
     <row r="27" spans="2:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="1387" t="s">
+      <c r="B27" s="1389" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="1387"/>
-      <c r="D27" s="1388"/>
+      <c r="C27" s="1389"/>
+      <c r="D27" s="1390"/>
       <c r="E27" s="1140">
         <f>+formato!D28</f>
         <v>0</v>
@@ -26908,11 +26911,11 @@
       </c>
     </row>
     <row r="28" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="1387" t="s">
+      <c r="B28" s="1389" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="1387"/>
-      <c r="D28" s="1388"/>
+      <c r="C28" s="1389"/>
+      <c r="D28" s="1390"/>
       <c r="E28" s="1156">
         <f t="shared" ref="E28:L28" si="6">+E24-E27</f>
         <v>0</v>
@@ -26949,11 +26952,11 @@
       <c r="N28" s="1146"/>
     </row>
     <row r="29" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="1387" t="s">
+      <c r="B29" s="1389" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="1387"/>
-      <c r="D29" s="1388"/>
+      <c r="C29" s="1389"/>
+      <c r="D29" s="1390"/>
       <c r="E29" s="1140">
         <f>+formato!D30</f>
         <v>0</v>
@@ -26990,11 +26993,11 @@
       <c r="N29" s="1146"/>
     </row>
     <row r="30" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="1388" t="s">
+      <c r="B30" s="1390" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="1409"/>
-      <c r="D30" s="1409"/>
+      <c r="C30" s="1391"/>
+      <c r="D30" s="1391"/>
       <c r="E30" s="1143"/>
       <c r="F30" s="1143" t="e">
         <f t="shared" ref="F30:L30" si="7">+F27-F29</f>
@@ -27019,11 +27022,11 @@
       <c r="N30" s="1146"/>
     </row>
     <row r="31" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="1388" t="s">
+      <c r="B31" s="1390" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="1409"/>
-      <c r="D31" s="1409"/>
+      <c r="C31" s="1391"/>
+      <c r="D31" s="1391"/>
       <c r="E31" s="1143"/>
       <c r="F31" s="1143" t="e">
         <f t="shared" ref="F31:L31" si="8">+F28/F30*100</f>
@@ -27051,11 +27054,11 @@
       </c>
     </row>
     <row r="32" spans="2:21" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="1411" t="s">
+      <c r="B32" s="1393" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="1412"/>
-      <c r="D32" s="1412"/>
+      <c r="C32" s="1396"/>
+      <c r="D32" s="1396"/>
       <c r="E32" s="1143"/>
       <c r="F32" s="1143" t="e">
         <f t="shared" ref="F32:L32" si="9">+F21/(1+F31/100)</f>
@@ -27181,11 +27184,11 @@
       </c>
       <c r="D37" s="706"/>
       <c r="E37" s="707"/>
-      <c r="F37" s="1403">
+      <c r="F37" s="1397">
         <v>0</v>
       </c>
-      <c r="G37" s="1403"/>
-      <c r="H37" s="1403"/>
+      <c r="G37" s="1397"/>
+      <c r="H37" s="1397"/>
     </row>
     <row r="38" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="678" t="s">
@@ -27193,11 +27196,11 @@
       </c>
       <c r="D38" s="706"/>
       <c r="E38" s="707"/>
-      <c r="F38" s="1404">
+      <c r="F38" s="1398">
         <v>0</v>
       </c>
-      <c r="G38" s="1404"/>
-      <c r="H38" s="1404"/>
+      <c r="G38" s="1398"/>
+      <c r="H38" s="1398"/>
     </row>
     <row r="39" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -27222,17 +27225,17 @@
       </c>
       <c r="D41" s="1029"/>
       <c r="E41" s="1030"/>
-      <c r="F41" s="1405">
+      <c r="F41" s="1399">
         <v>0</v>
       </c>
-      <c r="G41" s="1405"/>
-      <c r="H41" s="1405"/>
-      <c r="K41" s="1402" t="s">
+      <c r="G41" s="1399"/>
+      <c r="H41" s="1399"/>
+      <c r="K41" s="1412" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="1402"/>
+      <c r="L41" s="1412"/>
       <c r="M41" s="478"/>
-      <c r="N41" s="1400" t="s">
+      <c r="N41" s="1410" t="s">
         <v>106</v>
       </c>
     </row>
@@ -27245,7 +27248,7 @@
         <v>52</v>
       </c>
       <c r="M42" s="478"/>
-      <c r="N42" s="1401"/>
+      <c r="N42" s="1411"/>
     </row>
     <row r="43" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1027"/>
@@ -27418,21 +27421,21 @@
     </row>
     <row r="49" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="711"/>
-      <c r="C49" s="1389" t="s">
+      <c r="C49" s="1401" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="1390"/>
-      <c r="E49" s="1391"/>
+      <c r="D49" s="1402"/>
+      <c r="E49" s="1403"/>
       <c r="N49" s="712"/>
     </row>
     <row r="50" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="711"/>
-      <c r="C50" s="1406" t="e">
+      <c r="C50" s="1386" t="e">
         <f>IF(G54="","",IF(AND(G54&lt;=25),"A",IF(AND(G54&gt;25,G53&lt;=25),"B",IF(AND(G53&gt;25,G52&lt;30),"C"))))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D50" s="1407"/>
-      <c r="E50" s="1408"/>
+      <c r="D50" s="1387"/>
+      <c r="E50" s="1388"/>
       <c r="F50" s="475"/>
       <c r="N50" s="712"/>
       <c r="O50" s="713"/>
@@ -29097,23 +29100,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="e49E/OysaywdZI0JcuM+C0cQuCvqe9PMqZ/ilP9GIY/P45QRK0Ai6JyKU7eB4WtZltnkC9BaQI8vpXNlfCIiIw==" saltValue="LOl5Rt57JcvlkUy4kBpOXg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="33">
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B29:D29"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="I12:J12"/>
@@ -29130,6 +29116,23 @@
     <mergeCell ref="N41:N42"/>
     <mergeCell ref="K41:L41"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
   </mergeCells>
   <conditionalFormatting sqref="F34:F35">
     <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="No Cumple">
@@ -29203,16 +29206,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1420"/>
-      <c r="B1" s="1420"/>
-      <c r="C1" s="1420"/>
-      <c r="D1" s="1421" t="s">
+      <c r="A1" s="1421"/>
+      <c r="B1" s="1421"/>
+      <c r="C1" s="1421"/>
+      <c r="D1" s="1422" t="s">
         <v>132</v>
       </c>
-      <c r="E1" s="1421"/>
-      <c r="F1" s="1421"/>
-      <c r="G1" s="1421"/>
-      <c r="H1" s="1421"/>
+      <c r="E1" s="1422"/>
+      <c r="F1" s="1422"/>
+      <c r="G1" s="1422"/>
+      <c r="H1" s="1422"/>
       <c r="I1" s="484" t="s">
         <v>133</v>
       </c>
@@ -29221,14 +29224,14 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1420"/>
-      <c r="B2" s="1420"/>
-      <c r="C2" s="1420"/>
-      <c r="D2" s="1421"/>
-      <c r="E2" s="1421"/>
-      <c r="F2" s="1421"/>
-      <c r="G2" s="1421"/>
-      <c r="H2" s="1421"/>
+      <c r="A2" s="1421"/>
+      <c r="B2" s="1421"/>
+      <c r="C2" s="1421"/>
+      <c r="D2" s="1422"/>
+      <c r="E2" s="1422"/>
+      <c r="F2" s="1422"/>
+      <c r="G2" s="1422"/>
+      <c r="H2" s="1422"/>
       <c r="I2" s="484" t="s">
         <v>135</v>
       </c>
@@ -29237,14 +29240,14 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1420"/>
-      <c r="B3" s="1420"/>
-      <c r="C3" s="1420"/>
-      <c r="D3" s="1421"/>
-      <c r="E3" s="1421"/>
-      <c r="F3" s="1421"/>
-      <c r="G3" s="1421"/>
-      <c r="H3" s="1421"/>
+      <c r="A3" s="1421"/>
+      <c r="B3" s="1421"/>
+      <c r="C3" s="1421"/>
+      <c r="D3" s="1422"/>
+      <c r="E3" s="1422"/>
+      <c r="F3" s="1422"/>
+      <c r="G3" s="1422"/>
+      <c r="H3" s="1422"/>
       <c r="I3" s="484" t="s">
         <v>136</v>
       </c>
@@ -29253,14 +29256,14 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1420"/>
-      <c r="B4" s="1420"/>
-      <c r="C4" s="1420"/>
-      <c r="D4" s="1421"/>
-      <c r="E4" s="1421"/>
-      <c r="F4" s="1421"/>
-      <c r="G4" s="1421"/>
-      <c r="H4" s="1421"/>
+      <c r="A4" s="1421"/>
+      <c r="B4" s="1421"/>
+      <c r="C4" s="1421"/>
+      <c r="D4" s="1422"/>
+      <c r="E4" s="1422"/>
+      <c r="F4" s="1422"/>
+      <c r="G4" s="1422"/>
+      <c r="H4" s="1422"/>
       <c r="I4" s="484" t="s">
         <v>137</v>
       </c>
@@ -29272,17 +29275,17 @@
       <c r="A6" s="744" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="1416" t="s">
+      <c r="B6" s="1432" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="1417"/>
-      <c r="D6" s="1417"/>
-      <c r="E6" s="1417"/>
-      <c r="F6" s="1417"/>
-      <c r="G6" s="1417"/>
-      <c r="H6" s="1417"/>
-      <c r="I6" s="1417"/>
-      <c r="J6" s="1418"/>
+      <c r="C6" s="1433"/>
+      <c r="D6" s="1433"/>
+      <c r="E6" s="1433"/>
+      <c r="F6" s="1433"/>
+      <c r="G6" s="1433"/>
+      <c r="H6" s="1433"/>
+      <c r="I6" s="1433"/>
+      <c r="J6" s="1434"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="744" t="s">
@@ -29557,9 +29560,9 @@
       <c r="F30" s="470"/>
       <c r="G30" s="471"/>
       <c r="H30" s="470"/>
-      <c r="L30" s="1422"/>
-      <c r="R30" s="1419"/>
-      <c r="S30" s="1419"/>
+      <c r="L30" s="1423"/>
+      <c r="R30" s="1435"/>
+      <c r="S30" s="1435"/>
       <c r="T30" s="674"/>
       <c r="U30" s="675"/>
     </row>
@@ -29572,9 +29575,9 @@
       <c r="F31" s="470"/>
       <c r="G31" s="471"/>
       <c r="H31" s="471"/>
-      <c r="L31" s="1422"/>
-      <c r="R31" s="1419"/>
-      <c r="S31" s="1419"/>
+      <c r="L31" s="1423"/>
+      <c r="R31" s="1435"/>
+      <c r="S31" s="1435"/>
       <c r="T31" s="674"/>
       <c r="U31" s="675"/>
     </row>
@@ -29587,9 +29590,9 @@
       <c r="F32" s="471"/>
       <c r="G32" s="471"/>
       <c r="H32" s="471"/>
-      <c r="L32" s="1422"/>
-      <c r="R32" s="1419"/>
-      <c r="S32" s="1419"/>
+      <c r="L32" s="1423"/>
+      <c r="R32" s="1435"/>
+      <c r="S32" s="1435"/>
       <c r="T32" s="674"/>
       <c r="U32" s="675"/>
     </row>
@@ -29602,10 +29605,10 @@
       <c r="F33" s="471"/>
       <c r="G33" s="471"/>
       <c r="H33" s="471"/>
-      <c r="L33" s="1422"/>
+      <c r="L33" s="1423"/>
       <c r="O33" s="673"/>
-      <c r="R33" s="1419"/>
-      <c r="S33" s="1419"/>
+      <c r="R33" s="1435"/>
+      <c r="S33" s="1435"/>
       <c r="T33" s="488"/>
       <c r="U33" s="675"/>
     </row>
@@ -29620,42 +29623,42 @@
       <c r="H34" s="471"/>
       <c r="I34" s="467"/>
       <c r="J34" s="467"/>
-      <c r="L34" s="1423"/>
-      <c r="M34" s="1423"/>
-      <c r="N34" s="1423"/>
-      <c r="O34" s="1423"/>
-      <c r="P34" s="1423"/>
-      <c r="Q34" s="1423"/>
-      <c r="R34" s="1423"/>
-      <c r="S34" s="1423"/>
-      <c r="T34" s="1423"/>
-      <c r="U34" s="1423"/>
+      <c r="L34" s="1424"/>
+      <c r="M34" s="1424"/>
+      <c r="N34" s="1424"/>
+      <c r="O34" s="1424"/>
+      <c r="P34" s="1424"/>
+      <c r="Q34" s="1424"/>
+      <c r="R34" s="1424"/>
+      <c r="S34" s="1424"/>
+      <c r="T34" s="1424"/>
+      <c r="U34" s="1424"/>
     </row>
     <row r="35" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35"/>
       <c r="F35" s="470"/>
       <c r="I35" s="467"/>
       <c r="J35" s="467"/>
-      <c r="L35" s="1424"/>
-      <c r="M35" s="1424"/>
+      <c r="L35" s="1425"/>
+      <c r="M35" s="1425"/>
       <c r="N35" s="676"/>
-      <c r="P35" s="1425"/>
+      <c r="P35" s="1426"/>
       <c r="Q35" s="676"/>
-      <c r="S35" s="1426"/>
-      <c r="T35" s="1427"/>
-      <c r="U35" s="1427"/>
+      <c r="S35" s="1427"/>
+      <c r="T35" s="1428"/>
+      <c r="U35" s="1428"/>
     </row>
     <row r="36" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I36" s="467"/>
       <c r="J36" s="467"/>
-      <c r="L36" s="1424"/>
-      <c r="M36" s="1424"/>
+      <c r="L36" s="1425"/>
+      <c r="M36" s="1425"/>
       <c r="N36" s="677"/>
-      <c r="P36" s="1426"/>
+      <c r="P36" s="1427"/>
       <c r="Q36" s="677"/>
-      <c r="S36" s="1426"/>
-      <c r="T36" s="1427"/>
-      <c r="U36" s="1427"/>
+      <c r="S36" s="1427"/>
+      <c r="T36" s="1428"/>
+      <c r="U36" s="1428"/>
     </row>
     <row r="37" spans="1:26" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="534" t="s">
@@ -32173,12 +32176,12 @@
       <c r="M74" s="471"/>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A75" s="1415" t="s">
+      <c r="A75" s="1431" t="s">
         <v>192</v>
       </c>
-      <c r="B75" s="1415"/>
-      <c r="C75" s="1415"/>
-      <c r="D75" s="1415"/>
+      <c r="B75" s="1431"/>
+      <c r="C75" s="1431"/>
+      <c r="D75" s="1431"/>
       <c r="E75" s="467"/>
       <c r="F75" s="467"/>
       <c r="G75" s="467"/>
@@ -32188,10 +32191,10 @@
       <c r="M75" s="471"/>
     </row>
     <row r="76" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1414" t="s">
+      <c r="A76" s="1430" t="s">
         <v>193</v>
       </c>
-      <c r="B76" s="1414"/>
+      <c r="B76" s="1430"/>
       <c r="C76" s="641" t="s">
         <v>194</v>
       </c>
@@ -32378,16 +32381,16 @@
       <c r="R87" s="486" t="s">
         <v>202</v>
       </c>
-      <c r="T87" s="1413" t="s">
+      <c r="T87" s="1429" t="s">
         <v>531</v>
       </c>
-      <c r="U87" s="1413"/>
-      <c r="V87" s="1413"/>
-      <c r="W87" s="1413" t="s">
+      <c r="U87" s="1429"/>
+      <c r="V87" s="1429"/>
+      <c r="W87" s="1429" t="s">
         <v>532</v>
       </c>
-      <c r="X87" s="1413"/>
-      <c r="Y87" s="1413"/>
+      <c r="X87" s="1429"/>
+      <c r="Y87" s="1429"/>
     </row>
     <row r="88" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="596" t="s">
@@ -32911,19 +32914,19 @@
       <c r="A100" s="1270" t="s">
         <v>655</v>
       </c>
-      <c r="B100" s="1428" t="s">
+      <c r="B100" s="1413" t="s">
         <v>656</v>
       </c>
-      <c r="C100" s="1429"/>
+      <c r="C100" s="1414"/>
       <c r="D100" s="1271"/>
-      <c r="E100" s="1430" t="s">
+      <c r="E100" s="1415" t="s">
         <v>657</v>
       </c>
-      <c r="F100" s="1430"/>
-      <c r="G100" s="1431" t="s">
+      <c r="F100" s="1415"/>
+      <c r="G100" s="1416" t="s">
         <v>658</v>
       </c>
-      <c r="H100" s="1432"/>
+      <c r="H100" s="1417"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="940"/>
@@ -32939,19 +32942,19 @@
       <c r="A102" s="1272" t="s">
         <v>659</v>
       </c>
-      <c r="B102" s="1433">
+      <c r="B102" s="1418">
         <v>44944</v>
       </c>
-      <c r="C102" s="1434"/>
+      <c r="C102" s="1419"/>
       <c r="D102" s="940"/>
-      <c r="E102" s="1435" t="s">
+      <c r="E102" s="1420" t="s">
         <v>660</v>
       </c>
-      <c r="F102" s="1435"/>
-      <c r="G102" s="1433">
+      <c r="F102" s="1420"/>
+      <c r="G102" s="1418">
         <v>44944</v>
       </c>
-      <c r="H102" s="1434"/>
+      <c r="H102" s="1419"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="940"/>
@@ -32966,12 +32969,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wd0Sk3J/OeT0TxJIAnp4S2dGatByENh6gH5lE7pLCIYYn5xv110dK84OeIJzfd1un3raa/Q0kk7gUzEP+5w5+g==" saltValue="Nxfv9eN1cqS8LPjiSFaCXw==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="T87:V87"/>
+    <mergeCell ref="W87:Y87"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="R30:S33"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:H4"/>
     <mergeCell ref="L30:L33"/>
@@ -32980,12 +32983,12 @@
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="S35:S36"/>
     <mergeCell ref="T35:U36"/>
-    <mergeCell ref="T87:V87"/>
-    <mergeCell ref="W87:Y87"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="R30:S33"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G102:H102"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -34605,18 +34608,18 @@
       <c r="V6" s="365"/>
     </row>
     <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1353" t="s">
+      <c r="A7" s="1355" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1353"/>
-      <c r="C7" s="1353"/>
-      <c r="D7" s="1353"/>
-      <c r="E7" s="1353"/>
-      <c r="F7" s="1353"/>
-      <c r="G7" s="1353"/>
-      <c r="H7" s="1353"/>
-      <c r="I7" s="1353"/>
-      <c r="J7" s="1353"/>
+      <c r="B7" s="1355"/>
+      <c r="C7" s="1355"/>
+      <c r="D7" s="1355"/>
+      <c r="E7" s="1355"/>
+      <c r="F7" s="1355"/>
+      <c r="G7" s="1355"/>
+      <c r="H7" s="1355"/>
+      <c r="I7" s="1355"/>
+      <c r="J7" s="1355"/>
       <c r="L7" s="326"/>
       <c r="M7" s="364"/>
       <c r="N7" s="365"/>
@@ -34630,18 +34633,18 @@
       <c r="V7" s="365"/>
     </row>
     <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1447">
+      <c r="A8" s="1443">
         <v>1</v>
       </c>
-      <c r="B8" s="1447"/>
-      <c r="C8" s="1447"/>
-      <c r="D8" s="1447"/>
-      <c r="E8" s="1447"/>
-      <c r="F8" s="1447"/>
-      <c r="G8" s="1447"/>
-      <c r="H8" s="1447"/>
-      <c r="I8" s="1447"/>
-      <c r="J8" s="1447"/>
+      <c r="B8" s="1443"/>
+      <c r="C8" s="1443"/>
+      <c r="D8" s="1443"/>
+      <c r="E8" s="1443"/>
+      <c r="F8" s="1443"/>
+      <c r="G8" s="1443"/>
+      <c r="H8" s="1443"/>
+      <c r="I8" s="1443"/>
+      <c r="J8" s="1443"/>
       <c r="L8" s="334"/>
       <c r="M8" s="366"/>
       <c r="N8" s="367"/>
@@ -34920,18 +34923,18 @@
       <c r="AL14" s="315"/>
     </row>
     <row r="15" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1448" t="s">
+      <c r="A15" s="1444" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="1449"/>
-      <c r="C15" s="1449"/>
-      <c r="D15" s="1449"/>
-      <c r="E15" s="1449"/>
-      <c r="F15" s="1449"/>
-      <c r="G15" s="1449"/>
-      <c r="H15" s="1449"/>
-      <c r="I15" s="1449"/>
-      <c r="J15" s="1450"/>
+      <c r="B15" s="1445"/>
+      <c r="C15" s="1445"/>
+      <c r="D15" s="1445"/>
+      <c r="E15" s="1445"/>
+      <c r="F15" s="1445"/>
+      <c r="G15" s="1445"/>
+      <c r="H15" s="1445"/>
+      <c r="I15" s="1445"/>
+      <c r="J15" s="1446"/>
       <c r="K15" s="341"/>
       <c r="M15" s="365"/>
       <c r="N15" s="365"/>
@@ -34960,18 +34963,18 @@
       <c r="AL15" s="315"/>
     </row>
     <row r="16" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1451" t="s">
+      <c r="A16" s="1447" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="1452"/>
-      <c r="C16" s="1452"/>
-      <c r="D16" s="1452"/>
-      <c r="E16" s="1452"/>
-      <c r="F16" s="1452"/>
-      <c r="G16" s="1452"/>
-      <c r="H16" s="1452"/>
-      <c r="I16" s="1452"/>
-      <c r="J16" s="1453"/>
+      <c r="B16" s="1448"/>
+      <c r="C16" s="1448"/>
+      <c r="D16" s="1448"/>
+      <c r="E16" s="1448"/>
+      <c r="F16" s="1448"/>
+      <c r="G16" s="1448"/>
+      <c r="H16" s="1448"/>
+      <c r="I16" s="1448"/>
+      <c r="J16" s="1449"/>
       <c r="K16" s="341"/>
       <c r="L16" s="341"/>
       <c r="M16" s="365"/>
@@ -35040,18 +35043,18 @@
       <c r="AL17" s="315"/>
     </row>
     <row r="18" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1361" t="s">
+      <c r="A18" s="1363" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1362"/>
-      <c r="C18" s="1362"/>
-      <c r="D18" s="1362"/>
-      <c r="E18" s="1362"/>
-      <c r="F18" s="1362"/>
-      <c r="G18" s="1362"/>
-      <c r="H18" s="1362"/>
-      <c r="I18" s="1362"/>
-      <c r="J18" s="1363"/>
+      <c r="B18" s="1364"/>
+      <c r="C18" s="1364"/>
+      <c r="D18" s="1364"/>
+      <c r="E18" s="1364"/>
+      <c r="F18" s="1364"/>
+      <c r="G18" s="1364"/>
+      <c r="H18" s="1364"/>
+      <c r="I18" s="1364"/>
+      <c r="J18" s="1365"/>
       <c r="L18" s="341"/>
       <c r="M18" s="365"/>
       <c r="N18" s="365"/>
@@ -35097,10 +35100,10 @@
       </c>
       <c r="L19" s="341"/>
       <c r="M19" s="361"/>
-      <c r="N19" s="1445" t="s">
+      <c r="N19" s="1441" t="s">
         <v>234</v>
       </c>
-      <c r="O19" s="1445" t="s">
+      <c r="O19" s="1441" t="s">
         <v>235</v>
       </c>
       <c r="P19" s="361"/>
@@ -35152,8 +35155,8 @@
       </c>
       <c r="L20" s="341"/>
       <c r="M20" s="361"/>
-      <c r="N20" s="1446"/>
-      <c r="O20" s="1446"/>
+      <c r="N20" s="1442"/>
+      <c r="O20" s="1442"/>
       <c r="P20" s="371"/>
       <c r="Q20" s="372"/>
       <c r="R20" s="361"/>
@@ -35282,18 +35285,18 @@
       <c r="AL22" s="315"/>
     </row>
     <row r="23" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1454" t="s">
+      <c r="A23" s="1450" t="s">
         <v>239</v>
       </c>
-      <c r="B23" s="1454"/>
-      <c r="C23" s="1454"/>
-      <c r="D23" s="1454"/>
-      <c r="E23" s="1454"/>
-      <c r="F23" s="1454"/>
-      <c r="G23" s="1454"/>
-      <c r="H23" s="1454"/>
-      <c r="I23" s="1454"/>
-      <c r="J23" s="1454"/>
+      <c r="B23" s="1450"/>
+      <c r="C23" s="1450"/>
+      <c r="D23" s="1450"/>
+      <c r="E23" s="1450"/>
+      <c r="F23" s="1450"/>
+      <c r="G23" s="1450"/>
+      <c r="H23" s="1450"/>
+      <c r="I23" s="1450"/>
+      <c r="J23" s="1450"/>
       <c r="K23" s="341"/>
       <c r="L23" s="344"/>
       <c r="M23" s="361"/>
@@ -35736,18 +35739,18 @@
       <c r="AL32" s="315"/>
     </row>
     <row r="33" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1454" t="s">
+      <c r="A33" s="1450" t="s">
         <v>257</v>
       </c>
-      <c r="B33" s="1454"/>
-      <c r="C33" s="1454"/>
-      <c r="D33" s="1454"/>
-      <c r="E33" s="1454"/>
-      <c r="F33" s="1454"/>
-      <c r="G33" s="1454"/>
-      <c r="H33" s="1454"/>
-      <c r="I33" s="1454"/>
-      <c r="J33" s="1454"/>
+      <c r="B33" s="1450"/>
+      <c r="C33" s="1450"/>
+      <c r="D33" s="1450"/>
+      <c r="E33" s="1450"/>
+      <c r="F33" s="1450"/>
+      <c r="G33" s="1450"/>
+      <c r="H33" s="1450"/>
+      <c r="I33" s="1450"/>
+      <c r="J33" s="1450"/>
       <c r="K33" s="437"/>
       <c r="L33" s="437"/>
       <c r="T33" s="314"/>
@@ -35772,15 +35775,15 @@
     </row>
     <row r="34" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="749"/>
-      <c r="B34" s="1444" t="s">
+      <c r="B34" s="1440" t="s">
         <v>258</v>
       </c>
-      <c r="C34" s="1444"/>
-      <c r="D34" s="1444"/>
-      <c r="E34" s="1444"/>
-      <c r="F34" s="1444"/>
-      <c r="G34" s="1444"/>
-      <c r="H34" s="1444"/>
+      <c r="C34" s="1440"/>
+      <c r="D34" s="1440"/>
+      <c r="E34" s="1440"/>
+      <c r="F34" s="1440"/>
+      <c r="G34" s="1440"/>
+      <c r="H34" s="1440"/>
       <c r="I34" s="757"/>
       <c r="J34" s="758"/>
       <c r="K34" s="341"/>
@@ -35850,18 +35853,18 @@
       <c r="AL35" s="315"/>
     </row>
     <row r="36" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1454" t="s">
+      <c r="A36" s="1450" t="s">
         <v>261</v>
       </c>
-      <c r="B36" s="1454"/>
-      <c r="C36" s="1454"/>
-      <c r="D36" s="1454"/>
-      <c r="E36" s="1454"/>
-      <c r="F36" s="1454"/>
-      <c r="G36" s="1454"/>
-      <c r="H36" s="1454"/>
-      <c r="I36" s="1454"/>
-      <c r="J36" s="1454"/>
+      <c r="B36" s="1450"/>
+      <c r="C36" s="1450"/>
+      <c r="D36" s="1450"/>
+      <c r="E36" s="1450"/>
+      <c r="F36" s="1450"/>
+      <c r="G36" s="1450"/>
+      <c r="H36" s="1450"/>
+      <c r="I36" s="1450"/>
+      <c r="J36" s="1450"/>
       <c r="K36" s="341"/>
       <c r="L36" s="341"/>
       <c r="T36" s="314"/>
@@ -35886,15 +35889,15 @@
     </row>
     <row r="37" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="749"/>
-      <c r="B37" s="1444" t="s">
+      <c r="B37" s="1440" t="s">
         <v>262</v>
       </c>
-      <c r="C37" s="1444"/>
-      <c r="D37" s="1444"/>
-      <c r="E37" s="1444"/>
-      <c r="F37" s="1444"/>
-      <c r="G37" s="1444"/>
-      <c r="H37" s="1444"/>
+      <c r="C37" s="1440"/>
+      <c r="D37" s="1440"/>
+      <c r="E37" s="1440"/>
+      <c r="F37" s="1440"/>
+      <c r="G37" s="1440"/>
+      <c r="H37" s="1440"/>
       <c r="I37" s="757"/>
       <c r="J37" s="758"/>
       <c r="K37" s="341"/>
@@ -35997,18 +36000,18 @@
       <c r="AL39" s="315"/>
     </row>
     <row r="40" spans="1:38" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1440" t="s">
+      <c r="A40" s="1454" t="s">
         <v>265</v>
       </c>
-      <c r="B40" s="1440"/>
-      <c r="C40" s="1440"/>
-      <c r="D40" s="1440"/>
-      <c r="E40" s="1440"/>
-      <c r="F40" s="1440"/>
-      <c r="G40" s="1440"/>
-      <c r="H40" s="1440"/>
-      <c r="I40" s="1440"/>
-      <c r="J40" s="1440"/>
+      <c r="B40" s="1454"/>
+      <c r="C40" s="1454"/>
+      <c r="D40" s="1454"/>
+      <c r="E40" s="1454"/>
+      <c r="F40" s="1454"/>
+      <c r="G40" s="1454"/>
+      <c r="H40" s="1454"/>
+      <c r="I40" s="1454"/>
+      <c r="J40" s="1454"/>
       <c r="K40" s="341"/>
       <c r="L40" s="341"/>
       <c r="T40" s="314"/>
@@ -36032,16 +36035,16 @@
       <c r="AL40" s="315"/>
     </row>
     <row r="41" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1440"/>
-      <c r="B41" s="1440"/>
-      <c r="C41" s="1440"/>
-      <c r="D41" s="1440"/>
-      <c r="E41" s="1440"/>
-      <c r="F41" s="1440"/>
-      <c r="G41" s="1440"/>
-      <c r="H41" s="1440"/>
-      <c r="I41" s="1440"/>
-      <c r="J41" s="1440"/>
+      <c r="A41" s="1454"/>
+      <c r="B41" s="1454"/>
+      <c r="C41" s="1454"/>
+      <c r="D41" s="1454"/>
+      <c r="E41" s="1454"/>
+      <c r="F41" s="1454"/>
+      <c r="G41" s="1454"/>
+      <c r="H41" s="1454"/>
+      <c r="I41" s="1454"/>
+      <c r="J41" s="1454"/>
       <c r="K41" s="341"/>
       <c r="L41" s="341"/>
       <c r="T41" s="314"/>
@@ -36065,16 +36068,16 @@
       <c r="AL41" s="315"/>
     </row>
     <row r="42" spans="1:38" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1440"/>
-      <c r="B42" s="1440"/>
-      <c r="C42" s="1440"/>
-      <c r="D42" s="1440"/>
-      <c r="E42" s="1440"/>
-      <c r="F42" s="1440"/>
-      <c r="G42" s="1440"/>
-      <c r="H42" s="1440"/>
-      <c r="I42" s="1440"/>
-      <c r="J42" s="1440"/>
+      <c r="A42" s="1454"/>
+      <c r="B42" s="1454"/>
+      <c r="C42" s="1454"/>
+      <c r="D42" s="1454"/>
+      <c r="E42" s="1454"/>
+      <c r="F42" s="1454"/>
+      <c r="G42" s="1454"/>
+      <c r="H42" s="1454"/>
+      <c r="I42" s="1454"/>
+      <c r="J42" s="1454"/>
       <c r="K42" s="418"/>
       <c r="L42" s="381"/>
       <c r="N42" s="378"/>
@@ -36154,9 +36157,9 @@
       <c r="K44" s="341"/>
       <c r="L44" s="383"/>
       <c r="M44" s="383"/>
-      <c r="N44" s="1332"/>
-      <c r="O44" s="1332"/>
-      <c r="P44" s="1332"/>
+      <c r="N44" s="1340"/>
+      <c r="O44" s="1340"/>
+      <c r="P44" s="1340"/>
       <c r="T44" s="314"/>
       <c r="U44" s="325"/>
       <c r="V44" s="325"/>
@@ -36185,15 +36188,15 @@
       <c r="E45" s="197"/>
       <c r="F45" s="197"/>
       <c r="G45" s="200"/>
-      <c r="H45" s="1331"/>
-      <c r="I45" s="1331"/>
-      <c r="J45" s="1331"/>
+      <c r="H45" s="1379"/>
+      <c r="I45" s="1379"/>
+      <c r="J45" s="1379"/>
       <c r="K45" s="341"/>
       <c r="L45" s="384"/>
       <c r="M45" s="385"/>
-      <c r="N45" s="1442"/>
-      <c r="O45" s="1442"/>
-      <c r="P45" s="1442"/>
+      <c r="N45" s="1451"/>
+      <c r="O45" s="1451"/>
+      <c r="P45" s="1451"/>
       <c r="T45" s="314"/>
       <c r="U45" s="325"/>
       <c r="V45" s="325"/>
@@ -36222,15 +36225,15 @@
       <c r="E46" s="197"/>
       <c r="F46" s="197"/>
       <c r="G46" s="200"/>
-      <c r="H46" s="1332"/>
-      <c r="I46" s="1332"/>
-      <c r="J46" s="1332"/>
+      <c r="H46" s="1340"/>
+      <c r="I46" s="1340"/>
+      <c r="J46" s="1340"/>
       <c r="K46" s="341"/>
       <c r="L46" s="386"/>
       <c r="M46" s="387"/>
-      <c r="N46" s="1332"/>
-      <c r="O46" s="1332"/>
-      <c r="P46" s="1332"/>
+      <c r="N46" s="1340"/>
+      <c r="O46" s="1340"/>
+      <c r="P46" s="1340"/>
       <c r="T46" s="314"/>
       <c r="U46" s="325"/>
       <c r="V46" s="325"/>
@@ -36259,15 +36262,15 @@
       <c r="E47" s="197"/>
       <c r="F47" s="197"/>
       <c r="G47" s="200"/>
-      <c r="H47" s="1442"/>
-      <c r="I47" s="1442"/>
-      <c r="J47" s="1442"/>
+      <c r="H47" s="1451"/>
+      <c r="I47" s="1451"/>
+      <c r="J47" s="1451"/>
       <c r="K47" s="341"/>
       <c r="L47" s="386"/>
       <c r="M47" s="387"/>
-      <c r="N47" s="1331"/>
-      <c r="O47" s="1331"/>
-      <c r="P47" s="1331"/>
+      <c r="N47" s="1379"/>
+      <c r="O47" s="1379"/>
+      <c r="P47" s="1379"/>
       <c r="T47" s="314"/>
       <c r="U47" s="325"/>
       <c r="V47" s="325"/>
@@ -36296,15 +36299,15 @@
       <c r="E48" s="197"/>
       <c r="F48" s="197"/>
       <c r="G48" s="200"/>
-      <c r="H48" s="1332"/>
-      <c r="I48" s="1332"/>
-      <c r="J48" s="1332"/>
+      <c r="H48" s="1340"/>
+      <c r="I48" s="1340"/>
+      <c r="J48" s="1340"/>
       <c r="K48" s="341"/>
       <c r="L48" s="386"/>
       <c r="M48" s="387"/>
-      <c r="N48" s="1443"/>
-      <c r="O48" s="1443"/>
-      <c r="P48" s="1443"/>
+      <c r="N48" s="1453"/>
+      <c r="O48" s="1453"/>
+      <c r="P48" s="1453"/>
       <c r="T48" s="314"/>
       <c r="U48" s="325"/>
       <c r="V48" s="325"/>
@@ -36333,15 +36336,15 @@
       <c r="E49" s="200"/>
       <c r="F49" s="200"/>
       <c r="G49" s="200"/>
-      <c r="H49" s="1331"/>
-      <c r="I49" s="1331"/>
-      <c r="J49" s="1331"/>
+      <c r="H49" s="1379"/>
+      <c r="I49" s="1379"/>
+      <c r="J49" s="1379"/>
       <c r="K49" s="341"/>
       <c r="L49" s="386"/>
       <c r="M49" s="387"/>
-      <c r="N49" s="1442"/>
-      <c r="O49" s="1442"/>
-      <c r="P49" s="1442"/>
+      <c r="N49" s="1451"/>
+      <c r="O49" s="1451"/>
+      <c r="P49" s="1451"/>
       <c r="T49" s="314"/>
       <c r="U49" s="325"/>
       <c r="V49" s="325"/>
@@ -37111,16 +37114,16 @@
       <c r="AL74" s="315"/>
     </row>
     <row r="75" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1440"/>
-      <c r="B75" s="1440"/>
-      <c r="C75" s="1440"/>
-      <c r="D75" s="1440"/>
-      <c r="E75" s="1440"/>
-      <c r="F75" s="1440"/>
-      <c r="G75" s="1440"/>
-      <c r="H75" s="1440"/>
-      <c r="I75" s="1440"/>
-      <c r="J75" s="1440"/>
+      <c r="A75" s="1454"/>
+      <c r="B75" s="1454"/>
+      <c r="C75" s="1454"/>
+      <c r="D75" s="1454"/>
+      <c r="E75" s="1454"/>
+      <c r="F75" s="1454"/>
+      <c r="G75" s="1454"/>
+      <c r="H75" s="1454"/>
+      <c r="I75" s="1454"/>
+      <c r="J75" s="1454"/>
       <c r="T75" s="314"/>
       <c r="U75" s="325"/>
       <c r="V75" s="325"/>
@@ -37142,16 +37145,16 @@
       <c r="AL75" s="315"/>
     </row>
     <row r="76" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1440"/>
-      <c r="B76" s="1440"/>
-      <c r="C76" s="1440"/>
-      <c r="D76" s="1440"/>
-      <c r="E76" s="1440"/>
-      <c r="F76" s="1440"/>
-      <c r="G76" s="1440"/>
-      <c r="H76" s="1440"/>
-      <c r="I76" s="1440"/>
-      <c r="J76" s="1440"/>
+      <c r="A76" s="1454"/>
+      <c r="B76" s="1454"/>
+      <c r="C76" s="1454"/>
+      <c r="D76" s="1454"/>
+      <c r="E76" s="1454"/>
+      <c r="F76" s="1454"/>
+      <c r="G76" s="1454"/>
+      <c r="H76" s="1454"/>
+      <c r="I76" s="1454"/>
+      <c r="J76" s="1454"/>
       <c r="T76" s="314"/>
       <c r="U76" s="325"/>
       <c r="V76" s="325"/>
@@ -37173,16 +37176,16 @@
       <c r="AL76" s="315"/>
     </row>
     <row r="77" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1440"/>
-      <c r="B77" s="1440"/>
-      <c r="C77" s="1440"/>
-      <c r="D77" s="1440"/>
-      <c r="E77" s="1440"/>
-      <c r="F77" s="1440"/>
-      <c r="G77" s="1440"/>
-      <c r="H77" s="1440"/>
-      <c r="I77" s="1440"/>
-      <c r="J77" s="1440"/>
+      <c r="A77" s="1454"/>
+      <c r="B77" s="1454"/>
+      <c r="C77" s="1454"/>
+      <c r="D77" s="1454"/>
+      <c r="E77" s="1454"/>
+      <c r="F77" s="1454"/>
+      <c r="G77" s="1454"/>
+      <c r="H77" s="1454"/>
+      <c r="I77" s="1454"/>
+      <c r="J77" s="1454"/>
       <c r="T77" s="314"/>
       <c r="U77" s="325"/>
       <c r="V77" s="325"/>
@@ -37297,10 +37300,10 @@
       <c r="AL80" s="315"/>
     </row>
     <row r="81" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G81" s="1441"/>
-      <c r="H81" s="1441"/>
-      <c r="I81" s="1441"/>
-      <c r="J81" s="1441"/>
+      <c r="G81" s="1452"/>
+      <c r="H81" s="1452"/>
+      <c r="I81" s="1452"/>
+      <c r="J81" s="1452"/>
       <c r="T81" s="314"/>
       <c r="U81" s="325"/>
       <c r="V81" s="325"/>
@@ -37345,10 +37348,10 @@
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" s="313"/>
-      <c r="G83" s="1441"/>
-      <c r="H83" s="1441"/>
-      <c r="I83" s="1441"/>
-      <c r="J83" s="1441"/>
+      <c r="G83" s="1452"/>
+      <c r="H83" s="1452"/>
+      <c r="I83" s="1452"/>
+      <c r="J83" s="1452"/>
       <c r="T83" s="314"/>
       <c r="U83" s="325"/>
       <c r="V83" s="325"/>
@@ -39830,6 +39833,23 @@
     <protectedRange sqref="C10:C13" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="29">
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A41:J42"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A76:J77"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="N46:P46"/>
     <mergeCell ref="B37:H37"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
@@ -39842,23 +39862,6 @@
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="B34:H34"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="G83:J83"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J42"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A76:J77"/>
-    <mergeCell ref="G81:J81"/>
-    <mergeCell ref="H47:J47"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.78740157480314965" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -40071,19 +40074,19 @@
       <c r="Z6" s="37"/>
     </row>
     <row r="7" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1484" t="s">
+      <c r="A7" s="1462" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1484"/>
-      <c r="C7" s="1484"/>
-      <c r="D7" s="1484"/>
-      <c r="E7" s="1484"/>
-      <c r="F7" s="1484"/>
-      <c r="G7" s="1484"/>
-      <c r="H7" s="1484"/>
-      <c r="I7" s="1484"/>
-      <c r="J7" s="1484"/>
-      <c r="K7" s="1484"/>
+      <c r="B7" s="1462"/>
+      <c r="C7" s="1462"/>
+      <c r="D7" s="1462"/>
+      <c r="E7" s="1462"/>
+      <c r="F7" s="1462"/>
+      <c r="G7" s="1462"/>
+      <c r="H7" s="1462"/>
+      <c r="I7" s="1462"/>
+      <c r="J7" s="1462"/>
+      <c r="K7" s="1462"/>
       <c r="N7" s="309" t="s">
         <v>276</v>
       </c>
@@ -40108,20 +40111,20 @@
       <c r="Z7" s="37"/>
     </row>
     <row r="8" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1485">
+      <c r="A8" s="1463">
         <f>+K12</f>
         <v>1</v>
       </c>
-      <c r="B8" s="1485"/>
-      <c r="C8" s="1485"/>
-      <c r="D8" s="1485"/>
-      <c r="E8" s="1485"/>
-      <c r="F8" s="1485"/>
-      <c r="G8" s="1485"/>
-      <c r="H8" s="1485"/>
-      <c r="I8" s="1485"/>
-      <c r="J8" s="1485"/>
-      <c r="K8" s="1485"/>
+      <c r="B8" s="1463"/>
+      <c r="C8" s="1463"/>
+      <c r="D8" s="1463"/>
+      <c r="E8" s="1463"/>
+      <c r="F8" s="1463"/>
+      <c r="G8" s="1463"/>
+      <c r="H8" s="1463"/>
+      <c r="I8" s="1463"/>
+      <c r="J8" s="1463"/>
+      <c r="K8" s="1463"/>
       <c r="N8" s="769" t="s">
         <v>278</v>
       </c>
@@ -40176,14 +40179,14 @@
       <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1478" t="s">
+      <c r="C10" s="1486" t="s">
         <v>281</v>
       </c>
-      <c r="D10" s="1478"/>
-      <c r="E10" s="1478"/>
-      <c r="F10" s="1478"/>
-      <c r="G10" s="1478"/>
-      <c r="H10" s="1478"/>
+      <c r="D10" s="1486"/>
+      <c r="E10" s="1486"/>
+      <c r="F10" s="1486"/>
+      <c r="G10" s="1486"/>
+      <c r="H10" s="1486"/>
       <c r="I10" s="23" t="s">
         <v>3</v>
       </c>
@@ -40226,14 +40229,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1478" t="s">
+      <c r="C11" s="1486" t="s">
         <v>286</v>
       </c>
-      <c r="D11" s="1478"/>
-      <c r="E11" s="1478"/>
-      <c r="F11" s="1478"/>
-      <c r="G11" s="1478"/>
-      <c r="H11" s="1478"/>
+      <c r="D11" s="1486"/>
+      <c r="E11" s="1486"/>
+      <c r="F11" s="1486"/>
+      <c r="G11" s="1486"/>
+      <c r="H11" s="1486"/>
       <c r="I11" s="26" t="s">
         <v>6</v>
       </c>
@@ -40275,14 +40278,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1478" t="s">
+      <c r="C12" s="1486" t="s">
         <v>291</v>
       </c>
-      <c r="D12" s="1478"/>
-      <c r="E12" s="1478"/>
-      <c r="F12" s="1478"/>
-      <c r="G12" s="1478"/>
-      <c r="H12" s="1478"/>
+      <c r="D12" s="1486"/>
+      <c r="E12" s="1486"/>
+      <c r="F12" s="1486"/>
+      <c r="G12" s="1486"/>
+      <c r="H12" s="1486"/>
       <c r="I12" s="26" t="s">
         <v>292</v>
       </c>
@@ -40362,19 +40365,19 @@
       <c r="Z13" s="37"/>
     </row>
     <row r="14" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1448" t="s">
+      <c r="A14" s="1444" t="s">
         <v>297</v>
       </c>
-      <c r="B14" s="1449"/>
-      <c r="C14" s="1449"/>
-      <c r="D14" s="1449"/>
-      <c r="E14" s="1449"/>
-      <c r="F14" s="1449"/>
-      <c r="G14" s="1449"/>
-      <c r="H14" s="1449"/>
-      <c r="I14" s="1449"/>
-      <c r="J14" s="1449"/>
-      <c r="K14" s="1450"/>
+      <c r="B14" s="1445"/>
+      <c r="C14" s="1445"/>
+      <c r="D14" s="1445"/>
+      <c r="E14" s="1445"/>
+      <c r="F14" s="1445"/>
+      <c r="G14" s="1445"/>
+      <c r="H14" s="1445"/>
+      <c r="I14" s="1445"/>
+      <c r="J14" s="1445"/>
+      <c r="K14" s="1446"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="769" t="s">
@@ -40397,19 +40400,19 @@
       <c r="Z14" s="37"/>
     </row>
     <row r="15" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1451" t="s">
+      <c r="A15" s="1447" t="s">
         <v>299</v>
       </c>
-      <c r="B15" s="1452"/>
-      <c r="C15" s="1452"/>
-      <c r="D15" s="1452"/>
-      <c r="E15" s="1452"/>
-      <c r="F15" s="1452"/>
-      <c r="G15" s="1452"/>
-      <c r="H15" s="1452"/>
-      <c r="I15" s="1452"/>
-      <c r="J15" s="1452"/>
-      <c r="K15" s="1453"/>
+      <c r="B15" s="1448"/>
+      <c r="C15" s="1448"/>
+      <c r="D15" s="1448"/>
+      <c r="E15" s="1448"/>
+      <c r="F15" s="1448"/>
+      <c r="G15" s="1448"/>
+      <c r="H15" s="1448"/>
+      <c r="I15" s="1448"/>
+      <c r="J15" s="1448"/>
+      <c r="K15" s="1449"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="25"/>
@@ -40456,30 +40459,30 @@
       <c r="S16" s="232" t="s">
         <v>303</v>
       </c>
-      <c r="T16" s="1458" t="s">
+      <c r="T16" s="1490" t="s">
         <v>304</v>
       </c>
-      <c r="U16" s="1459"/>
-      <c r="V16" s="1460"/>
+      <c r="U16" s="1491"/>
+      <c r="V16" s="1492"/>
       <c r="W16" s="37"/>
       <c r="X16" s="37"/>
       <c r="Y16" s="37"/>
       <c r="Z16" s="37"/>
     </row>
     <row r="17" spans="1:26" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1475" t="s">
+      <c r="A17" s="1483" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1476"/>
-      <c r="C17" s="1476"/>
-      <c r="D17" s="1476"/>
-      <c r="E17" s="1476"/>
-      <c r="F17" s="1476"/>
-      <c r="G17" s="1476"/>
-      <c r="H17" s="1476"/>
-      <c r="I17" s="1476"/>
-      <c r="J17" s="1476"/>
-      <c r="K17" s="1477"/>
+      <c r="B17" s="1484"/>
+      <c r="C17" s="1484"/>
+      <c r="D17" s="1484"/>
+      <c r="E17" s="1484"/>
+      <c r="F17" s="1484"/>
+      <c r="G17" s="1484"/>
+      <c r="H17" s="1484"/>
+      <c r="I17" s="1484"/>
+      <c r="J17" s="1484"/>
+      <c r="K17" s="1485"/>
       <c r="M17" s="3"/>
       <c r="N17" s="775" t="s">
         <v>234</v>
@@ -40499,11 +40502,11 @@
       <c r="S17" s="776" t="s">
         <v>309</v>
       </c>
-      <c r="T17" s="1455" t="s">
+      <c r="T17" s="1487" t="s">
         <v>310</v>
       </c>
-      <c r="U17" s="1456"/>
-      <c r="V17" s="1457"/>
+      <c r="U17" s="1488"/>
+      <c r="V17" s="1489"/>
       <c r="W17" s="37"/>
       <c r="X17" s="37"/>
       <c r="Y17" s="37"/>
@@ -40763,21 +40766,21 @@
       <c r="Z22" s="37"/>
     </row>
     <row r="23" spans="1:26" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1488" t="s">
+      <c r="A23" s="1466" t="s">
         <v>234</v>
       </c>
-      <c r="B23" s="1489"/>
-      <c r="C23" s="1490"/>
-      <c r="D23" s="1463" t="s">
+      <c r="B23" s="1467"/>
+      <c r="C23" s="1468"/>
+      <c r="D23" s="1494" t="s">
         <v>324</v>
       </c>
       <c r="E23" s="197"/>
-      <c r="F23" s="1491" t="s">
+      <c r="F23" s="1470" t="s">
         <v>325</v>
       </c>
-      <c r="G23" s="1492"/>
-      <c r="H23" s="1493"/>
-      <c r="I23" s="1468" t="s">
+      <c r="G23" s="1471"/>
+      <c r="H23" s="1472"/>
+      <c r="I23" s="1476" t="s">
         <v>321</v>
       </c>
       <c r="J23" s="191"/>
@@ -40821,16 +40824,16 @@
       <c r="A24" s="785" t="s">
         <v>327</v>
       </c>
-      <c r="B24" s="1487" t="s">
+      <c r="B24" s="1465" t="s">
         <v>305</v>
       </c>
-      <c r="C24" s="1487"/>
-      <c r="D24" s="1464"/>
+      <c r="C24" s="1465"/>
+      <c r="D24" s="1495"/>
       <c r="E24" s="197"/>
-      <c r="F24" s="1494"/>
-      <c r="G24" s="1495"/>
-      <c r="H24" s="1496"/>
-      <c r="I24" s="1497"/>
+      <c r="F24" s="1473"/>
+      <c r="G24" s="1474"/>
+      <c r="H24" s="1475"/>
+      <c r="I24" s="1477"/>
       <c r="J24" s="191"/>
       <c r="K24" s="192"/>
       <c r="L24" s="3"/>
@@ -40868,10 +40871,10 @@
       <c r="A25" s="786" t="s">
         <v>314</v>
       </c>
-      <c r="B25" s="1486">
+      <c r="B25" s="1464">
         <v>76.2</v>
       </c>
-      <c r="C25" s="1486"/>
+      <c r="C25" s="1464"/>
       <c r="D25" s="787">
         <f>+S18</f>
         <v>100</v>
@@ -40922,21 +40925,21 @@
       <c r="A26" s="198" t="s">
         <v>321</v>
       </c>
-      <c r="B26" s="1462">
+      <c r="B26" s="1469">
         <v>50.6</v>
       </c>
-      <c r="C26" s="1462"/>
+      <c r="C26" s="1469"/>
       <c r="D26" s="199">
         <f>+S20</f>
         <v>96.737365729020368</v>
       </c>
       <c r="E26" s="197"/>
-      <c r="F26" s="1488" t="s">
+      <c r="F26" s="1466" t="s">
         <v>330</v>
       </c>
-      <c r="G26" s="1489"/>
-      <c r="H26" s="1489"/>
-      <c r="I26" s="1490"/>
+      <c r="G26" s="1467"/>
+      <c r="H26" s="1467"/>
+      <c r="I26" s="1468"/>
       <c r="J26" s="200"/>
       <c r="K26" s="201"/>
       <c r="L26" s="3"/>
@@ -40974,19 +40977,19 @@
       <c r="A27" s="202" t="s">
         <v>322</v>
       </c>
-      <c r="B27" s="1462">
+      <c r="B27" s="1469">
         <v>38.1</v>
       </c>
-      <c r="C27" s="1462"/>
+      <c r="C27" s="1469"/>
       <c r="D27" s="199">
         <f>+S21</f>
         <v>90.324022891039832</v>
       </c>
       <c r="E27" s="197"/>
-      <c r="F27" s="1498"/>
-      <c r="G27" s="1499"/>
-      <c r="H27" s="1499"/>
-      <c r="I27" s="1500"/>
+      <c r="F27" s="1478"/>
+      <c r="G27" s="1479"/>
+      <c r="H27" s="1479"/>
+      <c r="I27" s="1480"/>
       <c r="J27" s="200"/>
       <c r="K27" s="201"/>
       <c r="L27" s="3"/>
@@ -41028,19 +41031,19 @@
       <c r="A28" s="198" t="s">
         <v>323</v>
       </c>
-      <c r="B28" s="1462">
+      <c r="B28" s="1469">
         <v>25.4</v>
       </c>
-      <c r="C28" s="1462"/>
+      <c r="C28" s="1469"/>
       <c r="D28" s="199">
         <f>+S22</f>
         <v>84.873241107276272</v>
       </c>
       <c r="E28" s="197"/>
-      <c r="F28" s="1471" t="s">
+      <c r="F28" s="1481" t="s">
         <v>333</v>
       </c>
-      <c r="G28" s="1473">
+      <c r="G28" s="1482">
         <f>R27</f>
         <v>45.788805497693524</v>
       </c>
@@ -41088,17 +41091,17 @@
       <c r="A29" s="198" t="s">
         <v>326</v>
       </c>
-      <c r="B29" s="1462">
+      <c r="B29" s="1469">
         <v>19.05</v>
       </c>
-      <c r="C29" s="1462"/>
+      <c r="C29" s="1469"/>
       <c r="D29" s="199">
         <f>+S23</f>
         <v>73.456819301447041</v>
       </c>
       <c r="E29" s="197"/>
-      <c r="F29" s="1472"/>
-      <c r="G29" s="1474"/>
+      <c r="F29" s="1457"/>
+      <c r="G29" s="1460"/>
       <c r="H29" s="203" t="s">
         <v>335</v>
       </c>
@@ -41147,19 +41150,19 @@
       <c r="A30" s="198" t="s">
         <v>329</v>
       </c>
-      <c r="B30" s="1462">
+      <c r="B30" s="1469">
         <v>9.5250000000000004</v>
       </c>
-      <c r="C30" s="1462"/>
+      <c r="C30" s="1469"/>
       <c r="D30" s="199">
         <f>+S25</f>
         <v>62.661585152699679</v>
       </c>
       <c r="E30" s="197"/>
-      <c r="F30" s="1479" t="s">
+      <c r="F30" s="1455" t="s">
         <v>336</v>
       </c>
-      <c r="G30" s="1481">
+      <c r="G30" s="1458">
         <f>100-(G28+G33)</f>
         <v>40.754382185876274</v>
       </c>
@@ -41207,17 +41210,17 @@
       <c r="A31" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="B31" s="1462">
+      <c r="B31" s="1469">
         <v>4.76</v>
       </c>
-      <c r="C31" s="1462"/>
+      <c r="C31" s="1469"/>
       <c r="D31" s="199">
         <f>+S27</f>
         <v>54.211194502306476</v>
       </c>
       <c r="E31" s="197"/>
-      <c r="F31" s="1480"/>
-      <c r="G31" s="1482"/>
+      <c r="F31" s="1456"/>
+      <c r="G31" s="1459"/>
       <c r="H31" s="203" t="s">
         <v>337</v>
       </c>
@@ -41265,17 +41268,17 @@
       <c r="A32" s="198">
         <v>8</v>
       </c>
-      <c r="B32" s="1462">
+      <c r="B32" s="1469">
         <v>2.36</v>
       </c>
-      <c r="C32" s="1462"/>
+      <c r="C32" s="1469"/>
       <c r="D32" s="199">
         <f>+S28</f>
         <v>49.032616067382399</v>
       </c>
       <c r="E32" s="197"/>
-      <c r="F32" s="1472"/>
-      <c r="G32" s="1474"/>
+      <c r="F32" s="1457"/>
+      <c r="G32" s="1460"/>
       <c r="H32" s="203" t="s">
         <v>335</v>
       </c>
@@ -41327,10 +41330,10 @@
       <c r="A33" s="198">
         <v>16</v>
       </c>
-      <c r="B33" s="1462">
+      <c r="B33" s="1469">
         <v>1.19</v>
       </c>
-      <c r="C33" s="1462"/>
+      <c r="C33" s="1469"/>
       <c r="D33" s="199">
         <f t="shared" ref="D33:D38" si="4">+S30</f>
         <v>40.351707913359583</v>
@@ -41385,10 +41388,10 @@
       <c r="A34" s="198">
         <v>30</v>
       </c>
-      <c r="B34" s="1462">
+      <c r="B34" s="1469">
         <v>0.6</v>
       </c>
-      <c r="C34" s="1462"/>
+      <c r="C34" s="1469"/>
       <c r="D34" s="199">
         <f t="shared" si="4"/>
         <v>31.408593256302638</v>
@@ -41435,25 +41438,25 @@
       <c r="A35" s="198">
         <v>40</v>
       </c>
-      <c r="B35" s="1462">
+      <c r="B35" s="1469">
         <v>0.42</v>
       </c>
-      <c r="C35" s="1462"/>
+      <c r="C35" s="1469"/>
       <c r="D35" s="199">
         <f t="shared" si="4"/>
         <v>27.175831135894526</v>
       </c>
       <c r="E35" s="197"/>
-      <c r="F35" s="1465" t="str">
+      <c r="F35" s="1496" t="str">
         <f>IF(O3="No","","Clasificacion SUCS")</f>
         <v/>
       </c>
-      <c r="G35" s="1465"/>
-      <c r="H35" s="1468" t="str">
+      <c r="G35" s="1496"/>
+      <c r="H35" s="1476" t="str">
         <f>IF(O3="No","",'Sucs '!G4)</f>
         <v/>
       </c>
-      <c r="I35" s="1468"/>
+      <c r="I35" s="1476"/>
       <c r="J35" s="200"/>
       <c r="K35" s="201"/>
       <c r="L35" s="3"/>
@@ -41495,19 +41498,19 @@
       <c r="A36" s="198">
         <v>50</v>
       </c>
-      <c r="B36" s="1462">
+      <c r="B36" s="1469">
         <v>0.3</v>
       </c>
-      <c r="C36" s="1462"/>
+      <c r="C36" s="1469"/>
       <c r="D36" s="199">
         <f t="shared" si="4"/>
         <v>23.785875632381845</v>
       </c>
       <c r="E36" s="197"/>
-      <c r="F36" s="1466"/>
-      <c r="G36" s="1466"/>
-      <c r="H36" s="1469"/>
-      <c r="I36" s="1469"/>
+      <c r="F36" s="1497"/>
+      <c r="G36" s="1497"/>
+      <c r="H36" s="1499"/>
+      <c r="I36" s="1499"/>
       <c r="J36" s="200"/>
       <c r="K36" s="201"/>
       <c r="L36" s="3"/>
@@ -41546,25 +41549,25 @@
       <c r="A37" s="198">
         <v>100</v>
       </c>
-      <c r="B37" s="1462">
+      <c r="B37" s="1469">
         <v>0.14899999999999999</v>
       </c>
-      <c r="C37" s="1462"/>
+      <c r="C37" s="1469"/>
       <c r="D37" s="199">
         <f t="shared" si="4"/>
         <v>17.820677688355374</v>
       </c>
       <c r="E37" s="197"/>
-      <c r="F37" s="1466" t="str">
+      <c r="F37" s="1497" t="str">
         <f>IF(O3="No","","Clasificacion AASHTO")</f>
         <v/>
       </c>
-      <c r="G37" s="1466"/>
-      <c r="H37" s="1469" t="str">
+      <c r="G37" s="1497"/>
+      <c r="H37" s="1499" t="str">
         <f>IF(O3="No","",Aashto!J26)</f>
         <v/>
       </c>
-      <c r="I37" s="1469"/>
+      <c r="I37" s="1499"/>
       <c r="J37" s="200"/>
       <c r="K37" s="201"/>
       <c r="L37" s="3"/>
@@ -41590,19 +41593,19 @@
       <c r="A38" s="208">
         <v>200</v>
       </c>
-      <c r="B38" s="1461">
+      <c r="B38" s="1493">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="C38" s="1461"/>
+      <c r="C38" s="1493"/>
       <c r="D38" s="209">
         <f t="shared" si="4"/>
         <v>13.456812316430202</v>
       </c>
       <c r="E38" s="197"/>
-      <c r="F38" s="1467"/>
-      <c r="G38" s="1467"/>
-      <c r="H38" s="1470"/>
-      <c r="I38" s="1470"/>
+      <c r="F38" s="1498"/>
+      <c r="G38" s="1498"/>
+      <c r="H38" s="1500"/>
+      <c r="I38" s="1500"/>
       <c r="J38" s="200"/>
       <c r="K38" s="201"/>
       <c r="L38" s="3"/>
@@ -42494,19 +42497,19 @@
       <c r="Z63" s="37"/>
     </row>
     <row r="64" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1483" t="s">
+      <c r="A64" s="1461" t="s">
         <v>349</v>
       </c>
-      <c r="B64" s="1483"/>
-      <c r="C64" s="1483"/>
-      <c r="D64" s="1483"/>
-      <c r="E64" s="1483"/>
-      <c r="F64" s="1483"/>
-      <c r="G64" s="1483"/>
-      <c r="H64" s="1483"/>
-      <c r="I64" s="1483"/>
-      <c r="J64" s="1483"/>
-      <c r="K64" s="1483"/>
+      <c r="B64" s="1461"/>
+      <c r="C64" s="1461"/>
+      <c r="D64" s="1461"/>
+      <c r="E64" s="1461"/>
+      <c r="F64" s="1461"/>
+      <c r="G64" s="1461"/>
+      <c r="H64" s="1461"/>
+      <c r="I64" s="1461"/>
+      <c r="J64" s="1461"/>
+      <c r="K64" s="1461"/>
       <c r="W64" s="37"/>
       <c r="X64" s="37"/>
       <c r="Y64" s="37"/>
@@ -42542,6 +42545,29 @@
     <protectedRange sqref="C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="F35:G36"/>
+    <mergeCell ref="F37:G38"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
     <mergeCell ref="F30:F32"/>
     <mergeCell ref="G30:G32"/>
     <mergeCell ref="A64:K64"/>
@@ -42558,29 +42584,6 @@
     <mergeCell ref="F23:H24"/>
     <mergeCell ref="I23:I24"/>
     <mergeCell ref="F26:I27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="F35:G36"/>
-    <mergeCell ref="F37:G38"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="H37:I38"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -42708,35 +42711,35 @@
       <c r="K7" s="118"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1502" t="s">
+      <c r="A8" s="1520" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1502"/>
-      <c r="C8" s="1502"/>
-      <c r="D8" s="1502"/>
-      <c r="E8" s="1502"/>
-      <c r="F8" s="1502"/>
-      <c r="G8" s="1502"/>
-      <c r="H8" s="1502"/>
-      <c r="I8" s="1502"/>
-      <c r="J8" s="1502"/>
-      <c r="K8" s="1502"/>
+      <c r="B8" s="1520"/>
+      <c r="C8" s="1520"/>
+      <c r="D8" s="1520"/>
+      <c r="E8" s="1520"/>
+      <c r="F8" s="1520"/>
+      <c r="G8" s="1520"/>
+      <c r="H8" s="1520"/>
+      <c r="I8" s="1520"/>
+      <c r="J8" s="1520"/>
+      <c r="K8" s="1520"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1503">
+      <c r="A9" s="1521">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="1503"/>
-      <c r="C9" s="1503"/>
-      <c r="D9" s="1503"/>
-      <c r="E9" s="1503"/>
-      <c r="F9" s="1503"/>
-      <c r="G9" s="1503"/>
-      <c r="H9" s="1503"/>
-      <c r="I9" s="1503"/>
-      <c r="J9" s="1503"/>
-      <c r="K9" s="1503"/>
+      <c r="B9" s="1521"/>
+      <c r="C9" s="1521"/>
+      <c r="D9" s="1521"/>
+      <c r="E9" s="1521"/>
+      <c r="F9" s="1521"/>
+      <c r="G9" s="1521"/>
+      <c r="H9" s="1521"/>
+      <c r="I9" s="1521"/>
+      <c r="J9" s="1521"/>
+      <c r="K9" s="1521"/>
       <c r="O9" s="119"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -42759,14 +42762,14 @@
       <c r="B11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="1504" t="s">
+      <c r="C11" s="1522" t="s">
         <v>281</v>
       </c>
-      <c r="D11" s="1504"/>
-      <c r="E11" s="1504"/>
-      <c r="F11" s="1504"/>
-      <c r="G11" s="1504"/>
-      <c r="H11" s="1504"/>
+      <c r="D11" s="1522"/>
+      <c r="E11" s="1522"/>
+      <c r="F11" s="1522"/>
+      <c r="G11" s="1522"/>
+      <c r="H11" s="1522"/>
       <c r="I11" s="121" t="s">
         <v>3</v>
       </c>
@@ -42787,14 +42790,14 @@
       <c r="B12" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="1504" t="s">
+      <c r="C12" s="1522" t="s">
         <v>286</v>
       </c>
-      <c r="D12" s="1504"/>
-      <c r="E12" s="1504"/>
-      <c r="F12" s="1504"/>
-      <c r="G12" s="1504"/>
-      <c r="H12" s="1504"/>
+      <c r="D12" s="1522"/>
+      <c r="E12" s="1522"/>
+      <c r="F12" s="1522"/>
+      <c r="G12" s="1522"/>
+      <c r="H12" s="1522"/>
       <c r="I12" s="26" t="s">
         <v>6</v>
       </c>
@@ -42818,14 +42821,14 @@
       <c r="B13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1504" t="s">
+      <c r="C13" s="1522" t="s">
         <v>291</v>
       </c>
-      <c r="D13" s="1504"/>
-      <c r="E13" s="1504"/>
-      <c r="F13" s="1504"/>
-      <c r="G13" s="1504"/>
-      <c r="H13" s="1504"/>
+      <c r="D13" s="1522"/>
+      <c r="E13" s="1522"/>
+      <c r="F13" s="1522"/>
+      <c r="G13" s="1522"/>
+      <c r="H13" s="1522"/>
       <c r="I13" s="26" t="s">
         <v>292</v>
       </c>
@@ -42839,8 +42842,8 @@
       <c r="M13" s="124"/>
       <c r="P13" s="127"/>
       <c r="Q13" s="127"/>
-      <c r="R13" s="1501"/>
-      <c r="S13" s="1501"/>
+      <c r="R13" s="1519"/>
+      <c r="S13" s="1519"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
@@ -42862,19 +42865,19 @@
       <c r="S14" s="737"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1505" t="s">
+      <c r="A15" s="1508" t="s">
         <v>351</v>
       </c>
-      <c r="B15" s="1506"/>
-      <c r="C15" s="1506"/>
-      <c r="D15" s="1506"/>
-      <c r="E15" s="1506"/>
-      <c r="F15" s="1506"/>
-      <c r="G15" s="1506"/>
-      <c r="H15" s="1506"/>
-      <c r="I15" s="1506"/>
-      <c r="J15" s="1506"/>
-      <c r="K15" s="1507"/>
+      <c r="B15" s="1509"/>
+      <c r="C15" s="1509"/>
+      <c r="D15" s="1509"/>
+      <c r="E15" s="1509"/>
+      <c r="F15" s="1509"/>
+      <c r="G15" s="1509"/>
+      <c r="H15" s="1509"/>
+      <c r="I15" s="1509"/>
+      <c r="J15" s="1509"/>
+      <c r="K15" s="1510"/>
       <c r="L15" s="124"/>
       <c r="M15" s="124"/>
       <c r="P15" s="127"/>
@@ -42883,19 +42886,19 @@
       <c r="S15" s="737"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1508" t="s">
+      <c r="A16" s="1511" t="s">
         <v>352</v>
       </c>
-      <c r="B16" s="1509"/>
-      <c r="C16" s="1509"/>
-      <c r="D16" s="1509"/>
-      <c r="E16" s="1509"/>
-      <c r="F16" s="1509"/>
-      <c r="G16" s="1509"/>
-      <c r="H16" s="1509"/>
-      <c r="I16" s="1509"/>
-      <c r="J16" s="1509"/>
-      <c r="K16" s="1510"/>
+      <c r="B16" s="1512"/>
+      <c r="C16" s="1512"/>
+      <c r="D16" s="1512"/>
+      <c r="E16" s="1512"/>
+      <c r="F16" s="1512"/>
+      <c r="G16" s="1512"/>
+      <c r="H16" s="1512"/>
+      <c r="I16" s="1512"/>
+      <c r="J16" s="1512"/>
+      <c r="K16" s="1513"/>
       <c r="L16" s="124"/>
       <c r="M16" s="124"/>
       <c r="P16" s="127"/>
@@ -42923,19 +42926,19 @@
       <c r="S17" s="737"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1475" t="s">
+      <c r="A18" s="1483" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1476"/>
-      <c r="C18" s="1476"/>
-      <c r="D18" s="1476"/>
-      <c r="E18" s="1476"/>
-      <c r="F18" s="1476"/>
-      <c r="G18" s="1476"/>
-      <c r="H18" s="1476"/>
-      <c r="I18" s="1476"/>
-      <c r="J18" s="1476"/>
-      <c r="K18" s="1477"/>
+      <c r="B18" s="1484"/>
+      <c r="C18" s="1484"/>
+      <c r="D18" s="1484"/>
+      <c r="E18" s="1484"/>
+      <c r="F18" s="1484"/>
+      <c r="G18" s="1484"/>
+      <c r="H18" s="1484"/>
+      <c r="I18" s="1484"/>
+      <c r="J18" s="1484"/>
+      <c r="K18" s="1485"/>
       <c r="M18" s="124"/>
       <c r="P18" s="127"/>
       <c r="Q18" s="127"/>
@@ -43052,8 +43055,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="805"/>
-      <c r="I23" s="1511"/>
-      <c r="J23" s="1511"/>
+      <c r="I23" s="1514"/>
+      <c r="J23" s="1514"/>
       <c r="K23" s="806"/>
       <c r="L23" s="124"/>
       <c r="M23" s="139"/>
@@ -43061,41 +43064,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="141"/>
-      <c r="D24" s="1512" t="s">
+      <c r="D24" s="1515" t="s">
         <v>355</v>
       </c>
-      <c r="E24" s="1513"/>
-      <c r="F24" s="1513"/>
-      <c r="G24" s="1514" t="s">
+      <c r="E24" s="1516"/>
+      <c r="F24" s="1516"/>
+      <c r="G24" s="1517" t="s">
         <v>356</v>
       </c>
-      <c r="H24" s="1515"/>
-      <c r="I24" s="1516"/>
-      <c r="J24" s="1516"/>
+      <c r="H24" s="1518"/>
+      <c r="I24" s="1506"/>
+      <c r="J24" s="1506"/>
       <c r="K24" s="142"/>
       <c r="L24" s="124"/>
       <c r="M24" s="143"/>
-      <c r="O24" s="1517" t="s">
+      <c r="O24" s="1501" t="s">
         <v>355</v>
       </c>
-      <c r="P24" s="1518"/>
+      <c r="P24" s="1502"/>
       <c r="Q24" s="807" t="s">
         <v>354</v>
       </c>
-      <c r="R24" s="1517" t="s">
+      <c r="R24" s="1501" t="s">
         <v>356</v>
       </c>
-      <c r="S24" s="1519"/>
+      <c r="S24" s="1503"/>
       <c r="T24" s="807" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="141"/>
-      <c r="B25" s="1520" t="s">
+      <c r="B25" s="1504" t="s">
         <v>357</v>
       </c>
-      <c r="C25" s="1521"/>
+      <c r="C25" s="1505"/>
       <c r="D25" s="808" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -43116,8 +43119,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="1516"/>
-      <c r="J25" s="1516"/>
+      <c r="I25" s="1506"/>
+      <c r="J25" s="1506"/>
       <c r="K25" s="142"/>
       <c r="L25" s="124"/>
       <c r="M25" s="143"/>
@@ -43166,8 +43169,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="1522"/>
-      <c r="J26" s="1522"/>
+      <c r="I26" s="1507"/>
+      <c r="J26" s="1507"/>
       <c r="K26" s="151"/>
       <c r="L26" s="152"/>
       <c r="M26" s="143"/>
@@ -43882,19 +43885,19 @@
     </row>
     <row r="49" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1483" t="s">
+      <c r="A50" s="1461" t="s">
         <v>349</v>
       </c>
-      <c r="B50" s="1483"/>
-      <c r="C50" s="1483"/>
-      <c r="D50" s="1483"/>
-      <c r="E50" s="1483"/>
-      <c r="F50" s="1483"/>
-      <c r="G50" s="1483"/>
-      <c r="H50" s="1483"/>
-      <c r="I50" s="1483"/>
-      <c r="J50" s="1483"/>
-      <c r="K50" s="1483"/>
+      <c r="B50" s="1461"/>
+      <c r="C50" s="1461"/>
+      <c r="D50" s="1461"/>
+      <c r="E50" s="1461"/>
+      <c r="F50" s="1461"/>
+      <c r="G50" s="1461"/>
+      <c r="H50" s="1461"/>
+      <c r="I50" s="1461"/>
+      <c r="J50" s="1461"/>
+      <c r="K50" s="1461"/>
     </row>
     <row r="51" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -43904,11 +43907,12 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -43917,12 +43921,11 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0700-000000000000}">
